--- a/edb_data/NAND合约平均价格.xlsx
+++ b/edb_data/NAND合约平均价格.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8615"/>
+    <workbookView windowWidth="27948" windowHeight="11855"/>
   </bookViews>
   <sheets>
     <sheet name="合约平均价_NAND Flash(64G" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1266,10 +1266,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D300"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.8888888888889"/>
+    <col min="2" max="4" width="20.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1294,231 +1295,231 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3">
-        <v>46142</v>
+        <v>46171</v>
       </c>
       <c r="B3" s="4">
-        <v>17.325</v>
+        <v>19.165</v>
       </c>
       <c r="C3" s="4">
-        <v>14.1</v>
+        <v>15.493</v>
       </c>
       <c r="D3" s="4">
-        <v>24.158</v>
+        <v>26.508</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B4" s="4">
-        <v>12.713</v>
+        <v>17.325</v>
       </c>
       <c r="C4" s="4">
-        <v>10.45</v>
+        <v>14.1</v>
       </c>
       <c r="D4" s="4">
-        <v>17.725</v>
+        <v>24.158</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3">
-        <v>46079</v>
+        <v>46112</v>
       </c>
       <c r="B5" s="4">
-        <v>8.513</v>
+        <v>12.713</v>
       </c>
       <c r="C5" s="4">
-        <v>7.208</v>
+        <v>10.45</v>
       </c>
       <c r="D5" s="4">
-        <v>12.665</v>
+        <v>17.725</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="B6" s="4">
-        <v>7.023</v>
+        <v>8.513</v>
       </c>
       <c r="C6" s="4">
-        <v>5.57</v>
+        <v>7.208</v>
       </c>
       <c r="D6" s="4">
-        <v>9.458</v>
+        <v>12.665</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="B7" s="4">
-        <v>4.59</v>
+        <v>7.023</v>
       </c>
       <c r="C7" s="4">
-        <v>3.66</v>
+        <v>5.57</v>
       </c>
       <c r="D7" s="4">
-        <v>5.738</v>
+        <v>9.458</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="B8" s="4">
-        <v>4.02</v>
+        <v>4.59</v>
       </c>
       <c r="C8" s="4">
-        <v>3.295</v>
+        <v>3.66</v>
       </c>
       <c r="D8" s="4">
-        <v>5.19</v>
+        <v>5.738</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3">
-        <v>45961</v>
+        <v>45989</v>
       </c>
       <c r="B9" s="4">
-        <v>3.333</v>
+        <v>4.02</v>
       </c>
       <c r="C9" s="4">
-        <v>2.795</v>
+        <v>3.295</v>
       </c>
       <c r="D9" s="4">
-        <v>4.35</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B10" s="4">
-        <v>2.825</v>
+        <v>3.333</v>
       </c>
       <c r="C10" s="4">
-        <v>2.39</v>
+        <v>2.795</v>
       </c>
       <c r="D10" s="4">
-        <v>3.785</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3">
-        <v>45898</v>
+        <v>45930</v>
       </c>
       <c r="B11" s="4">
-        <v>2.44</v>
+        <v>2.825</v>
       </c>
       <c r="C11" s="4">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="D11" s="4">
-        <v>3.423</v>
+        <v>3.785</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3">
-        <v>45869</v>
+        <v>45898</v>
       </c>
       <c r="B12" s="4">
-        <v>2.408</v>
+        <v>2.44</v>
       </c>
       <c r="C12" s="4">
-        <v>2.035</v>
+        <v>2.05</v>
       </c>
       <c r="D12" s="4">
-        <v>3.385</v>
+        <v>3.423</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B13" s="4">
-        <v>2.23</v>
+        <v>2.408</v>
       </c>
       <c r="C13" s="4">
-        <v>1.878</v>
+        <v>2.035</v>
       </c>
       <c r="D13" s="4">
-        <v>3.115</v>
+        <v>3.385</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3">
-        <v>45806</v>
+        <v>45838</v>
       </c>
       <c r="B14" s="4">
-        <v>2.028</v>
+        <v>2.23</v>
       </c>
       <c r="C14" s="4">
-        <v>1.74</v>
+        <v>1.878</v>
       </c>
       <c r="D14" s="4">
-        <v>2.923</v>
+        <v>3.115</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3">
-        <v>45777</v>
+        <v>45806</v>
       </c>
       <c r="B15" s="4">
-        <v>1.925</v>
+        <v>2.028</v>
       </c>
       <c r="C15" s="4">
-        <v>1.655</v>
+        <v>1.74</v>
       </c>
       <c r="D15" s="4">
-        <v>2.788</v>
+        <v>2.923</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B16" s="4">
-        <v>0</v>
+        <v>1.925</v>
       </c>
       <c r="C16" s="4">
-        <v>1.455</v>
+        <v>1.655</v>
       </c>
       <c r="D16" s="4">
-        <v>2.51</v>
+        <v>2.788</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3">
-        <v>45715</v>
+        <v>45747</v>
       </c>
       <c r="B17" s="4">
         <v>0</v>
       </c>
       <c r="C17" s="4">
-        <v>1.318</v>
+        <v>1.455</v>
       </c>
       <c r="D17" s="4">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3">
-        <v>45681</v>
+        <v>45715</v>
       </c>
       <c r="B18" s="4">
         <v>0</v>
       </c>
       <c r="C18" s="4">
-        <v>0</v>
+        <v>1.318</v>
       </c>
       <c r="D18" s="4">
-        <v>2.175</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3">
-        <v>45657</v>
+        <v>45681</v>
       </c>
       <c r="B19" s="4">
         <v>0</v>
@@ -1527,12 +1528,12 @@
         <v>0</v>
       </c>
       <c r="D19" s="4">
-        <v>2.08</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3">
-        <v>45625</v>
+        <v>45657</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -1541,54 +1542,54 @@
         <v>0</v>
       </c>
       <c r="D20" s="4">
-        <v>2.155</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3">
-        <v>45596</v>
+        <v>45625</v>
       </c>
       <c r="B21" s="4">
-        <v>2.388</v>
+        <v>0</v>
       </c>
       <c r="C21" s="4">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="D21" s="4">
-        <v>3.07</v>
+        <v>2.155</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="3">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B22" s="4">
-        <v>2.985</v>
+        <v>2.388</v>
       </c>
       <c r="C22" s="4">
-        <v>2.349</v>
+        <v>1.81</v>
       </c>
       <c r="D22" s="4">
-        <v>4.335</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="3">
-        <v>45534</v>
+        <v>45565</v>
       </c>
       <c r="B23" s="4">
-        <v>3.385</v>
+        <v>2.985</v>
       </c>
       <c r="C23" s="4">
-        <v>2.604</v>
+        <v>2.349</v>
       </c>
       <c r="D23" s="4">
-        <v>4.895</v>
+        <v>4.335</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="3">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B24" s="4">
         <v>3.385</v>
@@ -1602,7 +1603,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="3">
-        <v>45471</v>
+        <v>45504</v>
       </c>
       <c r="B25" s="4">
         <v>3.385</v>
@@ -1616,7 +1617,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="3">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B26" s="4">
         <v>3.385</v>
@@ -1630,7 +1631,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="3">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B27" s="4">
         <v>3.385</v>
@@ -1644,7 +1645,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="3">
-        <v>45380</v>
+        <v>45412</v>
       </c>
       <c r="B28" s="4">
         <v>3.385</v>
@@ -1658,7 +1659,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="3">
-        <v>45351</v>
+        <v>45380</v>
       </c>
       <c r="B29" s="4">
         <v>3.385</v>
@@ -1672,77 +1673,77 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="3">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B30" s="4">
-        <v>3.278</v>
+        <v>3.385</v>
       </c>
       <c r="C30" s="4">
         <v>2.604</v>
       </c>
       <c r="D30" s="4">
-        <v>4.715</v>
+        <v>4.895</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="3">
-        <v>45289</v>
+        <v>45322</v>
       </c>
       <c r="B31" s="4">
-        <v>3.02</v>
+        <v>3.278</v>
       </c>
       <c r="C31" s="4">
-        <v>2.57</v>
+        <v>2.604</v>
       </c>
       <c r="D31" s="4">
-        <v>4.331</v>
+        <v>4.715</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3">
-        <v>45260</v>
+        <v>45289</v>
       </c>
       <c r="B32" s="4">
-        <v>2.915</v>
+        <v>3.02</v>
       </c>
       <c r="C32" s="4">
-        <v>2.516</v>
+        <v>2.57</v>
       </c>
       <c r="D32" s="4">
-        <v>4.085</v>
+        <v>4.331</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="3">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B33" s="4">
-        <v>2.794</v>
+        <v>2.915</v>
       </c>
       <c r="C33" s="4">
-        <v>2.469</v>
+        <v>2.516</v>
       </c>
       <c r="D33" s="4">
-        <v>3.876</v>
+        <v>4.085</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3">
-        <v>45197</v>
+        <v>45230</v>
       </c>
       <c r="B34" s="4">
-        <v>2.76</v>
+        <v>2.794</v>
       </c>
       <c r="C34" s="4">
-        <v>2.433</v>
+        <v>2.469</v>
       </c>
       <c r="D34" s="4">
-        <v>3.815</v>
+        <v>3.876</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3">
-        <v>45169</v>
+        <v>45197</v>
       </c>
       <c r="B35" s="4">
         <v>2.76</v>
@@ -1756,7 +1757,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B36" s="4">
         <v>2.76</v>
@@ -1770,7 +1771,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B37" s="4">
         <v>2.76</v>
@@ -1784,7 +1785,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B38" s="4">
         <v>2.76</v>
@@ -1798,7 +1799,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3">
-        <v>45044</v>
+        <v>45077</v>
       </c>
       <c r="B39" s="4">
         <v>2.76</v>
@@ -1812,35 +1813,35 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3">
-        <v>45016</v>
+        <v>45044</v>
       </c>
       <c r="B40" s="4">
-        <v>2.838</v>
+        <v>2.76</v>
       </c>
       <c r="C40" s="4">
-        <v>2.461</v>
+        <v>2.433</v>
       </c>
       <c r="D40" s="4">
-        <v>3.93</v>
+        <v>3.815</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3">
-        <v>44981</v>
+        <v>45016</v>
       </c>
       <c r="B41" s="4">
-        <v>2.983</v>
+        <v>2.838</v>
       </c>
       <c r="C41" s="4">
-        <v>2.587</v>
+        <v>2.461</v>
       </c>
       <c r="D41" s="4">
-        <v>4.142</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="3">
-        <v>44957</v>
+        <v>44981</v>
       </c>
       <c r="B42" s="4">
         <v>2.983</v>
@@ -1854,7 +1855,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="3">
-        <v>44925</v>
+        <v>44957</v>
       </c>
       <c r="B43" s="4">
         <v>2.983</v>
@@ -1868,10 +1869,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3">
-        <v>44895</v>
+        <v>44925</v>
       </c>
       <c r="B44" s="4">
-        <v>2.998</v>
+        <v>2.983</v>
       </c>
       <c r="C44" s="4">
         <v>2.587</v>
@@ -1882,7 +1883,7 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="3">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B45" s="4">
         <v>2.998</v>
@@ -1896,77 +1897,77 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="3">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B46" s="4">
-        <v>3.105</v>
+        <v>2.998</v>
       </c>
       <c r="C46" s="4">
-        <v>2.685</v>
+        <v>2.587</v>
       </c>
       <c r="D46" s="4">
-        <v>4.303</v>
+        <v>4.142</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="3">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B47" s="4">
-        <v>3.173</v>
+        <v>3.105</v>
       </c>
       <c r="C47" s="4">
-        <v>2.74</v>
+        <v>2.685</v>
       </c>
       <c r="D47" s="4">
-        <v>4.415</v>
+        <v>4.303</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="3">
-        <v>44771</v>
+        <v>44804</v>
       </c>
       <c r="B48" s="4">
-        <v>3.223</v>
+        <v>3.173</v>
       </c>
       <c r="C48" s="4">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="D48" s="4">
-        <v>4.49</v>
+        <v>4.415</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="3">
-        <v>44742</v>
+        <v>44771</v>
       </c>
       <c r="B49" s="4">
-        <v>3.337</v>
+        <v>3.223</v>
       </c>
       <c r="C49" s="4">
-        <v>2.855</v>
+        <v>2.79</v>
       </c>
       <c r="D49" s="4">
-        <v>4.665</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="3">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B50" s="4">
-        <v>3.44</v>
+        <v>3.337</v>
       </c>
       <c r="C50" s="4">
-        <v>3</v>
+        <v>2.855</v>
       </c>
       <c r="D50" s="4">
-        <v>4.81</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="3">
-        <v>44680</v>
+        <v>44712</v>
       </c>
       <c r="B51" s="4">
         <v>3.44</v>
@@ -1980,7 +1981,7 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="3">
-        <v>44651</v>
+        <v>44680</v>
       </c>
       <c r="B52" s="4">
         <v>3.44</v>
@@ -1994,7 +1995,7 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="3">
-        <v>44617</v>
+        <v>44651</v>
       </c>
       <c r="B53" s="4">
         <v>3.44</v>
@@ -2008,7 +2009,7 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="3">
-        <v>44589</v>
+        <v>44617</v>
       </c>
       <c r="B54" s="4">
         <v>3.44</v>
@@ -2022,7 +2023,7 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="3">
-        <v>44560</v>
+        <v>44589</v>
       </c>
       <c r="B55" s="4">
         <v>3.44</v>
@@ -2036,7 +2037,7 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="3">
-        <v>44530</v>
+        <v>44560</v>
       </c>
       <c r="B56" s="4">
         <v>3.44</v>
@@ -2050,7 +2051,7 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="3">
-        <v>44498</v>
+        <v>44530</v>
       </c>
       <c r="B57" s="4">
         <v>3.44</v>
@@ -2064,7 +2065,7 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="3">
-        <v>44469</v>
+        <v>44498</v>
       </c>
       <c r="B58" s="4">
         <v>3.44</v>
@@ -2078,7 +2079,7 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="3">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="B59" s="4">
         <v>3.44</v>
@@ -2092,7 +2093,7 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="3">
-        <v>44407</v>
+        <v>44439</v>
       </c>
       <c r="B60" s="4">
         <v>3.44</v>
@@ -2106,21 +2107,21 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="3">
-        <v>44377</v>
+        <v>44407</v>
       </c>
       <c r="B61" s="4">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="C61" s="4">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="D61" s="4">
-        <v>4.56</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="3">
-        <v>44347</v>
+        <v>44377</v>
       </c>
       <c r="B62" s="4">
         <v>3.26</v>
@@ -2134,13 +2135,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="3">
-        <v>44315</v>
+        <v>44347</v>
       </c>
       <c r="B63" s="4">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="C63" s="4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D63" s="4">
         <v>4.56</v>
@@ -2148,21 +2149,21 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="3">
-        <v>44286</v>
+        <v>44315</v>
       </c>
       <c r="B64" s="4">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="C64" s="4">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="D64" s="4">
-        <v>4.2</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="3">
-        <v>44253</v>
+        <v>44286</v>
       </c>
       <c r="B65" s="4">
         <v>2.94</v>
@@ -2176,7 +2177,7 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="3">
-        <v>44225</v>
+        <v>44253</v>
       </c>
       <c r="B66" s="4">
         <v>2.94</v>
@@ -2190,7 +2191,7 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="3">
-        <v>44196</v>
+        <v>44225</v>
       </c>
       <c r="B67" s="4">
         <v>2.94</v>
@@ -2204,7 +2205,7 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="3">
-        <v>44165</v>
+        <v>44196</v>
       </c>
       <c r="B68" s="4">
         <v>2.94</v>
@@ -2218,7 +2219,7 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="3">
-        <v>44134</v>
+        <v>44165</v>
       </c>
       <c r="B69" s="4">
         <v>2.94</v>
@@ -2227,18 +2228,18 @@
         <v>2.55</v>
       </c>
       <c r="D69" s="4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="3">
-        <v>44104</v>
+        <v>44134</v>
       </c>
       <c r="B70" s="4">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="C70" s="4">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="D70" s="4">
         <v>0</v>
@@ -2246,7 +2247,7 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="3">
-        <v>44074</v>
+        <v>44104</v>
       </c>
       <c r="B71" s="4">
         <v>3.03</v>
@@ -2260,13 +2261,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="3">
-        <v>44043</v>
+        <v>44074</v>
       </c>
       <c r="B72" s="4">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="C72" s="4">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="D72" s="4">
         <v>0</v>
@@ -2274,13 +2275,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="3">
-        <v>44012</v>
+        <v>44043</v>
       </c>
       <c r="B73" s="4">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="C73" s="4">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="D73" s="4">
         <v>0</v>
@@ -2288,7 +2289,7 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="3">
-        <v>43980</v>
+        <v>44012</v>
       </c>
       <c r="B74" s="4">
         <v>3.24</v>
@@ -2302,7 +2303,7 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="3">
-        <v>43951</v>
+        <v>43980</v>
       </c>
       <c r="B75" s="4">
         <v>3.24</v>
@@ -2316,7 +2317,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="3">
-        <v>43921</v>
+        <v>43951</v>
       </c>
       <c r="B76" s="4">
         <v>3.24</v>
@@ -2330,13 +2331,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="3">
-        <v>43888</v>
+        <v>43921</v>
       </c>
       <c r="B77" s="4">
-        <v>3.11</v>
+        <v>3.24</v>
       </c>
       <c r="C77" s="4">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="D77" s="4">
         <v>0</v>
@@ -2344,7 +2345,7 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="3">
-        <v>43860</v>
+        <v>43888</v>
       </c>
       <c r="B78" s="4">
         <v>3.11</v>
@@ -2358,10 +2359,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="3">
-        <v>43830</v>
+        <v>43860</v>
       </c>
       <c r="B79" s="4">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="C79" s="4">
         <v>2.66</v>
@@ -2372,13 +2373,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="3">
-        <v>43798</v>
+        <v>43830</v>
       </c>
       <c r="B80" s="4">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="C80" s="4">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="D80" s="4">
         <v>0</v>
@@ -2386,7 +2387,7 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="3">
-        <v>43769</v>
+        <v>43798</v>
       </c>
       <c r="B81" s="4">
         <v>2.85</v>
@@ -2400,13 +2401,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="3">
-        <v>43738</v>
+        <v>43769</v>
       </c>
       <c r="B82" s="4">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="C82" s="4">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="D82" s="4">
         <v>0</v>
@@ -2414,7 +2415,7 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="3">
-        <v>43707</v>
+        <v>43738</v>
       </c>
       <c r="B83" s="4">
         <v>2.75</v>
@@ -2428,13 +2429,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="3">
-        <v>43677</v>
+        <v>43707</v>
       </c>
       <c r="B84" s="4">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="C84" s="4">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="D84" s="4">
         <v>0</v>
@@ -2442,13 +2443,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="3">
-        <v>43644</v>
+        <v>43677</v>
       </c>
       <c r="B85" s="4">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="C85" s="4">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="D85" s="4">
         <v>0</v>
@@ -2456,7 +2457,7 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="3">
-        <v>43616</v>
+        <v>43644</v>
       </c>
       <c r="B86" s="4">
         <v>2.68</v>
@@ -2470,13 +2471,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="3">
-        <v>43585</v>
+        <v>43616</v>
       </c>
       <c r="B87" s="4">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="C87" s="4">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="D87" s="4">
         <v>0</v>
@@ -2484,13 +2485,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="3">
-        <v>43553</v>
+        <v>43585</v>
       </c>
       <c r="B88" s="4">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="C88" s="4">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="D88" s="4">
         <v>0</v>
@@ -2498,13 +2499,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="3">
-        <v>43523</v>
+        <v>43553</v>
       </c>
       <c r="B89" s="4">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="C89" s="4">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="D89" s="4">
         <v>0</v>
@@ -2512,10 +2513,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="3">
-        <v>43496</v>
+        <v>43523</v>
       </c>
       <c r="B90" s="4">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="C90" s="4">
         <v>2.64</v>
@@ -2526,10 +2527,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="3">
-        <v>43462</v>
+        <v>43496</v>
       </c>
       <c r="B91" s="4">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="C91" s="4">
         <v>2.64</v>
@@ -2540,13 +2541,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="3">
-        <v>43434</v>
+        <v>43462</v>
       </c>
       <c r="B92" s="4">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="C92" s="4">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="D92" s="4">
         <v>0</v>
@@ -2554,7 +2555,7 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="3">
-        <v>43404</v>
+        <v>43434</v>
       </c>
       <c r="B93" s="4">
         <v>3.25</v>
@@ -2568,13 +2569,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="3">
-        <v>43371</v>
+        <v>43404</v>
       </c>
       <c r="B94" s="4">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="C94" s="4">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="D94" s="4">
         <v>0</v>
@@ -2582,10 +2583,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="3">
-        <v>43343</v>
+        <v>43371</v>
       </c>
       <c r="B95" s="4">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="C95" s="4">
         <v>2.89</v>
@@ -2596,7 +2597,7 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="3">
-        <v>43312</v>
+        <v>43343</v>
       </c>
       <c r="B96" s="4">
         <v>3.55</v>
@@ -2610,13 +2611,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="3">
-        <v>43280</v>
+        <v>43312</v>
       </c>
       <c r="B97" s="4">
-        <v>3.69</v>
+        <v>3.55</v>
       </c>
       <c r="C97" s="4">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="D97" s="4">
         <v>0</v>
@@ -2624,7 +2625,7 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="3">
-        <v>43251</v>
+        <v>43280</v>
       </c>
       <c r="B98" s="4">
         <v>3.69</v>
@@ -2638,7 +2639,7 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="3">
-        <v>43220</v>
+        <v>43251</v>
       </c>
       <c r="B99" s="4">
         <v>3.69</v>
@@ -2652,7 +2653,7 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="3">
-        <v>43189</v>
+        <v>43220</v>
       </c>
       <c r="B100" s="4">
         <v>3.69</v>
@@ -2666,7 +2667,7 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="3">
-        <v>43158</v>
+        <v>43189</v>
       </c>
       <c r="B101" s="4">
         <v>3.69</v>
@@ -2680,7 +2681,7 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="3">
-        <v>43131</v>
+        <v>43158</v>
       </c>
       <c r="B102" s="4">
         <v>3.69</v>
@@ -2694,7 +2695,7 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="3">
-        <v>43098</v>
+        <v>43131</v>
       </c>
       <c r="B103" s="4">
         <v>3.69</v>
@@ -2708,7 +2709,7 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="3">
-        <v>43069</v>
+        <v>43098</v>
       </c>
       <c r="B104" s="4">
         <v>3.69</v>
@@ -2722,7 +2723,7 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="3">
-        <v>43039</v>
+        <v>43069</v>
       </c>
       <c r="B105" s="4">
         <v>3.69</v>
@@ -2736,13 +2737,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3">
-        <v>43007</v>
+        <v>43039</v>
       </c>
       <c r="B106" s="4">
         <v>3.69</v>
       </c>
       <c r="C106" s="4">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="D106" s="4">
         <v>0</v>
@@ -2750,10 +2751,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="3">
-        <v>42978</v>
+        <v>43007</v>
       </c>
       <c r="B107" s="4">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="C107" s="4">
         <v>2.82</v>
@@ -2764,13 +2765,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="3">
-        <v>42947</v>
+        <v>42978</v>
       </c>
       <c r="B108" s="4">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="C108" s="4">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="D108" s="4">
         <v>0</v>
@@ -2778,13 +2779,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3">
-        <v>42916</v>
+        <v>42947</v>
       </c>
       <c r="B109" s="4">
-        <v>3.57</v>
+        <v>3.65</v>
       </c>
       <c r="C109" s="4">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="D109" s="4">
         <v>0</v>
@@ -2792,7 +2793,7 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="3">
-        <v>42881</v>
+        <v>42916</v>
       </c>
       <c r="B110" s="4">
         <v>3.57</v>
@@ -2806,7 +2807,7 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="3">
-        <v>42853</v>
+        <v>42881</v>
       </c>
       <c r="B111" s="4">
         <v>3.57</v>
@@ -2820,13 +2821,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="3">
-        <v>42825</v>
+        <v>42853</v>
       </c>
       <c r="B112" s="4">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="C112" s="4">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="D112" s="4">
         <v>0</v>
@@ -2834,13 +2835,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="3">
-        <v>42790</v>
+        <v>42825</v>
       </c>
       <c r="B113" s="4">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="C113" s="4">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="D113" s="4">
         <v>0</v>
@@ -2848,13 +2849,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="3">
-        <v>42760</v>
+        <v>42790</v>
       </c>
       <c r="B114" s="4">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="C114" s="4">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="D114" s="4">
         <v>0</v>
@@ -2862,13 +2863,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="3">
-        <v>42733</v>
+        <v>42760</v>
       </c>
       <c r="B115" s="4">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="C115" s="4">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="D115" s="4">
         <v>0</v>
@@ -2876,13 +2877,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="3">
-        <v>42704</v>
+        <v>42733</v>
       </c>
       <c r="B116" s="4">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="C116" s="4">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="D116" s="4">
         <v>0</v>
@@ -2890,10 +2891,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="3">
-        <v>42674</v>
+        <v>42704</v>
       </c>
       <c r="B117" s="4">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="C117" s="4">
         <v>1.89</v>
@@ -2904,13 +2905,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="3">
-        <v>42643</v>
+        <v>42674</v>
       </c>
       <c r="B118" s="4">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="C118" s="4">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="D118" s="4">
         <v>0</v>
@@ -2918,13 +2919,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="3">
-        <v>42613</v>
+        <v>42643</v>
       </c>
       <c r="B119" s="4">
         <v>2.32</v>
       </c>
       <c r="C119" s="4">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="D119" s="4">
         <v>0</v>
@@ -2932,13 +2933,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="3">
-        <v>42580</v>
+        <v>42613</v>
       </c>
       <c r="B120" s="4">
         <v>2.32</v>
       </c>
       <c r="C120" s="4">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="D120" s="4">
         <v>0</v>
@@ -2946,13 +2947,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="3">
-        <v>42521</v>
+        <v>42580</v>
       </c>
       <c r="B121" s="4">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="C121" s="4">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="D121" s="4">
         <v>0</v>
@@ -2960,7 +2961,7 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="3">
-        <v>42489</v>
+        <v>42521</v>
       </c>
       <c r="B122" s="4">
         <v>2.02</v>
@@ -2974,13 +2975,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="3">
-        <v>42426</v>
+        <v>42489</v>
       </c>
       <c r="B123" s="4">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="C123" s="4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="D123" s="4">
         <v>0</v>
@@ -2988,13 +2989,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="3">
-        <v>42398</v>
+        <v>42426</v>
       </c>
       <c r="B124" s="4">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="C124" s="4">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="D124" s="4">
         <v>0</v>
@@ -3002,10 +3003,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="3">
-        <v>42368</v>
+        <v>42398</v>
       </c>
       <c r="B125" s="4">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="C125" s="4">
         <v>1.58</v>
@@ -3016,13 +3017,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="3">
-        <v>42338</v>
+        <v>42368</v>
       </c>
       <c r="B126" s="4">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="C126" s="4">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="D126" s="4">
         <v>0</v>
@@ -3030,13 +3031,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="3">
-        <v>42307</v>
+        <v>42338</v>
       </c>
       <c r="B127" s="4">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="C127" s="4">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="D127" s="4">
         <v>0</v>
@@ -3044,13 +3045,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="3">
-        <v>42291</v>
+        <v>42307</v>
       </c>
       <c r="B128" s="4">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="C128" s="4">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="D128" s="4">
         <v>0</v>
@@ -3058,10 +3059,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="3">
-        <v>42277</v>
+        <v>42291</v>
       </c>
       <c r="B129" s="4">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="C129" s="4">
         <v>1.77</v>
@@ -3072,13 +3073,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="3">
-        <v>42262</v>
+        <v>42277</v>
       </c>
       <c r="B130" s="4">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="C130" s="4">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="D130" s="4">
         <v>0</v>
@@ -3086,10 +3087,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="3">
-        <v>42247</v>
+        <v>42262</v>
       </c>
       <c r="B131" s="4">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="C131" s="4">
         <v>1.8</v>
@@ -3100,13 +3101,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="3">
-        <v>42230</v>
+        <v>42247</v>
       </c>
       <c r="B132" s="4">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="C132" s="4">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="D132" s="4">
         <v>0</v>
@@ -3114,13 +3115,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="3">
-        <v>42216</v>
+        <v>42230</v>
       </c>
       <c r="B133" s="4">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="C133" s="4">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="D133" s="4">
         <v>0</v>
@@ -3128,13 +3129,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="3">
-        <v>42200</v>
+        <v>42216</v>
       </c>
       <c r="B134" s="4">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="C134" s="4">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="D134" s="4">
         <v>0</v>
@@ -3142,10 +3143,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="3">
-        <v>42185</v>
+        <v>42200</v>
       </c>
       <c r="B135" s="4">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="C135" s="4">
         <v>1.96</v>
@@ -3156,13 +3157,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="3">
-        <v>42170</v>
+        <v>42185</v>
       </c>
       <c r="B136" s="4">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="C136" s="4">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="D136" s="4">
         <v>0</v>
@@ -3170,7 +3171,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="3">
-        <v>42153</v>
+        <v>42170</v>
       </c>
       <c r="B137" s="4">
         <v>2.58</v>
@@ -3184,13 +3185,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="3">
-        <v>42139</v>
+        <v>42153</v>
       </c>
       <c r="B138" s="4">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="C138" s="4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="D138" s="4">
         <v>0</v>
@@ -3198,7 +3199,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="3">
-        <v>42124</v>
+        <v>42139</v>
       </c>
       <c r="B139" s="4">
         <v>2.61</v>
@@ -3212,7 +3213,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="3">
-        <v>42109</v>
+        <v>42124</v>
       </c>
       <c r="B140" s="4">
         <v>2.61</v>
@@ -3226,7 +3227,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="3">
-        <v>42094</v>
+        <v>42109</v>
       </c>
       <c r="B141" s="4">
         <v>2.61</v>
@@ -3240,10 +3241,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="3">
-        <v>42076</v>
+        <v>42094</v>
       </c>
       <c r="B142" s="4">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="C142" s="4">
         <v>1.98</v>
@@ -3254,10 +3255,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="3">
-        <v>42061</v>
+        <v>42076</v>
       </c>
       <c r="B143" s="4">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="C143" s="4">
         <v>1.98</v>
@@ -3268,13 +3269,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="3">
-        <v>42048</v>
+        <v>42061</v>
       </c>
       <c r="B144" s="4">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="C144" s="4">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="D144" s="4">
         <v>0</v>
@@ -3282,13 +3283,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="3">
-        <v>42034</v>
+        <v>42048</v>
       </c>
       <c r="B145" s="4">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="C145" s="4">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="D145" s="4">
         <v>0</v>
@@ -3296,13 +3297,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="3">
-        <v>42019</v>
+        <v>42034</v>
       </c>
       <c r="B146" s="4">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C146" s="4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="D146" s="4">
         <v>0</v>
@@ -3310,13 +3311,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="3">
-        <v>42004</v>
+        <v>42019</v>
       </c>
       <c r="B147" s="4">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C147" s="4">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="D147" s="4">
         <v>0</v>
@@ -3324,13 +3325,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="3">
-        <v>41988</v>
+        <v>42004</v>
       </c>
       <c r="B148" s="4">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="C148" s="4">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="D148" s="4">
         <v>0</v>
@@ -3338,10 +3339,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="3">
-        <v>41971</v>
+        <v>41988</v>
       </c>
       <c r="B149" s="4">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="C149" s="4">
         <v>2.2</v>
@@ -3352,13 +3353,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="3">
-        <v>41957</v>
+        <v>41971</v>
       </c>
       <c r="B150" s="4">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="C150" s="4">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="D150" s="4">
         <v>0</v>
@@ -3366,13 +3367,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="3">
-        <v>41943</v>
+        <v>41957</v>
       </c>
       <c r="B151" s="4">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="C151" s="4">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="D151" s="4">
         <v>0</v>
@@ -3380,13 +3381,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="3">
-        <v>41927</v>
+        <v>41943</v>
       </c>
       <c r="B152" s="4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="C152" s="4">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="D152" s="4">
         <v>0</v>
@@ -3394,7 +3395,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="3">
-        <v>41912</v>
+        <v>41927</v>
       </c>
       <c r="B153" s="4">
         <v>3.05</v>
@@ -3408,7 +3409,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="3">
-        <v>41897</v>
+        <v>41912</v>
       </c>
       <c r="B154" s="4">
         <v>3.05</v>
@@ -3422,13 +3423,13 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="3">
-        <v>41883</v>
+        <v>41897</v>
       </c>
       <c r="B155" s="4">
         <v>3.05</v>
       </c>
       <c r="C155" s="4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="D155" s="4">
         <v>0</v>
@@ -3436,7 +3437,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="3">
-        <v>41866</v>
+        <v>41883</v>
       </c>
       <c r="B156" s="4">
         <v>3.05</v>
@@ -3450,7 +3451,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="3">
-        <v>41851</v>
+        <v>41866</v>
       </c>
       <c r="B157" s="4">
         <v>3.05</v>
@@ -3464,13 +3465,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="3">
-        <v>41835</v>
+        <v>41851</v>
       </c>
       <c r="B158" s="4">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="C158" s="4">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="D158" s="4">
         <v>0</v>
@@ -3478,13 +3479,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="3">
-        <v>41820</v>
+        <v>41835</v>
       </c>
       <c r="B159" s="4">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="C159" s="4">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="D159" s="4">
         <v>0</v>
@@ -3492,13 +3493,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="3">
-        <v>41803</v>
+        <v>41820</v>
       </c>
       <c r="B160" s="4">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="C160" s="4">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="D160" s="4">
         <v>0</v>
@@ -3506,13 +3507,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="3">
-        <v>41789</v>
+        <v>41803</v>
       </c>
       <c r="B161" s="4">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="C161" s="4">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="D161" s="4">
         <v>0</v>
@@ -3520,13 +3521,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="3">
-        <v>41774</v>
+        <v>41789</v>
       </c>
       <c r="B162" s="4">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="C162" s="4">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="D162" s="4">
         <v>0</v>
@@ -3534,10 +3535,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="3">
-        <v>41759</v>
+        <v>41774</v>
       </c>
       <c r="B163" s="4">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="C163" s="4">
         <v>2.14</v>
@@ -3548,13 +3549,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="3">
-        <v>41729</v>
+        <v>41759</v>
       </c>
       <c r="B164" s="4">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="C164" s="4">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="D164" s="4">
         <v>0</v>
@@ -3562,13 +3563,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="3">
-        <v>41697</v>
+        <v>41729</v>
       </c>
       <c r="B165" s="4">
-        <v>3.03</v>
+        <v>2.81</v>
       </c>
       <c r="C165" s="4">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="D165" s="4">
         <v>0</v>
@@ -3576,13 +3577,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="3">
-        <v>41687</v>
+        <v>41697</v>
       </c>
       <c r="B166" s="4">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="C166" s="4">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="D166" s="4">
         <v>0</v>
@@ -3590,13 +3591,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="3">
-        <v>41668</v>
+        <v>41687</v>
       </c>
       <c r="B167" s="4">
-        <v>3.51</v>
+        <v>3.41</v>
       </c>
       <c r="C167" s="4">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="D167" s="4">
         <v>0</v>
@@ -3604,13 +3605,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="3">
-        <v>41655</v>
+        <v>41668</v>
       </c>
       <c r="B168" s="4">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="C168" s="4">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="D168" s="4">
         <v>0</v>
@@ -3618,13 +3619,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="3">
-        <v>41639</v>
+        <v>41655</v>
       </c>
       <c r="B169" s="4">
-        <v>3.68</v>
+        <v>3.56</v>
       </c>
       <c r="C169" s="4">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="D169" s="4">
         <v>0</v>
@@ -3632,13 +3633,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="3">
-        <v>41624</v>
+        <v>41639</v>
       </c>
       <c r="B170" s="4">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="C170" s="4">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="D170" s="4">
         <v>0</v>
@@ -3646,10 +3647,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="3">
-        <v>41610</v>
+        <v>41624</v>
       </c>
       <c r="B171" s="4">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="C171" s="4">
         <v>2.62</v>
@@ -3660,13 +3661,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="3">
-        <v>41592</v>
+        <v>41610</v>
       </c>
       <c r="B172" s="4">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="C172" s="4">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="D172" s="4">
         <v>0</v>
@@ -3674,13 +3675,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="3">
-        <v>41578</v>
+        <v>41592</v>
       </c>
       <c r="B173" s="4">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C173" s="4">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="D173" s="4">
         <v>0</v>
@@ -3688,13 +3689,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="3">
-        <v>41562</v>
+        <v>41578</v>
       </c>
       <c r="B174" s="4">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="C174" s="4">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="D174" s="4">
         <v>0</v>
@@ -3702,7 +3703,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="3">
-        <v>41548</v>
+        <v>41562</v>
       </c>
       <c r="B175" s="4">
         <v>4.72</v>
@@ -3716,13 +3717,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="3">
-        <v>41456</v>
+        <v>41548</v>
       </c>
       <c r="B176" s="4">
-        <v>5.52</v>
+        <v>4.72</v>
       </c>
       <c r="C176" s="4">
-        <v>3.58</v>
+        <v>3.07</v>
       </c>
       <c r="D176" s="4">
         <v>0</v>
@@ -3730,13 +3731,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="3">
-        <v>41428</v>
+        <v>41456</v>
       </c>
       <c r="B177" s="4">
-        <v>5.26</v>
+        <v>5.52</v>
       </c>
       <c r="C177" s="4">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="D177" s="4">
         <v>0</v>
@@ -3744,13 +3745,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="3">
-        <v>41409</v>
+        <v>41428</v>
       </c>
       <c r="B178" s="4">
         <v>5.26</v>
       </c>
       <c r="C178" s="4">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="D178" s="4">
         <v>0</v>
@@ -3758,13 +3759,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="3">
-        <v>41394</v>
+        <v>41409</v>
       </c>
       <c r="B179" s="4">
-        <v>5.34</v>
+        <v>5.26</v>
       </c>
       <c r="C179" s="4">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D179" s="4">
         <v>0</v>
@@ -3772,13 +3773,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="3">
-        <v>41379</v>
+        <v>41394</v>
       </c>
       <c r="B180" s="4">
         <v>5.34</v>
       </c>
       <c r="C180" s="4">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="D180" s="4">
         <v>0</v>
@@ -3786,13 +3787,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="3">
-        <v>41362</v>
+        <v>41379</v>
       </c>
       <c r="B181" s="4">
         <v>5.34</v>
       </c>
       <c r="C181" s="4">
-        <v>2.96</v>
+        <v>3.14</v>
       </c>
       <c r="D181" s="4">
         <v>0</v>
@@ -3800,13 +3801,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="3">
-        <v>41348</v>
+        <v>41362</v>
       </c>
       <c r="B182" s="4">
         <v>5.34</v>
       </c>
       <c r="C182" s="4">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="D182" s="4">
         <v>0</v>
@@ -3814,13 +3815,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="3">
-        <v>41327</v>
+        <v>41348</v>
       </c>
       <c r="B183" s="4">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="C183" s="4">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="D183" s="4">
         <v>0</v>
@@ -3828,13 +3829,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="3">
-        <v>41304</v>
+        <v>41327</v>
       </c>
       <c r="B184" s="4">
         <v>5</v>
       </c>
       <c r="C184" s="4">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="D184" s="4">
         <v>0</v>
@@ -3842,13 +3843,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="3">
-        <v>41289</v>
+        <v>41304</v>
       </c>
       <c r="B185" s="4">
         <v>5</v>
       </c>
       <c r="C185" s="4">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="D185" s="4">
         <v>0</v>
@@ -3856,13 +3857,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="3">
-        <v>41256</v>
+        <v>41289</v>
       </c>
       <c r="B186" s="4">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="C186" s="4">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="D186" s="4">
         <v>0</v>
@@ -3870,13 +3871,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="3">
-        <v>41243</v>
+        <v>41256</v>
       </c>
       <c r="B187" s="4">
         <v>4.98</v>
       </c>
       <c r="C187" s="4">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="D187" s="4">
         <v>0</v>
@@ -3884,10 +3885,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="3">
-        <v>41228</v>
+        <v>41243</v>
       </c>
       <c r="B188" s="4">
-        <v>5.4</v>
+        <v>4.98</v>
       </c>
       <c r="C188" s="4">
         <v>2.52</v>
@@ -3898,13 +3899,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="3">
-        <v>41208</v>
+        <v>41228</v>
       </c>
       <c r="B189" s="4">
-        <v>5.52</v>
+        <v>5.4</v>
       </c>
       <c r="C189" s="4">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="D189" s="4">
         <v>0</v>
@@ -3912,10 +3913,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="3">
-        <v>41197</v>
+        <v>41208</v>
       </c>
       <c r="B190" s="4">
-        <v>4.99</v>
+        <v>5.52</v>
       </c>
       <c r="C190" s="4">
         <v>2.59</v>
@@ -3926,13 +3927,13 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="3">
-        <v>41184</v>
+        <v>41197</v>
       </c>
       <c r="B191" s="4">
-        <v>4.26</v>
+        <v>4.99</v>
       </c>
       <c r="C191" s="4">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="D191" s="4">
         <v>0</v>
@@ -3940,13 +3941,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="3">
-        <v>41166</v>
+        <v>41184</v>
       </c>
       <c r="B192" s="4">
-        <v>3.91</v>
+        <v>4.26</v>
       </c>
       <c r="C192" s="4">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="D192" s="4">
         <v>0</v>
@@ -3954,13 +3955,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="3">
-        <v>41152</v>
+        <v>41166</v>
       </c>
       <c r="B193" s="4">
-        <v>3.87</v>
+        <v>3.91</v>
       </c>
       <c r="C193" s="4">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="D193" s="4">
         <v>0</v>
@@ -3968,7 +3969,7 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="3">
-        <v>41135</v>
+        <v>41152</v>
       </c>
       <c r="B194" s="4">
         <v>3.87</v>
@@ -3982,7 +3983,7 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="3">
-        <v>41121</v>
+        <v>41135</v>
       </c>
       <c r="B195" s="4">
         <v>3.87</v>
@@ -3996,13 +3997,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="3">
-        <v>41103</v>
+        <v>41121</v>
       </c>
       <c r="B196" s="4">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="C196" s="4">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="D196" s="4">
         <v>0</v>
@@ -4010,13 +4011,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="3">
-        <v>41089</v>
+        <v>41103</v>
       </c>
       <c r="B197" s="4">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="C197" s="4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="D197" s="4">
         <v>0</v>
@@ -4024,13 +4025,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="3">
-        <v>41075</v>
+        <v>41089</v>
       </c>
       <c r="B198" s="4">
-        <v>4.04</v>
+        <v>3.84</v>
       </c>
       <c r="C198" s="4">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="D198" s="4">
         <v>0</v>
@@ -4038,7 +4039,7 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="3">
-        <v>41060</v>
+        <v>41075</v>
       </c>
       <c r="B199" s="4">
         <v>4.04</v>
@@ -4052,13 +4053,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="3">
-        <v>41044</v>
+        <v>41060</v>
       </c>
       <c r="B200" s="4">
-        <v>4.41</v>
+        <v>4.04</v>
       </c>
       <c r="C200" s="4">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="D200" s="4">
         <v>0</v>
@@ -4066,13 +4067,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="3">
-        <v>41029</v>
+        <v>41044</v>
       </c>
       <c r="B201" s="4">
-        <v>4.66</v>
+        <v>4.41</v>
       </c>
       <c r="C201" s="4">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="D201" s="4">
         <v>0</v>
@@ -4080,13 +4081,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="3">
-        <v>41014</v>
+        <v>41029</v>
       </c>
       <c r="B202" s="4">
-        <v>4.79</v>
+        <v>4.66</v>
       </c>
       <c r="C202" s="4">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="D202" s="4">
         <v>0</v>
@@ -4094,13 +4095,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="3">
-        <v>40995</v>
+        <v>41014</v>
       </c>
       <c r="B203" s="4">
-        <v>4.95</v>
+        <v>4.79</v>
       </c>
       <c r="C203" s="4">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="D203" s="4">
         <v>0</v>
@@ -4108,13 +4109,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="3">
-        <v>40982</v>
+        <v>40995</v>
       </c>
       <c r="B204" s="4">
-        <v>5.02</v>
+        <v>4.95</v>
       </c>
       <c r="C204" s="4">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="D204" s="4">
         <v>0</v>
@@ -4122,13 +4123,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="3">
-        <v>40968</v>
+        <v>40982</v>
       </c>
       <c r="B205" s="4">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
       <c r="C205" s="4">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D205" s="4">
         <v>0</v>
@@ -4136,13 +4137,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="3">
-        <v>40954</v>
+        <v>40968</v>
       </c>
       <c r="B206" s="4">
-        <v>5.34</v>
+        <v>5.06</v>
       </c>
       <c r="C206" s="4">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="D206" s="4">
         <v>0</v>
@@ -4150,13 +4151,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="3">
-        <v>40924</v>
+        <v>40954</v>
       </c>
       <c r="B207" s="4">
-        <v>5.49</v>
+        <v>5.34</v>
       </c>
       <c r="C207" s="4">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="D207" s="4">
         <v>0</v>
@@ -4164,13 +4165,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="3">
-        <v>40907</v>
+        <v>40924</v>
       </c>
       <c r="B208" s="4">
-        <v>5.71</v>
+        <v>5.49</v>
       </c>
       <c r="C208" s="4">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="D208" s="4">
         <v>0</v>
@@ -4178,13 +4179,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="3">
-        <v>40892</v>
+        <v>40907</v>
       </c>
       <c r="B209" s="4">
-        <v>6.09</v>
+        <v>5.71</v>
       </c>
       <c r="C209" s="4">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="D209" s="4">
         <v>0</v>
@@ -4192,10 +4193,10 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="3">
-        <v>40877</v>
+        <v>40892</v>
       </c>
       <c r="B210" s="4">
-        <v>6.12</v>
+        <v>6.09</v>
       </c>
       <c r="C210" s="4">
         <v>3.48</v>
@@ -4206,13 +4207,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="3">
-        <v>40862</v>
+        <v>40877</v>
       </c>
       <c r="B211" s="4">
-        <v>6.38</v>
+        <v>6.12</v>
       </c>
       <c r="C211" s="4">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="D211" s="4">
         <v>0</v>
@@ -4220,13 +4221,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="3">
-        <v>40847</v>
+        <v>40862</v>
       </c>
       <c r="B212" s="4">
-        <v>6.49</v>
+        <v>6.38</v>
       </c>
       <c r="C212" s="4">
-        <v>3.77</v>
+        <v>3.64</v>
       </c>
       <c r="D212" s="4">
         <v>0</v>
@@ -4234,13 +4235,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="3">
-        <v>40830</v>
+        <v>40847</v>
       </c>
       <c r="B213" s="4">
-        <v>6.66</v>
+        <v>6.49</v>
       </c>
       <c r="C213" s="4">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="D213" s="4">
         <v>0</v>
@@ -4248,13 +4249,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="3">
-        <v>40816</v>
+        <v>40830</v>
       </c>
       <c r="B214" s="4">
-        <v>6.72</v>
+        <v>6.66</v>
       </c>
       <c r="C214" s="4">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="D214" s="4">
         <v>0</v>
@@ -4262,13 +4263,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="3">
-        <v>40801</v>
+        <v>40816</v>
       </c>
       <c r="B215" s="4">
-        <v>6.9</v>
+        <v>6.72</v>
       </c>
       <c r="C215" s="4">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="D215" s="4">
         <v>0</v>
@@ -4276,13 +4277,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="3">
-        <v>40786</v>
+        <v>40801</v>
       </c>
       <c r="B216" s="4">
-        <v>8.06</v>
+        <v>6.9</v>
       </c>
       <c r="C216" s="4">
-        <v>4.48</v>
+        <v>3.8</v>
       </c>
       <c r="D216" s="4">
         <v>0</v>
@@ -4290,13 +4291,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="3">
-        <v>40770</v>
+        <v>40786</v>
       </c>
       <c r="B217" s="4">
         <v>8.06</v>
       </c>
       <c r="C217" s="4">
-        <v>4.35</v>
+        <v>4.48</v>
       </c>
       <c r="D217" s="4">
         <v>0</v>
@@ -4304,13 +4305,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="3">
-        <v>40755</v>
+        <v>40770</v>
       </c>
       <c r="B218" s="4">
-        <v>8.16</v>
+        <v>8.06</v>
       </c>
       <c r="C218" s="4">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="D218" s="4">
         <v>0</v>
@@ -4318,13 +4319,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="3">
-        <v>40694</v>
+        <v>40755</v>
       </c>
       <c r="B219" s="4">
-        <v>9.39</v>
+        <v>8.16</v>
       </c>
       <c r="C219" s="4">
-        <v>4.85</v>
+        <v>4.37</v>
       </c>
       <c r="D219" s="4">
         <v>0</v>
@@ -4332,13 +4333,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="3">
-        <v>40679</v>
+        <v>40694</v>
       </c>
       <c r="B220" s="4">
-        <v>10.28</v>
+        <v>9.39</v>
       </c>
       <c r="C220" s="4">
-        <v>5.76</v>
+        <v>4.85</v>
       </c>
       <c r="D220" s="4">
         <v>0</v>
@@ -4346,13 +4347,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="3">
-        <v>40662</v>
+        <v>40679</v>
       </c>
       <c r="B221" s="4">
-        <v>10.4</v>
+        <v>10.28</v>
       </c>
       <c r="C221" s="4">
-        <v>5.98</v>
+        <v>5.76</v>
       </c>
       <c r="D221" s="4">
         <v>0</v>
@@ -4360,13 +4361,13 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="3">
-        <v>40648</v>
+        <v>40662</v>
       </c>
       <c r="B222" s="4">
-        <v>10.64</v>
+        <v>10.4</v>
       </c>
       <c r="C222" s="4">
-        <v>6.1</v>
+        <v>5.98</v>
       </c>
       <c r="D222" s="4">
         <v>0</v>
@@ -4374,13 +4375,13 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="3">
-        <v>40627</v>
+        <v>40648</v>
       </c>
       <c r="B223" s="4">
-        <v>10.42</v>
+        <v>10.64</v>
       </c>
       <c r="C223" s="4">
-        <v>5.92</v>
+        <v>6.1</v>
       </c>
       <c r="D223" s="4">
         <v>0</v>
@@ -4388,13 +4389,13 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="3">
-        <v>40617</v>
+        <v>40627</v>
       </c>
       <c r="B224" s="4">
-        <v>10.12</v>
+        <v>10.42</v>
       </c>
       <c r="C224" s="4">
-        <v>5.66</v>
+        <v>5.92</v>
       </c>
       <c r="D224" s="4">
         <v>0</v>
@@ -4402,13 +4403,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="3">
-        <v>40599</v>
+        <v>40617</v>
       </c>
       <c r="B225" s="4">
-        <v>9.34</v>
+        <v>10.12</v>
       </c>
       <c r="C225" s="4">
-        <v>5.36</v>
+        <v>5.66</v>
       </c>
       <c r="D225" s="4">
         <v>0</v>
@@ -4416,13 +4417,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="3">
-        <v>40590</v>
+        <v>40599</v>
       </c>
       <c r="B226" s="4">
-        <v>9.5</v>
+        <v>9.34</v>
       </c>
       <c r="C226" s="4">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="D226" s="4">
         <v>0</v>
@@ -4430,7 +4431,7 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="3">
-        <v>40570</v>
+        <v>40590</v>
       </c>
       <c r="B227" s="4">
         <v>9.5</v>
@@ -4444,7 +4445,7 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="3">
-        <v>40557</v>
+        <v>40570</v>
       </c>
       <c r="B228" s="4">
         <v>9.5</v>
@@ -4458,13 +4459,13 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="3">
-        <v>40536</v>
+        <v>40557</v>
       </c>
       <c r="B229" s="4">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="C229" s="4">
-        <v>5.22</v>
+        <v>5.38</v>
       </c>
       <c r="D229" s="4">
         <v>0</v>
@@ -4472,10 +4473,10 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="3">
-        <v>40526</v>
+        <v>40536</v>
       </c>
       <c r="B230" s="4">
-        <v>9.18</v>
+        <v>9.4</v>
       </c>
       <c r="C230" s="4">
         <v>5.22</v>
@@ -4486,13 +4487,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="3">
-        <v>40512</v>
+        <v>40526</v>
       </c>
       <c r="B231" s="4">
-        <v>9.1</v>
+        <v>9.18</v>
       </c>
       <c r="C231" s="4">
-        <v>4.98</v>
+        <v>5.22</v>
       </c>
       <c r="D231" s="4">
         <v>0</v>
@@ -4500,13 +4501,13 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="3">
-        <v>40497</v>
+        <v>40512</v>
       </c>
       <c r="B232" s="4">
-        <v>9.2</v>
+        <v>9.1</v>
       </c>
       <c r="C232" s="4">
-        <v>4.93</v>
+        <v>4.98</v>
       </c>
       <c r="D232" s="4">
         <v>0</v>
@@ -4514,13 +4515,13 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="3">
-        <v>40480</v>
+        <v>40497</v>
       </c>
       <c r="B233" s="4">
-        <v>9.92</v>
+        <v>9.2</v>
       </c>
       <c r="C233" s="4">
-        <v>5.17</v>
+        <v>4.93</v>
       </c>
       <c r="D233" s="4">
         <v>0</v>
@@ -4528,13 +4529,13 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="3">
-        <v>40466</v>
+        <v>40480</v>
       </c>
       <c r="B234" s="4">
-        <v>10.08</v>
+        <v>9.92</v>
       </c>
       <c r="C234" s="4">
-        <v>5.23</v>
+        <v>5.17</v>
       </c>
       <c r="D234" s="4">
         <v>0</v>
@@ -4542,13 +4543,13 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="3">
-        <v>40451</v>
+        <v>40466</v>
       </c>
       <c r="B235" s="4">
-        <v>10.68</v>
+        <v>10.08</v>
       </c>
       <c r="C235" s="4">
-        <v>5.27</v>
+        <v>5.23</v>
       </c>
       <c r="D235" s="4">
         <v>0</v>
@@ -4556,13 +4557,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="3">
-        <v>40436</v>
+        <v>40451</v>
       </c>
       <c r="B236" s="4">
-        <v>11.78</v>
+        <v>10.68</v>
       </c>
       <c r="C236" s="4">
-        <v>5.57</v>
+        <v>5.27</v>
       </c>
       <c r="D236" s="4">
         <v>0</v>
@@ -4570,13 +4571,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="3">
-        <v>40421</v>
+        <v>40436</v>
       </c>
       <c r="B237" s="4">
-        <v>12.72</v>
+        <v>11.78</v>
       </c>
       <c r="C237" s="4">
-        <v>5.92</v>
+        <v>5.57</v>
       </c>
       <c r="D237" s="4">
         <v>0</v>
@@ -4584,13 +4585,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="3">
-        <v>40403</v>
+        <v>40421</v>
       </c>
       <c r="B238" s="4">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="C238" s="4">
-        <v>6.36</v>
+        <v>5.92</v>
       </c>
       <c r="D238" s="4">
         <v>0</v>
@@ -4598,13 +4599,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="3">
-        <v>40389</v>
+        <v>40403</v>
       </c>
       <c r="B239" s="4">
-        <v>13.82</v>
+        <v>13.56</v>
       </c>
       <c r="C239" s="4">
-        <v>6.44</v>
+        <v>6.36</v>
       </c>
       <c r="D239" s="4">
         <v>0</v>
@@ -4612,13 +4613,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="3">
-        <v>40368</v>
+        <v>40389</v>
       </c>
       <c r="B240" s="4">
         <v>13.82</v>
       </c>
       <c r="C240" s="4">
-        <v>6.58</v>
+        <v>6.44</v>
       </c>
       <c r="D240" s="4">
         <v>0</v>
@@ -4626,13 +4627,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="3">
-        <v>40354</v>
+        <v>40368</v>
       </c>
       <c r="B241" s="4">
         <v>13.82</v>
       </c>
       <c r="C241" s="4">
-        <v>6.67</v>
+        <v>6.58</v>
       </c>
       <c r="D241" s="4">
         <v>0</v>
@@ -4640,13 +4641,13 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="3">
-        <v>40339</v>
+        <v>40354</v>
       </c>
       <c r="B242" s="4">
-        <v>14.36</v>
+        <v>13.82</v>
       </c>
       <c r="C242" s="4">
-        <v>7.07</v>
+        <v>6.67</v>
       </c>
       <c r="D242" s="4">
         <v>0</v>
@@ -4654,13 +4655,13 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="3">
-        <v>40323</v>
+        <v>40339</v>
       </c>
       <c r="B243" s="4">
-        <v>15.16</v>
+        <v>14.36</v>
       </c>
       <c r="C243" s="4">
-        <v>7.19</v>
+        <v>7.07</v>
       </c>
       <c r="D243" s="4">
         <v>0</v>
@@ -4668,13 +4669,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="3">
-        <v>40308</v>
+        <v>40323</v>
       </c>
       <c r="B244" s="4">
         <v>15.16</v>
       </c>
       <c r="C244" s="4">
-        <v>7.29</v>
+        <v>7.19</v>
       </c>
       <c r="D244" s="4">
         <v>0</v>
@@ -4682,13 +4683,13 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="3">
-        <v>40291</v>
+        <v>40308</v>
       </c>
       <c r="B245" s="4">
-        <v>15.34</v>
+        <v>15.16</v>
       </c>
       <c r="C245" s="4">
-        <v>7.42</v>
+        <v>7.29</v>
       </c>
       <c r="D245" s="4">
         <v>0</v>
@@ -4696,13 +4697,13 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="3">
-        <v>40275</v>
+        <v>40291</v>
       </c>
       <c r="B246" s="4">
-        <v>15.38</v>
+        <v>15.34</v>
       </c>
       <c r="C246" s="4">
-        <v>7.54</v>
+        <v>7.42</v>
       </c>
       <c r="D246" s="4">
         <v>0</v>
@@ -4710,13 +4711,13 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="3">
-        <v>40261</v>
+        <v>40275</v>
       </c>
       <c r="B247" s="4">
-        <v>15.34</v>
+        <v>15.38</v>
       </c>
       <c r="C247" s="4">
-        <v>7.04</v>
+        <v>7.54</v>
       </c>
       <c r="D247" s="4">
         <v>0</v>
@@ -4724,13 +4725,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="3">
-        <v>40247</v>
+        <v>40261</v>
       </c>
       <c r="B248" s="4">
-        <v>15.18</v>
+        <v>15.34</v>
       </c>
       <c r="C248" s="4">
-        <v>7.12</v>
+        <v>7.04</v>
       </c>
       <c r="D248" s="4">
         <v>0</v>
@@ -4738,13 +4739,13 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="3">
-        <v>40234</v>
+        <v>40247</v>
       </c>
       <c r="B249" s="4">
-        <v>15.26</v>
+        <v>15.18</v>
       </c>
       <c r="C249" s="4">
-        <v>7.18</v>
+        <v>7.12</v>
       </c>
       <c r="D249" s="4">
         <v>0</v>
@@ -4752,13 +4753,13 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="3">
-        <v>40214</v>
+        <v>40234</v>
       </c>
       <c r="B250" s="4">
-        <v>15.34</v>
+        <v>15.26</v>
       </c>
       <c r="C250" s="4">
-        <v>7.22</v>
+        <v>7.18</v>
       </c>
       <c r="D250" s="4">
         <v>0</v>
@@ -4766,13 +4767,13 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="3">
-        <v>40200</v>
+        <v>40214</v>
       </c>
       <c r="B251" s="4">
-        <v>15.5</v>
+        <v>15.34</v>
       </c>
       <c r="C251" s="4">
-        <v>7.24</v>
+        <v>7.22</v>
       </c>
       <c r="D251" s="4">
         <v>0</v>
@@ -4780,13 +4781,13 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="3">
-        <v>40185</v>
+        <v>40200</v>
       </c>
       <c r="B252" s="4">
-        <v>15.1</v>
+        <v>15.5</v>
       </c>
       <c r="C252" s="4">
-        <v>7.18</v>
+        <v>7.24</v>
       </c>
       <c r="D252" s="4">
         <v>0</v>
@@ -4794,10 +4795,10 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="3">
-        <v>40169</v>
+        <v>40185</v>
       </c>
       <c r="B253" s="4">
-        <v>15.14</v>
+        <v>15.1</v>
       </c>
       <c r="C253" s="4">
         <v>7.18</v>
@@ -4808,13 +4809,13 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="3">
-        <v>40156</v>
+        <v>40169</v>
       </c>
       <c r="B254" s="4">
         <v>15.14</v>
       </c>
       <c r="C254" s="4">
-        <v>7.26</v>
+        <v>7.18</v>
       </c>
       <c r="D254" s="4">
         <v>0</v>
@@ -4822,13 +4823,13 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="3">
-        <v>40141</v>
+        <v>40156</v>
       </c>
       <c r="B255" s="4">
-        <v>15.72</v>
+        <v>15.14</v>
       </c>
       <c r="C255" s="4">
-        <v>7.72</v>
+        <v>7.26</v>
       </c>
       <c r="D255" s="4">
         <v>0</v>
@@ -4836,13 +4837,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="3">
-        <v>40126</v>
+        <v>40141</v>
       </c>
       <c r="B256" s="4">
         <v>15.72</v>
       </c>
       <c r="C256" s="4">
-        <v>8</v>
+        <v>7.72</v>
       </c>
       <c r="D256" s="4">
         <v>0</v>
@@ -4850,13 +4851,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="3">
-        <v>40108</v>
+        <v>40126</v>
       </c>
       <c r="B257" s="4">
-        <v>15.26</v>
+        <v>15.72</v>
       </c>
       <c r="C257" s="4">
-        <v>8.12</v>
+        <v>8</v>
       </c>
       <c r="D257" s="4">
         <v>0</v>
@@ -4864,13 +4865,13 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="3">
-        <v>40094</v>
+        <v>40108</v>
       </c>
       <c r="B258" s="4">
-        <v>14.5</v>
+        <v>15.26</v>
       </c>
       <c r="C258" s="4">
-        <v>7.68</v>
+        <v>8.12</v>
       </c>
       <c r="D258" s="4">
         <v>0</v>
@@ -4878,13 +4879,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="3">
-        <v>40078</v>
+        <v>40094</v>
       </c>
       <c r="B259" s="4">
-        <v>13.48</v>
+        <v>14.5</v>
       </c>
       <c r="C259" s="4">
-        <v>6.98</v>
+        <v>7.68</v>
       </c>
       <c r="D259" s="4">
         <v>0</v>
@@ -4892,13 +4893,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="3">
-        <v>40064</v>
+        <v>40078</v>
       </c>
       <c r="B260" s="4">
-        <v>13.36</v>
+        <v>13.48</v>
       </c>
       <c r="C260" s="4">
-        <v>6.8</v>
+        <v>6.98</v>
       </c>
       <c r="D260" s="4">
         <v>0</v>
@@ -4906,13 +4907,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="3">
-        <v>40049</v>
+        <v>40064</v>
       </c>
       <c r="B261" s="4">
-        <v>13</v>
+        <v>13.36</v>
       </c>
       <c r="C261" s="4">
-        <v>6.52</v>
+        <v>6.8</v>
       </c>
       <c r="D261" s="4">
         <v>0</v>
@@ -4920,7 +4921,7 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="3">
-        <v>40031</v>
+        <v>40049</v>
       </c>
       <c r="B262" s="4">
         <v>13</v>
@@ -4934,10 +4935,10 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="3">
-        <v>40016</v>
+        <v>40031</v>
       </c>
       <c r="B263" s="4">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="C263" s="4">
         <v>6.52</v>
@@ -4948,13 +4949,13 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="3">
-        <v>40002</v>
+        <v>40016</v>
       </c>
       <c r="B264" s="4">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="C264" s="4">
-        <v>6.64</v>
+        <v>6.52</v>
       </c>
       <c r="D264" s="4">
         <v>0</v>
@@ -4962,13 +4963,13 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="3">
-        <v>39987</v>
+        <v>40002</v>
       </c>
       <c r="B265" s="4">
-        <v>13.36</v>
+        <v>13.3</v>
       </c>
       <c r="C265" s="4">
-        <v>7</v>
+        <v>6.64</v>
       </c>
       <c r="D265" s="4">
         <v>0</v>
@@ -4976,10 +4977,10 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="3">
-        <v>39972</v>
+        <v>39987</v>
       </c>
       <c r="B266" s="4">
-        <v>14</v>
+        <v>13.36</v>
       </c>
       <c r="C266" s="4">
         <v>7</v>
@@ -4990,13 +4991,13 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="3">
-        <v>39955</v>
+        <v>39972</v>
       </c>
       <c r="B267" s="4">
-        <v>14.26</v>
+        <v>14</v>
       </c>
       <c r="C267" s="4">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="D267" s="4">
         <v>0</v>
@@ -5004,13 +5005,13 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="3">
-        <v>39941</v>
+        <v>39955</v>
       </c>
       <c r="B268" s="4">
-        <v>14.86</v>
+        <v>14.26</v>
       </c>
       <c r="C268" s="4">
-        <v>7.56</v>
+        <v>7.08</v>
       </c>
       <c r="D268" s="4">
         <v>0</v>
@@ -5018,13 +5019,13 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="3">
-        <v>39926</v>
+        <v>39941</v>
       </c>
       <c r="B269" s="4">
         <v>14.86</v>
       </c>
       <c r="C269" s="4">
-        <v>7.4</v>
+        <v>7.56</v>
       </c>
       <c r="D269" s="4">
         <v>0</v>
@@ -5032,13 +5033,13 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="3">
-        <v>39910</v>
+        <v>39926</v>
       </c>
       <c r="B270" s="4">
-        <v>12.58</v>
+        <v>14.86</v>
       </c>
       <c r="C270" s="4">
-        <v>6.44</v>
+        <v>7.4</v>
       </c>
       <c r="D270" s="4">
         <v>0</v>
@@ -5046,13 +5047,13 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="3">
-        <v>39896</v>
+        <v>39910</v>
       </c>
       <c r="B271" s="4">
-        <v>12.16</v>
+        <v>12.58</v>
       </c>
       <c r="C271" s="4">
-        <v>5.88</v>
+        <v>6.44</v>
       </c>
       <c r="D271" s="4">
         <v>0</v>
@@ -5060,13 +5061,13 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="3">
-        <v>39881</v>
+        <v>39896</v>
       </c>
       <c r="B272" s="4">
         <v>12.16</v>
       </c>
       <c r="C272" s="4">
-        <v>5.98</v>
+        <v>5.88</v>
       </c>
       <c r="D272" s="4">
         <v>0</v>
@@ -5074,10 +5075,10 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="3">
-        <v>39864</v>
+        <v>39881</v>
       </c>
       <c r="B273" s="4">
-        <v>12</v>
+        <v>12.16</v>
       </c>
       <c r="C273" s="4">
         <v>5.98</v>
@@ -5088,13 +5089,13 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="3">
-        <v>39850</v>
+        <v>39864</v>
       </c>
       <c r="B274" s="4">
-        <v>9.96</v>
+        <v>12</v>
       </c>
       <c r="C274" s="4">
-        <v>5</v>
+        <v>5.98</v>
       </c>
       <c r="D274" s="4">
         <v>0</v>
@@ -5102,13 +5103,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="3">
-        <v>39828</v>
+        <v>39850</v>
       </c>
       <c r="B275" s="4">
-        <v>9.02</v>
+        <v>9.96</v>
       </c>
       <c r="C275" s="4">
-        <v>4.74</v>
+        <v>5</v>
       </c>
       <c r="D275" s="4">
         <v>0</v>
@@ -5116,13 +5117,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="3">
-        <v>39820</v>
+        <v>39828</v>
       </c>
       <c r="B276" s="4">
-        <v>8.52</v>
+        <v>9.02</v>
       </c>
       <c r="C276" s="4">
-        <v>4.11</v>
+        <v>4.74</v>
       </c>
       <c r="D276" s="4">
         <v>0</v>
@@ -5130,13 +5131,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="3">
-        <v>39806</v>
+        <v>39820</v>
       </c>
       <c r="B277" s="4">
-        <v>9.5</v>
+        <v>8.52</v>
       </c>
       <c r="C277" s="4">
-        <v>3.72</v>
+        <v>4.11</v>
       </c>
       <c r="D277" s="4">
         <v>0</v>
@@ -5144,13 +5145,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="3">
-        <v>39791</v>
+        <v>39806</v>
       </c>
       <c r="B278" s="4">
-        <v>9.42</v>
+        <v>9.5</v>
       </c>
       <c r="C278" s="4">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="D278" s="4">
         <v>0</v>
@@ -5158,13 +5159,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="3">
-        <v>39776</v>
+        <v>39791</v>
       </c>
       <c r="B279" s="4">
-        <v>10.84</v>
+        <v>9.42</v>
       </c>
       <c r="C279" s="4">
-        <v>4.85</v>
+        <v>3.62</v>
       </c>
       <c r="D279" s="4">
         <v>0</v>
@@ -5172,7 +5173,7 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="3">
-        <v>39762</v>
+        <v>39776</v>
       </c>
       <c r="B280" s="4">
         <v>10.84</v>
@@ -5186,13 +5187,13 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="3">
-        <v>39744</v>
+        <v>39762</v>
       </c>
       <c r="B281" s="4">
-        <v>11.6</v>
+        <v>10.84</v>
       </c>
       <c r="C281" s="4">
-        <v>5.36</v>
+        <v>4.85</v>
       </c>
       <c r="D281" s="4">
         <v>0</v>
@@ -5200,7 +5201,7 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" s="3">
-        <v>39729</v>
+        <v>39744</v>
       </c>
       <c r="B282" s="4">
         <v>11.6</v>
@@ -5214,13 +5215,13 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" s="3">
-        <v>39713</v>
+        <v>39729</v>
       </c>
       <c r="B283" s="4">
-        <v>12.38</v>
+        <v>11.6</v>
       </c>
       <c r="C283" s="4">
-        <v>5.53</v>
+        <v>5.36</v>
       </c>
       <c r="D283" s="4">
         <v>0</v>
@@ -5228,13 +5229,13 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" s="3">
-        <v>39700</v>
+        <v>39713</v>
       </c>
       <c r="B284" s="4">
-        <v>13.44</v>
+        <v>12.38</v>
       </c>
       <c r="C284" s="4">
-        <v>6.36</v>
+        <v>5.53</v>
       </c>
       <c r="D284" s="4">
         <v>0</v>
@@ -5242,13 +5243,13 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="3">
-        <v>39682</v>
+        <v>39700</v>
       </c>
       <c r="B285" s="4">
-        <v>15</v>
+        <v>13.44</v>
       </c>
       <c r="C285" s="4">
-        <v>7.36</v>
+        <v>6.36</v>
       </c>
       <c r="D285" s="4">
         <v>0</v>
@@ -5256,13 +5257,13 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="3">
-        <v>39667</v>
+        <v>39682</v>
       </c>
       <c r="B286" s="4">
-        <v>16.18</v>
+        <v>15</v>
       </c>
       <c r="C286" s="4">
-        <v>7.98</v>
+        <v>7.36</v>
       </c>
       <c r="D286" s="4">
         <v>0</v>
@@ -5270,13 +5271,13 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" s="3">
-        <v>39652</v>
+        <v>39667</v>
       </c>
       <c r="B287" s="4">
-        <v>18.54</v>
+        <v>16.18</v>
       </c>
       <c r="C287" s="4">
-        <v>9.04</v>
+        <v>7.98</v>
       </c>
       <c r="D287" s="4">
         <v>0</v>
@@ -5284,13 +5285,13 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="3">
-        <v>39636</v>
+        <v>39652</v>
       </c>
       <c r="B288" s="4">
-        <v>19.02</v>
+        <v>18.54</v>
       </c>
       <c r="C288" s="4">
-        <v>9.18</v>
+        <v>9.04</v>
       </c>
       <c r="D288" s="4">
         <v>0</v>
@@ -5298,13 +5299,13 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="3">
-        <v>39624</v>
+        <v>39636</v>
       </c>
       <c r="B289" s="4">
-        <v>20.5</v>
+        <v>19.02</v>
       </c>
       <c r="C289" s="4">
-        <v>9.64</v>
+        <v>9.18</v>
       </c>
       <c r="D289" s="4">
         <v>0</v>
@@ -5312,13 +5313,13 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" s="3">
-        <v>39605</v>
+        <v>39624</v>
       </c>
       <c r="B290" s="4">
-        <v>22.7</v>
+        <v>20.5</v>
       </c>
       <c r="C290" s="4">
-        <v>11.16</v>
+        <v>9.64</v>
       </c>
       <c r="D290" s="4">
         <v>0</v>
@@ -5326,13 +5327,13 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" s="3">
-        <v>39591</v>
+        <v>39605</v>
       </c>
       <c r="B291" s="4">
-        <v>23.9</v>
+        <v>22.7</v>
       </c>
       <c r="C291" s="4">
-        <v>11.46</v>
+        <v>11.16</v>
       </c>
       <c r="D291" s="4">
         <v>0</v>
@@ -5340,13 +5341,13 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" s="3">
-        <v>39576</v>
+        <v>39591</v>
       </c>
       <c r="B292" s="4">
-        <v>24.96</v>
+        <v>23.9</v>
       </c>
       <c r="C292" s="4">
-        <v>11.92</v>
+        <v>11.46</v>
       </c>
       <c r="D292" s="4">
         <v>0</v>
@@ -5354,13 +5355,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" s="3">
-        <v>39561</v>
+        <v>39576</v>
       </c>
       <c r="B293" s="4">
-        <v>25.08</v>
+        <v>24.96</v>
       </c>
       <c r="C293" s="4">
-        <v>11.94</v>
+        <v>11.92</v>
       </c>
       <c r="D293" s="4">
         <v>0</v>
@@ -5368,13 +5369,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" s="3">
-        <v>39549</v>
+        <v>39561</v>
       </c>
       <c r="B294" s="4">
-        <v>26</v>
+        <v>25.08</v>
       </c>
       <c r="C294" s="4">
-        <v>11.76</v>
+        <v>11.94</v>
       </c>
       <c r="D294" s="4">
         <v>0</v>
@@ -5382,13 +5383,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" s="3">
-        <v>39533</v>
+        <v>39549</v>
       </c>
       <c r="B295" s="4">
-        <v>24.76</v>
+        <v>26</v>
       </c>
       <c r="C295" s="4">
-        <v>11.1</v>
+        <v>11.76</v>
       </c>
       <c r="D295" s="4">
         <v>0</v>
@@ -5396,13 +5397,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" s="3">
-        <v>39517</v>
+        <v>39533</v>
       </c>
       <c r="B296" s="4">
-        <v>25.3</v>
+        <v>24.76</v>
       </c>
       <c r="C296" s="4">
-        <v>11.32</v>
+        <v>11.1</v>
       </c>
       <c r="D296" s="4">
         <v>0</v>
@@ -5410,13 +5411,13 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" s="3">
-        <v>39503</v>
+        <v>39517</v>
       </c>
       <c r="B297" s="4">
         <v>25.3</v>
       </c>
       <c r="C297" s="4">
-        <v>11.7</v>
+        <v>11.32</v>
       </c>
       <c r="D297" s="4">
         <v>0</v>
@@ -5424,13 +5425,13 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" s="3">
-        <v>39483</v>
+        <v>39503</v>
       </c>
       <c r="B298" s="4">
-        <v>26.16</v>
+        <v>25.3</v>
       </c>
       <c r="C298" s="4">
-        <v>12.12</v>
+        <v>11.7</v>
       </c>
       <c r="D298" s="4">
         <v>0</v>
@@ -5438,7 +5439,7 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" s="3">
-        <v>39469</v>
+        <v>39483</v>
       </c>
       <c r="B299" s="4">
         <v>26.16</v>
@@ -5452,7 +5453,7 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" s="3">
-        <v>39456</v>
+        <v>39469</v>
       </c>
       <c r="B300" s="4">
         <v>26.16</v>
@@ -5461,6 +5462,20 @@
         <v>12.12</v>
       </c>
       <c r="D300" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="3">
+        <v>39456</v>
+      </c>
+      <c r="B301" s="4">
+        <v>26.16</v>
+      </c>
+      <c r="C301" s="4">
+        <v>12.12</v>
+      </c>
+      <c r="D301" s="4">
         <v>0</v>
       </c>
     </row>

--- a/edb_data/NAND合约平均价格.xlsx
+++ b/edb_data/NAND合约平均价格.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="22188" windowHeight="8460"/>
   </bookViews>
   <sheets>
     <sheet name="合约平均价_NAND Flash(64G" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029" calcMode="manual"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/edb_data/NAND合约平均价格.xlsx
+++ b/edb_data/NAND合约平均价格.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8460"/>
+    <workbookView windowWidth="27948" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="合约平均价_NAND Flash(64G" sheetId="1" r:id="rId1"/>

--- a/edb_data/NAND合约平均价格.xlsx
+++ b/edb_data/NAND合约平均价格.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="合约平均价_NAND Flash(64G" sheetId="1" r:id="rId1"/>
@@ -699,13 +699,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1266,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D302"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.8888888888889"/>
@@ -1295,245 +1301,245 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3">
-        <v>46171</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="4">
-        <v>19.165</v>
+        <v>21.365</v>
       </c>
       <c r="C3" s="4">
-        <v>15.493</v>
+        <v>17.075</v>
       </c>
       <c r="D3" s="4">
-        <v>26.508</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3">
-        <v>46142</v>
+        <v>46171</v>
       </c>
       <c r="B4" s="4">
-        <v>17.325</v>
+        <v>19.165</v>
       </c>
       <c r="C4" s="4">
-        <v>14.1</v>
+        <v>15.493</v>
       </c>
       <c r="D4" s="4">
-        <v>24.158</v>
+        <v>26.508</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B5" s="4">
-        <v>12.713</v>
+        <v>17.325</v>
       </c>
       <c r="C5" s="4">
-        <v>10.45</v>
+        <v>14.1</v>
       </c>
       <c r="D5" s="4">
-        <v>17.725</v>
+        <v>24.158</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3">
-        <v>46079</v>
+        <v>46112</v>
       </c>
       <c r="B6" s="4">
-        <v>8.513</v>
+        <v>12.713</v>
       </c>
       <c r="C6" s="4">
-        <v>7.208</v>
+        <v>10.45</v>
       </c>
       <c r="D6" s="4">
-        <v>12.665</v>
+        <v>17.725</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="B7" s="4">
-        <v>7.023</v>
+        <v>8.513</v>
       </c>
       <c r="C7" s="4">
-        <v>5.57</v>
+        <v>7.208</v>
       </c>
       <c r="D7" s="4">
-        <v>9.458</v>
+        <v>12.665</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="B8" s="4">
-        <v>4.59</v>
+        <v>7.023</v>
       </c>
       <c r="C8" s="4">
-        <v>3.66</v>
+        <v>5.57</v>
       </c>
       <c r="D8" s="4">
-        <v>5.738</v>
+        <v>9.458</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="B9" s="4">
-        <v>4.02</v>
+        <v>4.59</v>
       </c>
       <c r="C9" s="4">
-        <v>3.295</v>
+        <v>3.66</v>
       </c>
       <c r="D9" s="4">
-        <v>5.19</v>
+        <v>5.738</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3">
-        <v>45961</v>
+        <v>45989</v>
       </c>
       <c r="B10" s="4">
-        <v>3.333</v>
+        <v>4.02</v>
       </c>
       <c r="C10" s="4">
-        <v>2.795</v>
+        <v>3.295</v>
       </c>
       <c r="D10" s="4">
-        <v>4.35</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B11" s="4">
-        <v>2.825</v>
+        <v>3.333</v>
       </c>
       <c r="C11" s="4">
-        <v>2.39</v>
+        <v>2.795</v>
       </c>
       <c r="D11" s="4">
-        <v>3.785</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3">
-        <v>45898</v>
+        <v>45930</v>
       </c>
       <c r="B12" s="4">
-        <v>2.44</v>
+        <v>2.825</v>
       </c>
       <c r="C12" s="4">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="D12" s="4">
-        <v>3.423</v>
+        <v>3.785</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3">
-        <v>45869</v>
+        <v>45898</v>
       </c>
       <c r="B13" s="4">
-        <v>2.408</v>
+        <v>2.44</v>
       </c>
       <c r="C13" s="4">
-        <v>2.035</v>
+        <v>2.05</v>
       </c>
       <c r="D13" s="4">
-        <v>3.385</v>
+        <v>3.423</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B14" s="4">
-        <v>2.23</v>
+        <v>2.408</v>
       </c>
       <c r="C14" s="4">
-        <v>1.878</v>
+        <v>2.035</v>
       </c>
       <c r="D14" s="4">
-        <v>3.115</v>
+        <v>3.385</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3">
-        <v>45806</v>
+        <v>45838</v>
       </c>
       <c r="B15" s="4">
-        <v>2.028</v>
+        <v>2.23</v>
       </c>
       <c r="C15" s="4">
-        <v>1.74</v>
+        <v>1.878</v>
       </c>
       <c r="D15" s="4">
-        <v>2.923</v>
+        <v>3.115</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3">
-        <v>45777</v>
+        <v>45806</v>
       </c>
       <c r="B16" s="4">
-        <v>1.925</v>
+        <v>2.028</v>
       </c>
       <c r="C16" s="4">
-        <v>1.655</v>
+        <v>1.74</v>
       </c>
       <c r="D16" s="4">
-        <v>2.788</v>
+        <v>2.923</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B17" s="4">
-        <v>0</v>
+        <v>1.925</v>
       </c>
       <c r="C17" s="4">
-        <v>1.455</v>
+        <v>1.655</v>
       </c>
       <c r="D17" s="4">
-        <v>2.51</v>
+        <v>2.788</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3">
-        <v>45715</v>
+        <v>45747</v>
       </c>
       <c r="B18" s="4">
         <v>0</v>
       </c>
       <c r="C18" s="4">
-        <v>1.318</v>
+        <v>1.455</v>
       </c>
       <c r="D18" s="4">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3">
-        <v>45681</v>
+        <v>45715</v>
       </c>
       <c r="B19" s="4">
         <v>0</v>
       </c>
       <c r="C19" s="4">
-        <v>0</v>
+        <v>1.318</v>
       </c>
       <c r="D19" s="4">
-        <v>2.175</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3">
-        <v>45657</v>
+        <v>45681</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -1542,12 +1548,12 @@
         <v>0</v>
       </c>
       <c r="D20" s="4">
-        <v>2.08</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3">
-        <v>45625</v>
+        <v>45657</v>
       </c>
       <c r="B21" s="4">
         <v>0</v>
@@ -1556,54 +1562,54 @@
         <v>0</v>
       </c>
       <c r="D21" s="4">
-        <v>2.155</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="3">
-        <v>45596</v>
+        <v>45625</v>
       </c>
       <c r="B22" s="4">
-        <v>2.388</v>
+        <v>0</v>
       </c>
       <c r="C22" s="4">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="D22" s="4">
-        <v>3.07</v>
+        <v>2.155</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="3">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B23" s="4">
-        <v>2.985</v>
+        <v>2.388</v>
       </c>
       <c r="C23" s="4">
-        <v>2.349</v>
+        <v>1.81</v>
       </c>
       <c r="D23" s="4">
-        <v>4.335</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="3">
-        <v>45534</v>
+        <v>45565</v>
       </c>
       <c r="B24" s="4">
-        <v>3.385</v>
+        <v>2.985</v>
       </c>
       <c r="C24" s="4">
-        <v>2.604</v>
+        <v>2.349</v>
       </c>
       <c r="D24" s="4">
-        <v>4.895</v>
+        <v>4.335</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="3">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B25" s="4">
         <v>3.385</v>
@@ -1617,7 +1623,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="3">
-        <v>45471</v>
+        <v>45504</v>
       </c>
       <c r="B26" s="4">
         <v>3.385</v>
@@ -1631,7 +1637,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="3">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B27" s="4">
         <v>3.385</v>
@@ -1645,7 +1651,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="3">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B28" s="4">
         <v>3.385</v>
@@ -1659,7 +1665,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="3">
-        <v>45380</v>
+        <v>45412</v>
       </c>
       <c r="B29" s="4">
         <v>3.385</v>
@@ -1673,7 +1679,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="3">
-        <v>45351</v>
+        <v>45380</v>
       </c>
       <c r="B30" s="4">
         <v>3.385</v>
@@ -1687,77 +1693,77 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="3">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B31" s="4">
-        <v>3.278</v>
+        <v>3.385</v>
       </c>
       <c r="C31" s="4">
         <v>2.604</v>
       </c>
       <c r="D31" s="4">
-        <v>4.715</v>
+        <v>4.895</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3">
-        <v>45289</v>
+        <v>45322</v>
       </c>
       <c r="B32" s="4">
-        <v>3.02</v>
+        <v>3.278</v>
       </c>
       <c r="C32" s="4">
-        <v>2.57</v>
+        <v>2.604</v>
       </c>
       <c r="D32" s="4">
-        <v>4.331</v>
+        <v>4.715</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="3">
-        <v>45260</v>
+        <v>45289</v>
       </c>
       <c r="B33" s="4">
-        <v>2.915</v>
+        <v>3.02</v>
       </c>
       <c r="C33" s="4">
-        <v>2.516</v>
+        <v>2.57</v>
       </c>
       <c r="D33" s="4">
-        <v>4.085</v>
+        <v>4.331</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B34" s="4">
-        <v>2.794</v>
+        <v>2.915</v>
       </c>
       <c r="C34" s="4">
-        <v>2.469</v>
+        <v>2.516</v>
       </c>
       <c r="D34" s="4">
-        <v>3.876</v>
+        <v>4.085</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3">
-        <v>45197</v>
+        <v>45230</v>
       </c>
       <c r="B35" s="4">
-        <v>2.76</v>
+        <v>2.794</v>
       </c>
       <c r="C35" s="4">
-        <v>2.433</v>
+        <v>2.469</v>
       </c>
       <c r="D35" s="4">
-        <v>3.815</v>
+        <v>3.876</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3">
-        <v>45169</v>
+        <v>45197</v>
       </c>
       <c r="B36" s="4">
         <v>2.76</v>
@@ -1771,7 +1777,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B37" s="4">
         <v>2.76</v>
@@ -1785,7 +1791,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B38" s="4">
         <v>2.76</v>
@@ -1799,7 +1805,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B39" s="4">
         <v>2.76</v>
@@ -1813,7 +1819,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3">
-        <v>45044</v>
+        <v>45077</v>
       </c>
       <c r="B40" s="4">
         <v>2.76</v>
@@ -1827,35 +1833,35 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3">
-        <v>45016</v>
+        <v>45044</v>
       </c>
       <c r="B41" s="4">
-        <v>2.838</v>
+        <v>2.76</v>
       </c>
       <c r="C41" s="4">
-        <v>2.461</v>
+        <v>2.433</v>
       </c>
       <c r="D41" s="4">
-        <v>3.93</v>
+        <v>3.815</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="3">
-        <v>44981</v>
+        <v>45016</v>
       </c>
       <c r="B42" s="4">
-        <v>2.983</v>
+        <v>2.838</v>
       </c>
       <c r="C42" s="4">
-        <v>2.587</v>
+        <v>2.461</v>
       </c>
       <c r="D42" s="4">
-        <v>4.142</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="3">
-        <v>44957</v>
+        <v>44981</v>
       </c>
       <c r="B43" s="4">
         <v>2.983</v>
@@ -1869,7 +1875,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3">
-        <v>44925</v>
+        <v>44957</v>
       </c>
       <c r="B44" s="4">
         <v>2.983</v>
@@ -1883,10 +1889,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="3">
-        <v>44895</v>
+        <v>44925</v>
       </c>
       <c r="B45" s="4">
-        <v>2.998</v>
+        <v>2.983</v>
       </c>
       <c r="C45" s="4">
         <v>2.587</v>
@@ -1897,7 +1903,7 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="3">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B46" s="4">
         <v>2.998</v>
@@ -1911,77 +1917,77 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="3">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B47" s="4">
-        <v>3.105</v>
+        <v>2.998</v>
       </c>
       <c r="C47" s="4">
-        <v>2.685</v>
+        <v>2.587</v>
       </c>
       <c r="D47" s="4">
-        <v>4.303</v>
+        <v>4.142</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="3">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B48" s="4">
-        <v>3.173</v>
+        <v>3.105</v>
       </c>
       <c r="C48" s="4">
-        <v>2.74</v>
+        <v>2.685</v>
       </c>
       <c r="D48" s="4">
-        <v>4.415</v>
+        <v>4.303</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="3">
-        <v>44771</v>
+        <v>44804</v>
       </c>
       <c r="B49" s="4">
-        <v>3.223</v>
+        <v>3.173</v>
       </c>
       <c r="C49" s="4">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="D49" s="4">
-        <v>4.49</v>
+        <v>4.415</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="3">
-        <v>44742</v>
+        <v>44771</v>
       </c>
       <c r="B50" s="4">
-        <v>3.337</v>
+        <v>3.223</v>
       </c>
       <c r="C50" s="4">
-        <v>2.855</v>
+        <v>2.79</v>
       </c>
       <c r="D50" s="4">
-        <v>4.665</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="3">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B51" s="4">
-        <v>3.44</v>
+        <v>3.337</v>
       </c>
       <c r="C51" s="4">
-        <v>3</v>
+        <v>2.855</v>
       </c>
       <c r="D51" s="4">
-        <v>4.81</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="3">
-        <v>44680</v>
+        <v>44712</v>
       </c>
       <c r="B52" s="4">
         <v>3.44</v>
@@ -1995,7 +2001,7 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="3">
-        <v>44651</v>
+        <v>44680</v>
       </c>
       <c r="B53" s="4">
         <v>3.44</v>
@@ -2009,7 +2015,7 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="3">
-        <v>44617</v>
+        <v>44651</v>
       </c>
       <c r="B54" s="4">
         <v>3.44</v>
@@ -2023,7 +2029,7 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="3">
-        <v>44589</v>
+        <v>44617</v>
       </c>
       <c r="B55" s="4">
         <v>3.44</v>
@@ -2037,7 +2043,7 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="3">
-        <v>44560</v>
+        <v>44589</v>
       </c>
       <c r="B56" s="4">
         <v>3.44</v>
@@ -2051,7 +2057,7 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="3">
-        <v>44530</v>
+        <v>44560</v>
       </c>
       <c r="B57" s="4">
         <v>3.44</v>
@@ -2065,7 +2071,7 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="3">
-        <v>44498</v>
+        <v>44530</v>
       </c>
       <c r="B58" s="4">
         <v>3.44</v>
@@ -2079,7 +2085,7 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="3">
-        <v>44469</v>
+        <v>44498</v>
       </c>
       <c r="B59" s="4">
         <v>3.44</v>
@@ -2093,7 +2099,7 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="3">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="B60" s="4">
         <v>3.44</v>
@@ -2107,7 +2113,7 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="3">
-        <v>44407</v>
+        <v>44439</v>
       </c>
       <c r="B61" s="4">
         <v>3.44</v>
@@ -2121,21 +2127,21 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="3">
-        <v>44377</v>
+        <v>44407</v>
       </c>
       <c r="B62" s="4">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="C62" s="4">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="D62" s="4">
-        <v>4.56</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="3">
-        <v>44347</v>
+        <v>44377</v>
       </c>
       <c r="B63" s="4">
         <v>3.26</v>
@@ -2149,13 +2155,13 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="3">
-        <v>44315</v>
+        <v>44347</v>
       </c>
       <c r="B64" s="4">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="C64" s="4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D64" s="4">
         <v>4.56</v>
@@ -2163,21 +2169,21 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="3">
-        <v>44286</v>
+        <v>44315</v>
       </c>
       <c r="B65" s="4">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="C65" s="4">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="D65" s="4">
-        <v>4.2</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="3">
-        <v>44253</v>
+        <v>44286</v>
       </c>
       <c r="B66" s="4">
         <v>2.94</v>
@@ -2191,7 +2197,7 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="3">
-        <v>44225</v>
+        <v>44253</v>
       </c>
       <c r="B67" s="4">
         <v>2.94</v>
@@ -2205,7 +2211,7 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="3">
-        <v>44196</v>
+        <v>44225</v>
       </c>
       <c r="B68" s="4">
         <v>2.94</v>
@@ -2219,7 +2225,7 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="3">
-        <v>44165</v>
+        <v>44196</v>
       </c>
       <c r="B69" s="4">
         <v>2.94</v>
@@ -2233,7 +2239,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="3">
-        <v>44134</v>
+        <v>44165</v>
       </c>
       <c r="B70" s="4">
         <v>2.94</v>
@@ -2242,18 +2248,18 @@
         <v>2.55</v>
       </c>
       <c r="D70" s="4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="3">
-        <v>44104</v>
+        <v>44134</v>
       </c>
       <c r="B71" s="4">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="C71" s="4">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="D71" s="4">
         <v>0</v>
@@ -2261,7 +2267,7 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="3">
-        <v>44074</v>
+        <v>44104</v>
       </c>
       <c r="B72" s="4">
         <v>3.03</v>
@@ -2275,13 +2281,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="3">
-        <v>44043</v>
+        <v>44074</v>
       </c>
       <c r="B73" s="4">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="C73" s="4">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="D73" s="4">
         <v>0</v>
@@ -2289,13 +2295,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="3">
-        <v>44012</v>
+        <v>44043</v>
       </c>
       <c r="B74" s="4">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="C74" s="4">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="D74" s="4">
         <v>0</v>
@@ -2303,7 +2309,7 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="3">
-        <v>43980</v>
+        <v>44012</v>
       </c>
       <c r="B75" s="4">
         <v>3.24</v>
@@ -2317,7 +2323,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="3">
-        <v>43951</v>
+        <v>43980</v>
       </c>
       <c r="B76" s="4">
         <v>3.24</v>
@@ -2331,7 +2337,7 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="3">
-        <v>43921</v>
+        <v>43951</v>
       </c>
       <c r="B77" s="4">
         <v>3.24</v>
@@ -2345,13 +2351,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="3">
-        <v>43888</v>
+        <v>43921</v>
       </c>
       <c r="B78" s="4">
-        <v>3.11</v>
+        <v>3.24</v>
       </c>
       <c r="C78" s="4">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="D78" s="4">
         <v>0</v>
@@ -2359,7 +2365,7 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="3">
-        <v>43860</v>
+        <v>43888</v>
       </c>
       <c r="B79" s="4">
         <v>3.11</v>
@@ -2373,10 +2379,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="3">
-        <v>43830</v>
+        <v>43860</v>
       </c>
       <c r="B80" s="4">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="C80" s="4">
         <v>2.66</v>
@@ -2387,13 +2393,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="3">
-        <v>43798</v>
+        <v>43830</v>
       </c>
       <c r="B81" s="4">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="C81" s="4">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="D81" s="4">
         <v>0</v>
@@ -2401,7 +2407,7 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="3">
-        <v>43769</v>
+        <v>43798</v>
       </c>
       <c r="B82" s="4">
         <v>2.85</v>
@@ -2415,13 +2421,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="3">
-        <v>43738</v>
+        <v>43769</v>
       </c>
       <c r="B83" s="4">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="C83" s="4">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="D83" s="4">
         <v>0</v>
@@ -2429,7 +2435,7 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="3">
-        <v>43707</v>
+        <v>43738</v>
       </c>
       <c r="B84" s="4">
         <v>2.75</v>
@@ -2443,13 +2449,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="3">
-        <v>43677</v>
+        <v>43707</v>
       </c>
       <c r="B85" s="4">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="C85" s="4">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="D85" s="4">
         <v>0</v>
@@ -2457,13 +2463,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="3">
-        <v>43644</v>
+        <v>43677</v>
       </c>
       <c r="B86" s="4">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="C86" s="4">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="D86" s="4">
         <v>0</v>
@@ -2471,7 +2477,7 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="3">
-        <v>43616</v>
+        <v>43644</v>
       </c>
       <c r="B87" s="4">
         <v>2.68</v>
@@ -2485,13 +2491,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="3">
-        <v>43585</v>
+        <v>43616</v>
       </c>
       <c r="B88" s="4">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="C88" s="4">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="D88" s="4">
         <v>0</v>
@@ -2499,13 +2505,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="3">
-        <v>43553</v>
+        <v>43585</v>
       </c>
       <c r="B89" s="4">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="C89" s="4">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="D89" s="4">
         <v>0</v>
@@ -2513,13 +2519,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="3">
-        <v>43523</v>
+        <v>43553</v>
       </c>
       <c r="B90" s="4">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="C90" s="4">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="D90" s="4">
         <v>0</v>
@@ -2527,10 +2533,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="3">
-        <v>43496</v>
+        <v>43523</v>
       </c>
       <c r="B91" s="4">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="C91" s="4">
         <v>2.64</v>
@@ -2541,10 +2547,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="3">
-        <v>43462</v>
+        <v>43496</v>
       </c>
       <c r="B92" s="4">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="C92" s="4">
         <v>2.64</v>
@@ -2555,13 +2561,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="3">
-        <v>43434</v>
+        <v>43462</v>
       </c>
       <c r="B93" s="4">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="C93" s="4">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="D93" s="4">
         <v>0</v>
@@ -2569,7 +2575,7 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="3">
-        <v>43404</v>
+        <v>43434</v>
       </c>
       <c r="B94" s="4">
         <v>3.25</v>
@@ -2583,13 +2589,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="3">
-        <v>43371</v>
+        <v>43404</v>
       </c>
       <c r="B95" s="4">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="C95" s="4">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="D95" s="4">
         <v>0</v>
@@ -2597,10 +2603,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="3">
-        <v>43343</v>
+        <v>43371</v>
       </c>
       <c r="B96" s="4">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="C96" s="4">
         <v>2.89</v>
@@ -2611,7 +2617,7 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="3">
-        <v>43312</v>
+        <v>43343</v>
       </c>
       <c r="B97" s="4">
         <v>3.55</v>
@@ -2625,13 +2631,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="3">
-        <v>43280</v>
+        <v>43312</v>
       </c>
       <c r="B98" s="4">
-        <v>3.69</v>
+        <v>3.55</v>
       </c>
       <c r="C98" s="4">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="D98" s="4">
         <v>0</v>
@@ -2639,7 +2645,7 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="3">
-        <v>43251</v>
+        <v>43280</v>
       </c>
       <c r="B99" s="4">
         <v>3.69</v>
@@ -2653,7 +2659,7 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="3">
-        <v>43220</v>
+        <v>43251</v>
       </c>
       <c r="B100" s="4">
         <v>3.69</v>
@@ -2667,7 +2673,7 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="3">
-        <v>43189</v>
+        <v>43220</v>
       </c>
       <c r="B101" s="4">
         <v>3.69</v>
@@ -2681,7 +2687,7 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="3">
-        <v>43158</v>
+        <v>43189</v>
       </c>
       <c r="B102" s="4">
         <v>3.69</v>
@@ -2695,7 +2701,7 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="3">
-        <v>43131</v>
+        <v>43158</v>
       </c>
       <c r="B103" s="4">
         <v>3.69</v>
@@ -2709,7 +2715,7 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="3">
-        <v>43098</v>
+        <v>43131</v>
       </c>
       <c r="B104" s="4">
         <v>3.69</v>
@@ -2723,7 +2729,7 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="3">
-        <v>43069</v>
+        <v>43098</v>
       </c>
       <c r="B105" s="4">
         <v>3.69</v>
@@ -2737,7 +2743,7 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3">
-        <v>43039</v>
+        <v>43069</v>
       </c>
       <c r="B106" s="4">
         <v>3.69</v>
@@ -2751,13 +2757,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="3">
-        <v>43007</v>
+        <v>43039</v>
       </c>
       <c r="B107" s="4">
         <v>3.69</v>
       </c>
       <c r="C107" s="4">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="D107" s="4">
         <v>0</v>
@@ -2765,10 +2771,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="3">
-        <v>42978</v>
+        <v>43007</v>
       </c>
       <c r="B108" s="4">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="C108" s="4">
         <v>2.82</v>
@@ -2779,13 +2785,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3">
-        <v>42947</v>
+        <v>42978</v>
       </c>
       <c r="B109" s="4">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="C109" s="4">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="D109" s="4">
         <v>0</v>
@@ -2793,13 +2799,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="3">
-        <v>42916</v>
+        <v>42947</v>
       </c>
       <c r="B110" s="4">
-        <v>3.57</v>
+        <v>3.65</v>
       </c>
       <c r="C110" s="4">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="D110" s="4">
         <v>0</v>
@@ -2807,7 +2813,7 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="3">
-        <v>42881</v>
+        <v>42916</v>
       </c>
       <c r="B111" s="4">
         <v>3.57</v>
@@ -2821,7 +2827,7 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="3">
-        <v>42853</v>
+        <v>42881</v>
       </c>
       <c r="B112" s="4">
         <v>3.57</v>
@@ -2835,13 +2841,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="3">
-        <v>42825</v>
+        <v>42853</v>
       </c>
       <c r="B113" s="4">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="C113" s="4">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="D113" s="4">
         <v>0</v>
@@ -2849,13 +2855,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="3">
-        <v>42790</v>
+        <v>42825</v>
       </c>
       <c r="B114" s="4">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="C114" s="4">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="D114" s="4">
         <v>0</v>
@@ -2863,13 +2869,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="3">
-        <v>42760</v>
+        <v>42790</v>
       </c>
       <c r="B115" s="4">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="C115" s="4">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="D115" s="4">
         <v>0</v>
@@ -2877,13 +2883,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="3">
-        <v>42733</v>
+        <v>42760</v>
       </c>
       <c r="B116" s="4">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="C116" s="4">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="D116" s="4">
         <v>0</v>
@@ -2891,13 +2897,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="3">
-        <v>42704</v>
+        <v>42733</v>
       </c>
       <c r="B117" s="4">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="C117" s="4">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="D117" s="4">
         <v>0</v>
@@ -2905,10 +2911,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="3">
-        <v>42674</v>
+        <v>42704</v>
       </c>
       <c r="B118" s="4">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="C118" s="4">
         <v>1.89</v>
@@ -2919,13 +2925,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="3">
-        <v>42643</v>
+        <v>42674</v>
       </c>
       <c r="B119" s="4">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="C119" s="4">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="D119" s="4">
         <v>0</v>
@@ -2933,13 +2939,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="3">
-        <v>42613</v>
+        <v>42643</v>
       </c>
       <c r="B120" s="4">
         <v>2.32</v>
       </c>
       <c r="C120" s="4">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="D120" s="4">
         <v>0</v>
@@ -2947,13 +2953,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="3">
-        <v>42580</v>
+        <v>42613</v>
       </c>
       <c r="B121" s="4">
         <v>2.32</v>
       </c>
       <c r="C121" s="4">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="D121" s="4">
         <v>0</v>
@@ -2961,13 +2967,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="3">
-        <v>42521</v>
+        <v>42580</v>
       </c>
       <c r="B122" s="4">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="C122" s="4">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="D122" s="4">
         <v>0</v>
@@ -2975,7 +2981,7 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="3">
-        <v>42489</v>
+        <v>42521</v>
       </c>
       <c r="B123" s="4">
         <v>2.02</v>
@@ -2989,13 +2995,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="3">
-        <v>42426</v>
+        <v>42489</v>
       </c>
       <c r="B124" s="4">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="C124" s="4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="D124" s="4">
         <v>0</v>
@@ -3003,13 +3009,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="3">
-        <v>42398</v>
+        <v>42426</v>
       </c>
       <c r="B125" s="4">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="C125" s="4">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="D125" s="4">
         <v>0</v>
@@ -3017,10 +3023,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="3">
-        <v>42368</v>
+        <v>42398</v>
       </c>
       <c r="B126" s="4">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="C126" s="4">
         <v>1.58</v>
@@ -3031,13 +3037,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="3">
-        <v>42338</v>
+        <v>42368</v>
       </c>
       <c r="B127" s="4">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="C127" s="4">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="D127" s="4">
         <v>0</v>
@@ -3045,13 +3051,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="3">
-        <v>42307</v>
+        <v>42338</v>
       </c>
       <c r="B128" s="4">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="C128" s="4">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="D128" s="4">
         <v>0</v>
@@ -3059,13 +3065,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="3">
-        <v>42291</v>
+        <v>42307</v>
       </c>
       <c r="B129" s="4">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="C129" s="4">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="D129" s="4">
         <v>0</v>
@@ -3073,10 +3079,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="3">
-        <v>42277</v>
+        <v>42291</v>
       </c>
       <c r="B130" s="4">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="C130" s="4">
         <v>1.77</v>
@@ -3087,13 +3093,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="3">
-        <v>42262</v>
+        <v>42277</v>
       </c>
       <c r="B131" s="4">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="C131" s="4">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="D131" s="4">
         <v>0</v>
@@ -3101,10 +3107,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="3">
-        <v>42247</v>
+        <v>42262</v>
       </c>
       <c r="B132" s="4">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="C132" s="4">
         <v>1.8</v>
@@ -3115,13 +3121,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="3">
-        <v>42230</v>
+        <v>42247</v>
       </c>
       <c r="B133" s="4">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="C133" s="4">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="D133" s="4">
         <v>0</v>
@@ -3129,13 +3135,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="3">
-        <v>42216</v>
+        <v>42230</v>
       </c>
       <c r="B134" s="4">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="C134" s="4">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="D134" s="4">
         <v>0</v>
@@ -3143,13 +3149,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="3">
-        <v>42200</v>
+        <v>42216</v>
       </c>
       <c r="B135" s="4">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="C135" s="4">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="D135" s="4">
         <v>0</v>
@@ -3157,10 +3163,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="3">
-        <v>42185</v>
+        <v>42200</v>
       </c>
       <c r="B136" s="4">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="C136" s="4">
         <v>1.96</v>
@@ -3171,13 +3177,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="3">
-        <v>42170</v>
+        <v>42185</v>
       </c>
       <c r="B137" s="4">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="C137" s="4">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="D137" s="4">
         <v>0</v>
@@ -3185,7 +3191,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="3">
-        <v>42153</v>
+        <v>42170</v>
       </c>
       <c r="B138" s="4">
         <v>2.58</v>
@@ -3199,13 +3205,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="3">
-        <v>42139</v>
+        <v>42153</v>
       </c>
       <c r="B139" s="4">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="C139" s="4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="D139" s="4">
         <v>0</v>
@@ -3213,7 +3219,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="3">
-        <v>42124</v>
+        <v>42139</v>
       </c>
       <c r="B140" s="4">
         <v>2.61</v>
@@ -3227,7 +3233,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="3">
-        <v>42109</v>
+        <v>42124</v>
       </c>
       <c r="B141" s="4">
         <v>2.61</v>
@@ -3241,7 +3247,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="3">
-        <v>42094</v>
+        <v>42109</v>
       </c>
       <c r="B142" s="4">
         <v>2.61</v>
@@ -3255,10 +3261,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="3">
-        <v>42076</v>
+        <v>42094</v>
       </c>
       <c r="B143" s="4">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="C143" s="4">
         <v>1.98</v>
@@ -3269,10 +3275,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="3">
-        <v>42061</v>
+        <v>42076</v>
       </c>
       <c r="B144" s="4">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="C144" s="4">
         <v>1.98</v>
@@ -3283,13 +3289,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="3">
-        <v>42048</v>
+        <v>42061</v>
       </c>
       <c r="B145" s="4">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="C145" s="4">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="D145" s="4">
         <v>0</v>
@@ -3297,13 +3303,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="3">
-        <v>42034</v>
+        <v>42048</v>
       </c>
       <c r="B146" s="4">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="C146" s="4">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="D146" s="4">
         <v>0</v>
@@ -3311,13 +3317,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="3">
-        <v>42019</v>
+        <v>42034</v>
       </c>
       <c r="B147" s="4">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C147" s="4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="D147" s="4">
         <v>0</v>
@@ -3325,13 +3331,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="3">
-        <v>42004</v>
+        <v>42019</v>
       </c>
       <c r="B148" s="4">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C148" s="4">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="D148" s="4">
         <v>0</v>
@@ -3339,13 +3345,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="3">
-        <v>41988</v>
+        <v>42004</v>
       </c>
       <c r="B149" s="4">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="C149" s="4">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="D149" s="4">
         <v>0</v>
@@ -3353,10 +3359,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="3">
-        <v>41971</v>
+        <v>41988</v>
       </c>
       <c r="B150" s="4">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="C150" s="4">
         <v>2.2</v>
@@ -3367,13 +3373,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="3">
-        <v>41957</v>
+        <v>41971</v>
       </c>
       <c r="B151" s="4">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="C151" s="4">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="D151" s="4">
         <v>0</v>
@@ -3381,13 +3387,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="3">
-        <v>41943</v>
+        <v>41957</v>
       </c>
       <c r="B152" s="4">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="C152" s="4">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="D152" s="4">
         <v>0</v>
@@ -3395,13 +3401,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="3">
-        <v>41927</v>
+        <v>41943</v>
       </c>
       <c r="B153" s="4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="C153" s="4">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="D153" s="4">
         <v>0</v>
@@ -3409,7 +3415,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="3">
-        <v>41912</v>
+        <v>41927</v>
       </c>
       <c r="B154" s="4">
         <v>3.05</v>
@@ -3423,7 +3429,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="3">
-        <v>41897</v>
+        <v>41912</v>
       </c>
       <c r="B155" s="4">
         <v>3.05</v>
@@ -3437,13 +3443,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="3">
-        <v>41883</v>
+        <v>41897</v>
       </c>
       <c r="B156" s="4">
         <v>3.05</v>
       </c>
       <c r="C156" s="4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="D156" s="4">
         <v>0</v>
@@ -3451,7 +3457,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="3">
-        <v>41866</v>
+        <v>41883</v>
       </c>
       <c r="B157" s="4">
         <v>3.05</v>
@@ -3465,7 +3471,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="3">
-        <v>41851</v>
+        <v>41866</v>
       </c>
       <c r="B158" s="4">
         <v>3.05</v>
@@ -3479,13 +3485,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="3">
-        <v>41835</v>
+        <v>41851</v>
       </c>
       <c r="B159" s="4">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="C159" s="4">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="D159" s="4">
         <v>0</v>
@@ -3493,13 +3499,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="3">
-        <v>41820</v>
+        <v>41835</v>
       </c>
       <c r="B160" s="4">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="C160" s="4">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="D160" s="4">
         <v>0</v>
@@ -3507,13 +3513,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="3">
-        <v>41803</v>
+        <v>41820</v>
       </c>
       <c r="B161" s="4">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="C161" s="4">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="D161" s="4">
         <v>0</v>
@@ -3521,13 +3527,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="3">
-        <v>41789</v>
+        <v>41803</v>
       </c>
       <c r="B162" s="4">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="C162" s="4">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="D162" s="4">
         <v>0</v>
@@ -3535,13 +3541,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="3">
-        <v>41774</v>
+        <v>41789</v>
       </c>
       <c r="B163" s="4">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="C163" s="4">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="D163" s="4">
         <v>0</v>
@@ -3549,10 +3555,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="3">
-        <v>41759</v>
+        <v>41774</v>
       </c>
       <c r="B164" s="4">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="C164" s="4">
         <v>2.14</v>
@@ -3563,13 +3569,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="3">
-        <v>41729</v>
+        <v>41759</v>
       </c>
       <c r="B165" s="4">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="C165" s="4">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="D165" s="4">
         <v>0</v>
@@ -3577,13 +3583,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="3">
-        <v>41697</v>
+        <v>41729</v>
       </c>
       <c r="B166" s="4">
-        <v>3.03</v>
+        <v>2.81</v>
       </c>
       <c r="C166" s="4">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="D166" s="4">
         <v>0</v>
@@ -3591,13 +3597,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="3">
-        <v>41687</v>
+        <v>41697</v>
       </c>
       <c r="B167" s="4">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="C167" s="4">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="D167" s="4">
         <v>0</v>
@@ -3605,13 +3611,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="3">
-        <v>41668</v>
+        <v>41687</v>
       </c>
       <c r="B168" s="4">
-        <v>3.51</v>
+        <v>3.41</v>
       </c>
       <c r="C168" s="4">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="D168" s="4">
         <v>0</v>
@@ -3619,13 +3625,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="3">
-        <v>41655</v>
+        <v>41668</v>
       </c>
       <c r="B169" s="4">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="C169" s="4">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="D169" s="4">
         <v>0</v>
@@ -3633,13 +3639,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="3">
-        <v>41639</v>
+        <v>41655</v>
       </c>
       <c r="B170" s="4">
-        <v>3.68</v>
+        <v>3.56</v>
       </c>
       <c r="C170" s="4">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="D170" s="4">
         <v>0</v>
@@ -3647,13 +3653,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="3">
-        <v>41624</v>
+        <v>41639</v>
       </c>
       <c r="B171" s="4">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="C171" s="4">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="D171" s="4">
         <v>0</v>
@@ -3661,10 +3667,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="3">
-        <v>41610</v>
+        <v>41624</v>
       </c>
       <c r="B172" s="4">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="C172" s="4">
         <v>2.62</v>
@@ -3675,13 +3681,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="3">
-        <v>41592</v>
+        <v>41610</v>
       </c>
       <c r="B173" s="4">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="C173" s="4">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="D173" s="4">
         <v>0</v>
@@ -3689,13 +3695,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="3">
-        <v>41578</v>
+        <v>41592</v>
       </c>
       <c r="B174" s="4">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C174" s="4">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="D174" s="4">
         <v>0</v>
@@ -3703,13 +3709,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="3">
-        <v>41562</v>
+        <v>41578</v>
       </c>
       <c r="B175" s="4">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="C175" s="4">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="D175" s="4">
         <v>0</v>
@@ -3717,7 +3723,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="3">
-        <v>41548</v>
+        <v>41562</v>
       </c>
       <c r="B176" s="4">
         <v>4.72</v>
@@ -3731,13 +3737,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="3">
-        <v>41456</v>
+        <v>41548</v>
       </c>
       <c r="B177" s="4">
-        <v>5.52</v>
+        <v>4.72</v>
       </c>
       <c r="C177" s="4">
-        <v>3.58</v>
+        <v>3.07</v>
       </c>
       <c r="D177" s="4">
         <v>0</v>
@@ -3745,13 +3751,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="3">
-        <v>41428</v>
+        <v>41456</v>
       </c>
       <c r="B178" s="4">
-        <v>5.26</v>
+        <v>5.52</v>
       </c>
       <c r="C178" s="4">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="D178" s="4">
         <v>0</v>
@@ -3759,13 +3765,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="3">
-        <v>41409</v>
+        <v>41428</v>
       </c>
       <c r="B179" s="4">
         <v>5.26</v>
       </c>
       <c r="C179" s="4">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="D179" s="4">
         <v>0</v>
@@ -3773,13 +3779,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="3">
-        <v>41394</v>
+        <v>41409</v>
       </c>
       <c r="B180" s="4">
-        <v>5.34</v>
+        <v>5.26</v>
       </c>
       <c r="C180" s="4">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D180" s="4">
         <v>0</v>
@@ -3787,13 +3793,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="3">
-        <v>41379</v>
+        <v>41394</v>
       </c>
       <c r="B181" s="4">
         <v>5.34</v>
       </c>
       <c r="C181" s="4">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="D181" s="4">
         <v>0</v>
@@ -3801,13 +3807,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="3">
-        <v>41362</v>
+        <v>41379</v>
       </c>
       <c r="B182" s="4">
         <v>5.34</v>
       </c>
       <c r="C182" s="4">
-        <v>2.96</v>
+        <v>3.14</v>
       </c>
       <c r="D182" s="4">
         <v>0</v>
@@ -3815,13 +3821,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="3">
-        <v>41348</v>
+        <v>41362</v>
       </c>
       <c r="B183" s="4">
         <v>5.34</v>
       </c>
       <c r="C183" s="4">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="D183" s="4">
         <v>0</v>
@@ -3829,13 +3835,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="3">
-        <v>41327</v>
+        <v>41348</v>
       </c>
       <c r="B184" s="4">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="C184" s="4">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="D184" s="4">
         <v>0</v>
@@ -3843,13 +3849,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="3">
-        <v>41304</v>
+        <v>41327</v>
       </c>
       <c r="B185" s="4">
         <v>5</v>
       </c>
       <c r="C185" s="4">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="D185" s="4">
         <v>0</v>
@@ -3857,13 +3863,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="3">
-        <v>41289</v>
+        <v>41304</v>
       </c>
       <c r="B186" s="4">
         <v>5</v>
       </c>
       <c r="C186" s="4">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="D186" s="4">
         <v>0</v>
@@ -3871,13 +3877,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="3">
-        <v>41256</v>
+        <v>41289</v>
       </c>
       <c r="B187" s="4">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="C187" s="4">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="D187" s="4">
         <v>0</v>
@@ -3885,13 +3891,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="3">
-        <v>41243</v>
+        <v>41256</v>
       </c>
       <c r="B188" s="4">
         <v>4.98</v>
       </c>
       <c r="C188" s="4">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="D188" s="4">
         <v>0</v>
@@ -3899,10 +3905,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="3">
-        <v>41228</v>
+        <v>41243</v>
       </c>
       <c r="B189" s="4">
-        <v>5.4</v>
+        <v>4.98</v>
       </c>
       <c r="C189" s="4">
         <v>2.52</v>
@@ -3913,13 +3919,13 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="3">
-        <v>41208</v>
+        <v>41228</v>
       </c>
       <c r="B190" s="4">
-        <v>5.52</v>
+        <v>5.4</v>
       </c>
       <c r="C190" s="4">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="D190" s="4">
         <v>0</v>
@@ -3927,10 +3933,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="3">
-        <v>41197</v>
+        <v>41208</v>
       </c>
       <c r="B191" s="4">
-        <v>4.99</v>
+        <v>5.52</v>
       </c>
       <c r="C191" s="4">
         <v>2.59</v>
@@ -3941,13 +3947,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="3">
-        <v>41184</v>
+        <v>41197</v>
       </c>
       <c r="B192" s="4">
-        <v>4.26</v>
+        <v>4.99</v>
       </c>
       <c r="C192" s="4">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="D192" s="4">
         <v>0</v>
@@ -3955,13 +3961,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="3">
-        <v>41166</v>
+        <v>41184</v>
       </c>
       <c r="B193" s="4">
-        <v>3.91</v>
+        <v>4.26</v>
       </c>
       <c r="C193" s="4">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="D193" s="4">
         <v>0</v>
@@ -3969,13 +3975,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="3">
-        <v>41152</v>
+        <v>41166</v>
       </c>
       <c r="B194" s="4">
-        <v>3.87</v>
+        <v>3.91</v>
       </c>
       <c r="C194" s="4">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="D194" s="4">
         <v>0</v>
@@ -3983,7 +3989,7 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="3">
-        <v>41135</v>
+        <v>41152</v>
       </c>
       <c r="B195" s="4">
         <v>3.87</v>
@@ -3997,7 +4003,7 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="3">
-        <v>41121</v>
+        <v>41135</v>
       </c>
       <c r="B196" s="4">
         <v>3.87</v>
@@ -4011,13 +4017,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="3">
-        <v>41103</v>
+        <v>41121</v>
       </c>
       <c r="B197" s="4">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="C197" s="4">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="D197" s="4">
         <v>0</v>
@@ -4025,13 +4031,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="3">
-        <v>41089</v>
+        <v>41103</v>
       </c>
       <c r="B198" s="4">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="C198" s="4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="D198" s="4">
         <v>0</v>
@@ -4039,13 +4045,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="3">
-        <v>41075</v>
+        <v>41089</v>
       </c>
       <c r="B199" s="4">
-        <v>4.04</v>
+        <v>3.84</v>
       </c>
       <c r="C199" s="4">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="D199" s="4">
         <v>0</v>
@@ -4053,7 +4059,7 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="3">
-        <v>41060</v>
+        <v>41075</v>
       </c>
       <c r="B200" s="4">
         <v>4.04</v>
@@ -4067,13 +4073,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="3">
-        <v>41044</v>
+        <v>41060</v>
       </c>
       <c r="B201" s="4">
-        <v>4.41</v>
+        <v>4.04</v>
       </c>
       <c r="C201" s="4">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="D201" s="4">
         <v>0</v>
@@ -4081,13 +4087,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="3">
-        <v>41029</v>
+        <v>41044</v>
       </c>
       <c r="B202" s="4">
-        <v>4.66</v>
+        <v>4.41</v>
       </c>
       <c r="C202" s="4">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="D202" s="4">
         <v>0</v>
@@ -4095,13 +4101,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="3">
-        <v>41014</v>
+        <v>41029</v>
       </c>
       <c r="B203" s="4">
-        <v>4.79</v>
+        <v>4.66</v>
       </c>
       <c r="C203" s="4">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="D203" s="4">
         <v>0</v>
@@ -4109,13 +4115,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="3">
-        <v>40995</v>
+        <v>41014</v>
       </c>
       <c r="B204" s="4">
-        <v>4.95</v>
+        <v>4.79</v>
       </c>
       <c r="C204" s="4">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="D204" s="4">
         <v>0</v>
@@ -4123,13 +4129,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="3">
-        <v>40982</v>
+        <v>40995</v>
       </c>
       <c r="B205" s="4">
-        <v>5.02</v>
+        <v>4.95</v>
       </c>
       <c r="C205" s="4">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="D205" s="4">
         <v>0</v>
@@ -4137,13 +4143,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="3">
-        <v>40968</v>
+        <v>40982</v>
       </c>
       <c r="B206" s="4">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
       <c r="C206" s="4">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D206" s="4">
         <v>0</v>
@@ -4151,13 +4157,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="3">
-        <v>40954</v>
+        <v>40968</v>
       </c>
       <c r="B207" s="4">
-        <v>5.34</v>
+        <v>5.06</v>
       </c>
       <c r="C207" s="4">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="D207" s="4">
         <v>0</v>
@@ -4165,13 +4171,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="3">
-        <v>40924</v>
+        <v>40954</v>
       </c>
       <c r="B208" s="4">
-        <v>5.49</v>
+        <v>5.34</v>
       </c>
       <c r="C208" s="4">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="D208" s="4">
         <v>0</v>
@@ -4179,13 +4185,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="3">
-        <v>40907</v>
+        <v>40924</v>
       </c>
       <c r="B209" s="4">
-        <v>5.71</v>
+        <v>5.49</v>
       </c>
       <c r="C209" s="4">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="D209" s="4">
         <v>0</v>
@@ -4193,13 +4199,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="3">
-        <v>40892</v>
+        <v>40907</v>
       </c>
       <c r="B210" s="4">
-        <v>6.09</v>
+        <v>5.71</v>
       </c>
       <c r="C210" s="4">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="D210" s="4">
         <v>0</v>
@@ -4207,10 +4213,10 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="3">
-        <v>40877</v>
+        <v>40892</v>
       </c>
       <c r="B211" s="4">
-        <v>6.12</v>
+        <v>6.09</v>
       </c>
       <c r="C211" s="4">
         <v>3.48</v>
@@ -4221,13 +4227,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="3">
-        <v>40862</v>
+        <v>40877</v>
       </c>
       <c r="B212" s="4">
-        <v>6.38</v>
+        <v>6.12</v>
       </c>
       <c r="C212" s="4">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="D212" s="4">
         <v>0</v>
@@ -4235,13 +4241,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="3">
-        <v>40847</v>
+        <v>40862</v>
       </c>
       <c r="B213" s="4">
-        <v>6.49</v>
+        <v>6.38</v>
       </c>
       <c r="C213" s="4">
-        <v>3.77</v>
+        <v>3.64</v>
       </c>
       <c r="D213" s="4">
         <v>0</v>
@@ -4249,13 +4255,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="3">
-        <v>40830</v>
+        <v>40847</v>
       </c>
       <c r="B214" s="4">
-        <v>6.66</v>
+        <v>6.49</v>
       </c>
       <c r="C214" s="4">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="D214" s="4">
         <v>0</v>
@@ -4263,13 +4269,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="3">
-        <v>40816</v>
+        <v>40830</v>
       </c>
       <c r="B215" s="4">
-        <v>6.72</v>
+        <v>6.66</v>
       </c>
       <c r="C215" s="4">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="D215" s="4">
         <v>0</v>
@@ -4277,13 +4283,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="3">
-        <v>40801</v>
+        <v>40816</v>
       </c>
       <c r="B216" s="4">
-        <v>6.9</v>
+        <v>6.72</v>
       </c>
       <c r="C216" s="4">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="D216" s="4">
         <v>0</v>
@@ -4291,13 +4297,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="3">
-        <v>40786</v>
+        <v>40801</v>
       </c>
       <c r="B217" s="4">
-        <v>8.06</v>
+        <v>6.9</v>
       </c>
       <c r="C217" s="4">
-        <v>4.48</v>
+        <v>3.8</v>
       </c>
       <c r="D217" s="4">
         <v>0</v>
@@ -4305,13 +4311,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="3">
-        <v>40770</v>
+        <v>40786</v>
       </c>
       <c r="B218" s="4">
         <v>8.06</v>
       </c>
       <c r="C218" s="4">
-        <v>4.35</v>
+        <v>4.48</v>
       </c>
       <c r="D218" s="4">
         <v>0</v>
@@ -4319,13 +4325,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="3">
-        <v>40755</v>
+        <v>40770</v>
       </c>
       <c r="B219" s="4">
-        <v>8.16</v>
+        <v>8.06</v>
       </c>
       <c r="C219" s="4">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="D219" s="4">
         <v>0</v>
@@ -4333,13 +4339,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="3">
-        <v>40694</v>
+        <v>40755</v>
       </c>
       <c r="B220" s="4">
-        <v>9.39</v>
+        <v>8.16</v>
       </c>
       <c r="C220" s="4">
-        <v>4.85</v>
+        <v>4.37</v>
       </c>
       <c r="D220" s="4">
         <v>0</v>
@@ -4347,13 +4353,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="3">
-        <v>40679</v>
+        <v>40694</v>
       </c>
       <c r="B221" s="4">
-        <v>10.28</v>
+        <v>9.39</v>
       </c>
       <c r="C221" s="4">
-        <v>5.76</v>
+        <v>4.85</v>
       </c>
       <c r="D221" s="4">
         <v>0</v>
@@ -4361,13 +4367,13 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="3">
-        <v>40662</v>
+        <v>40679</v>
       </c>
       <c r="B222" s="4">
-        <v>10.4</v>
+        <v>10.28</v>
       </c>
       <c r="C222" s="4">
-        <v>5.98</v>
+        <v>5.76</v>
       </c>
       <c r="D222" s="4">
         <v>0</v>
@@ -4375,13 +4381,13 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="3">
-        <v>40648</v>
+        <v>40662</v>
       </c>
       <c r="B223" s="4">
-        <v>10.64</v>
+        <v>10.4</v>
       </c>
       <c r="C223" s="4">
-        <v>6.1</v>
+        <v>5.98</v>
       </c>
       <c r="D223" s="4">
         <v>0</v>
@@ -4389,13 +4395,13 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="3">
-        <v>40627</v>
+        <v>40648</v>
       </c>
       <c r="B224" s="4">
-        <v>10.42</v>
+        <v>10.64</v>
       </c>
       <c r="C224" s="4">
-        <v>5.92</v>
+        <v>6.1</v>
       </c>
       <c r="D224" s="4">
         <v>0</v>
@@ -4403,13 +4409,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="3">
-        <v>40617</v>
+        <v>40627</v>
       </c>
       <c r="B225" s="4">
-        <v>10.12</v>
+        <v>10.42</v>
       </c>
       <c r="C225" s="4">
-        <v>5.66</v>
+        <v>5.92</v>
       </c>
       <c r="D225" s="4">
         <v>0</v>
@@ -4417,13 +4423,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="3">
-        <v>40599</v>
+        <v>40617</v>
       </c>
       <c r="B226" s="4">
-        <v>9.34</v>
+        <v>10.12</v>
       </c>
       <c r="C226" s="4">
-        <v>5.36</v>
+        <v>5.66</v>
       </c>
       <c r="D226" s="4">
         <v>0</v>
@@ -4431,13 +4437,13 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="3">
-        <v>40590</v>
+        <v>40599</v>
       </c>
       <c r="B227" s="4">
-        <v>9.5</v>
+        <v>9.34</v>
       </c>
       <c r="C227" s="4">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="D227" s="4">
         <v>0</v>
@@ -4445,7 +4451,7 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="3">
-        <v>40570</v>
+        <v>40590</v>
       </c>
       <c r="B228" s="4">
         <v>9.5</v>
@@ -4459,7 +4465,7 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="3">
-        <v>40557</v>
+        <v>40570</v>
       </c>
       <c r="B229" s="4">
         <v>9.5</v>
@@ -4473,13 +4479,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="3">
-        <v>40536</v>
+        <v>40557</v>
       </c>
       <c r="B230" s="4">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="C230" s="4">
-        <v>5.22</v>
+        <v>5.38</v>
       </c>
       <c r="D230" s="4">
         <v>0</v>
@@ -4487,10 +4493,10 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="3">
-        <v>40526</v>
+        <v>40536</v>
       </c>
       <c r="B231" s="4">
-        <v>9.18</v>
+        <v>9.4</v>
       </c>
       <c r="C231" s="4">
         <v>5.22</v>
@@ -4501,13 +4507,13 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="3">
-        <v>40512</v>
+        <v>40526</v>
       </c>
       <c r="B232" s="4">
-        <v>9.1</v>
+        <v>9.18</v>
       </c>
       <c r="C232" s="4">
-        <v>4.98</v>
+        <v>5.22</v>
       </c>
       <c r="D232" s="4">
         <v>0</v>
@@ -4515,13 +4521,13 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="3">
-        <v>40497</v>
+        <v>40512</v>
       </c>
       <c r="B233" s="4">
-        <v>9.2</v>
+        <v>9.1</v>
       </c>
       <c r="C233" s="4">
-        <v>4.93</v>
+        <v>4.98</v>
       </c>
       <c r="D233" s="4">
         <v>0</v>
@@ -4529,13 +4535,13 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="3">
-        <v>40480</v>
+        <v>40497</v>
       </c>
       <c r="B234" s="4">
-        <v>9.92</v>
+        <v>9.2</v>
       </c>
       <c r="C234" s="4">
-        <v>5.17</v>
+        <v>4.93</v>
       </c>
       <c r="D234" s="4">
         <v>0</v>
@@ -4543,13 +4549,13 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="3">
-        <v>40466</v>
+        <v>40480</v>
       </c>
       <c r="B235" s="4">
-        <v>10.08</v>
+        <v>9.92</v>
       </c>
       <c r="C235" s="4">
-        <v>5.23</v>
+        <v>5.17</v>
       </c>
       <c r="D235" s="4">
         <v>0</v>
@@ -4557,13 +4563,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="3">
-        <v>40451</v>
+        <v>40466</v>
       </c>
       <c r="B236" s="4">
-        <v>10.68</v>
+        <v>10.08</v>
       </c>
       <c r="C236" s="4">
-        <v>5.27</v>
+        <v>5.23</v>
       </c>
       <c r="D236" s="4">
         <v>0</v>
@@ -4571,13 +4577,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="3">
-        <v>40436</v>
+        <v>40451</v>
       </c>
       <c r="B237" s="4">
-        <v>11.78</v>
+        <v>10.68</v>
       </c>
       <c r="C237" s="4">
-        <v>5.57</v>
+        <v>5.27</v>
       </c>
       <c r="D237" s="4">
         <v>0</v>
@@ -4585,13 +4591,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="3">
-        <v>40421</v>
+        <v>40436</v>
       </c>
       <c r="B238" s="4">
-        <v>12.72</v>
+        <v>11.78</v>
       </c>
       <c r="C238" s="4">
-        <v>5.92</v>
+        <v>5.57</v>
       </c>
       <c r="D238" s="4">
         <v>0</v>
@@ -4599,13 +4605,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="3">
-        <v>40403</v>
+        <v>40421</v>
       </c>
       <c r="B239" s="4">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="C239" s="4">
-        <v>6.36</v>
+        <v>5.92</v>
       </c>
       <c r="D239" s="4">
         <v>0</v>
@@ -4613,13 +4619,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="3">
-        <v>40389</v>
+        <v>40403</v>
       </c>
       <c r="B240" s="4">
-        <v>13.82</v>
+        <v>13.56</v>
       </c>
       <c r="C240" s="4">
-        <v>6.44</v>
+        <v>6.36</v>
       </c>
       <c r="D240" s="4">
         <v>0</v>
@@ -4627,13 +4633,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="3">
-        <v>40368</v>
+        <v>40389</v>
       </c>
       <c r="B241" s="4">
         <v>13.82</v>
       </c>
       <c r="C241" s="4">
-        <v>6.58</v>
+        <v>6.44</v>
       </c>
       <c r="D241" s="4">
         <v>0</v>
@@ -4641,13 +4647,13 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="3">
-        <v>40354</v>
+        <v>40368</v>
       </c>
       <c r="B242" s="4">
         <v>13.82</v>
       </c>
       <c r="C242" s="4">
-        <v>6.67</v>
+        <v>6.58</v>
       </c>
       <c r="D242" s="4">
         <v>0</v>
@@ -4655,13 +4661,13 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="3">
-        <v>40339</v>
+        <v>40354</v>
       </c>
       <c r="B243" s="4">
-        <v>14.36</v>
+        <v>13.82</v>
       </c>
       <c r="C243" s="4">
-        <v>7.07</v>
+        <v>6.67</v>
       </c>
       <c r="D243" s="4">
         <v>0</v>
@@ -4669,13 +4675,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="3">
-        <v>40323</v>
+        <v>40339</v>
       </c>
       <c r="B244" s="4">
-        <v>15.16</v>
+        <v>14.36</v>
       </c>
       <c r="C244" s="4">
-        <v>7.19</v>
+        <v>7.07</v>
       </c>
       <c r="D244" s="4">
         <v>0</v>
@@ -4683,13 +4689,13 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="3">
-        <v>40308</v>
+        <v>40323</v>
       </c>
       <c r="B245" s="4">
         <v>15.16</v>
       </c>
       <c r="C245" s="4">
-        <v>7.29</v>
+        <v>7.19</v>
       </c>
       <c r="D245" s="4">
         <v>0</v>
@@ -4697,13 +4703,13 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="3">
-        <v>40291</v>
+        <v>40308</v>
       </c>
       <c r="B246" s="4">
-        <v>15.34</v>
+        <v>15.16</v>
       </c>
       <c r="C246" s="4">
-        <v>7.42</v>
+        <v>7.29</v>
       </c>
       <c r="D246" s="4">
         <v>0</v>
@@ -4711,13 +4717,13 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="3">
-        <v>40275</v>
+        <v>40291</v>
       </c>
       <c r="B247" s="4">
-        <v>15.38</v>
+        <v>15.34</v>
       </c>
       <c r="C247" s="4">
-        <v>7.54</v>
+        <v>7.42</v>
       </c>
       <c r="D247" s="4">
         <v>0</v>
@@ -4725,13 +4731,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="3">
-        <v>40261</v>
+        <v>40275</v>
       </c>
       <c r="B248" s="4">
-        <v>15.34</v>
+        <v>15.38</v>
       </c>
       <c r="C248" s="4">
-        <v>7.04</v>
+        <v>7.54</v>
       </c>
       <c r="D248" s="4">
         <v>0</v>
@@ -4739,13 +4745,13 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="3">
-        <v>40247</v>
+        <v>40261</v>
       </c>
       <c r="B249" s="4">
-        <v>15.18</v>
+        <v>15.34</v>
       </c>
       <c r="C249" s="4">
-        <v>7.12</v>
+        <v>7.04</v>
       </c>
       <c r="D249" s="4">
         <v>0</v>
@@ -4753,13 +4759,13 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="3">
-        <v>40234</v>
+        <v>40247</v>
       </c>
       <c r="B250" s="4">
-        <v>15.26</v>
+        <v>15.18</v>
       </c>
       <c r="C250" s="4">
-        <v>7.18</v>
+        <v>7.12</v>
       </c>
       <c r="D250" s="4">
         <v>0</v>
@@ -4767,13 +4773,13 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="3">
-        <v>40214</v>
+        <v>40234</v>
       </c>
       <c r="B251" s="4">
-        <v>15.34</v>
+        <v>15.26</v>
       </c>
       <c r="C251" s="4">
-        <v>7.22</v>
+        <v>7.18</v>
       </c>
       <c r="D251" s="4">
         <v>0</v>
@@ -4781,13 +4787,13 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="3">
-        <v>40200</v>
+        <v>40214</v>
       </c>
       <c r="B252" s="4">
-        <v>15.5</v>
+        <v>15.34</v>
       </c>
       <c r="C252" s="4">
-        <v>7.24</v>
+        <v>7.22</v>
       </c>
       <c r="D252" s="4">
         <v>0</v>
@@ -4795,13 +4801,13 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="3">
-        <v>40185</v>
+        <v>40200</v>
       </c>
       <c r="B253" s="4">
-        <v>15.1</v>
+        <v>15.5</v>
       </c>
       <c r="C253" s="4">
-        <v>7.18</v>
+        <v>7.24</v>
       </c>
       <c r="D253" s="4">
         <v>0</v>
@@ -4809,10 +4815,10 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="3">
-        <v>40169</v>
+        <v>40185</v>
       </c>
       <c r="B254" s="4">
-        <v>15.14</v>
+        <v>15.1</v>
       </c>
       <c r="C254" s="4">
         <v>7.18</v>
@@ -4823,13 +4829,13 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="3">
-        <v>40156</v>
+        <v>40169</v>
       </c>
       <c r="B255" s="4">
         <v>15.14</v>
       </c>
       <c r="C255" s="4">
-        <v>7.26</v>
+        <v>7.18</v>
       </c>
       <c r="D255" s="4">
         <v>0</v>
@@ -4837,13 +4843,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="3">
-        <v>40141</v>
+        <v>40156</v>
       </c>
       <c r="B256" s="4">
-        <v>15.72</v>
+        <v>15.14</v>
       </c>
       <c r="C256" s="4">
-        <v>7.72</v>
+        <v>7.26</v>
       </c>
       <c r="D256" s="4">
         <v>0</v>
@@ -4851,13 +4857,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="3">
-        <v>40126</v>
+        <v>40141</v>
       </c>
       <c r="B257" s="4">
         <v>15.72</v>
       </c>
       <c r="C257" s="4">
-        <v>8</v>
+        <v>7.72</v>
       </c>
       <c r="D257" s="4">
         <v>0</v>
@@ -4865,13 +4871,13 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="3">
-        <v>40108</v>
+        <v>40126</v>
       </c>
       <c r="B258" s="4">
-        <v>15.26</v>
+        <v>15.72</v>
       </c>
       <c r="C258" s="4">
-        <v>8.12</v>
+        <v>8</v>
       </c>
       <c r="D258" s="4">
         <v>0</v>
@@ -4879,13 +4885,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="3">
-        <v>40094</v>
+        <v>40108</v>
       </c>
       <c r="B259" s="4">
-        <v>14.5</v>
+        <v>15.26</v>
       </c>
       <c r="C259" s="4">
-        <v>7.68</v>
+        <v>8.12</v>
       </c>
       <c r="D259" s="4">
         <v>0</v>
@@ -4893,13 +4899,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="3">
-        <v>40078</v>
+        <v>40094</v>
       </c>
       <c r="B260" s="4">
-        <v>13.48</v>
+        <v>14.5</v>
       </c>
       <c r="C260" s="4">
-        <v>6.98</v>
+        <v>7.68</v>
       </c>
       <c r="D260" s="4">
         <v>0</v>
@@ -4907,13 +4913,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="3">
-        <v>40064</v>
+        <v>40078</v>
       </c>
       <c r="B261" s="4">
-        <v>13.36</v>
+        <v>13.48</v>
       </c>
       <c r="C261" s="4">
-        <v>6.8</v>
+        <v>6.98</v>
       </c>
       <c r="D261" s="4">
         <v>0</v>
@@ -4921,13 +4927,13 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="3">
-        <v>40049</v>
+        <v>40064</v>
       </c>
       <c r="B262" s="4">
-        <v>13</v>
+        <v>13.36</v>
       </c>
       <c r="C262" s="4">
-        <v>6.52</v>
+        <v>6.8</v>
       </c>
       <c r="D262" s="4">
         <v>0</v>
@@ -4935,7 +4941,7 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="3">
-        <v>40031</v>
+        <v>40049</v>
       </c>
       <c r="B263" s="4">
         <v>13</v>
@@ -4949,10 +4955,10 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="3">
-        <v>40016</v>
+        <v>40031</v>
       </c>
       <c r="B264" s="4">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="C264" s="4">
         <v>6.52</v>
@@ -4963,13 +4969,13 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="3">
-        <v>40002</v>
+        <v>40016</v>
       </c>
       <c r="B265" s="4">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="C265" s="4">
-        <v>6.64</v>
+        <v>6.52</v>
       </c>
       <c r="D265" s="4">
         <v>0</v>
@@ -4977,13 +4983,13 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="3">
-        <v>39987</v>
+        <v>40002</v>
       </c>
       <c r="B266" s="4">
-        <v>13.36</v>
+        <v>13.3</v>
       </c>
       <c r="C266" s="4">
-        <v>7</v>
+        <v>6.64</v>
       </c>
       <c r="D266" s="4">
         <v>0</v>
@@ -4991,10 +4997,10 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="3">
-        <v>39972</v>
+        <v>39987</v>
       </c>
       <c r="B267" s="4">
-        <v>14</v>
+        <v>13.36</v>
       </c>
       <c r="C267" s="4">
         <v>7</v>
@@ -5005,13 +5011,13 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="3">
-        <v>39955</v>
+        <v>39972</v>
       </c>
       <c r="B268" s="4">
-        <v>14.26</v>
+        <v>14</v>
       </c>
       <c r="C268" s="4">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="D268" s="4">
         <v>0</v>
@@ -5019,13 +5025,13 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="3">
-        <v>39941</v>
+        <v>39955</v>
       </c>
       <c r="B269" s="4">
-        <v>14.86</v>
+        <v>14.26</v>
       </c>
       <c r="C269" s="4">
-        <v>7.56</v>
+        <v>7.08</v>
       </c>
       <c r="D269" s="4">
         <v>0</v>
@@ -5033,13 +5039,13 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="3">
-        <v>39926</v>
+        <v>39941</v>
       </c>
       <c r="B270" s="4">
         <v>14.86</v>
       </c>
       <c r="C270" s="4">
-        <v>7.4</v>
+        <v>7.56</v>
       </c>
       <c r="D270" s="4">
         <v>0</v>
@@ -5047,13 +5053,13 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="3">
-        <v>39910</v>
+        <v>39926</v>
       </c>
       <c r="B271" s="4">
-        <v>12.58</v>
+        <v>14.86</v>
       </c>
       <c r="C271" s="4">
-        <v>6.44</v>
+        <v>7.4</v>
       </c>
       <c r="D271" s="4">
         <v>0</v>
@@ -5061,13 +5067,13 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="3">
-        <v>39896</v>
+        <v>39910</v>
       </c>
       <c r="B272" s="4">
-        <v>12.16</v>
+        <v>12.58</v>
       </c>
       <c r="C272" s="4">
-        <v>5.88</v>
+        <v>6.44</v>
       </c>
       <c r="D272" s="4">
         <v>0</v>
@@ -5075,13 +5081,13 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="3">
-        <v>39881</v>
+        <v>39896</v>
       </c>
       <c r="B273" s="4">
         <v>12.16</v>
       </c>
       <c r="C273" s="4">
-        <v>5.98</v>
+        <v>5.88</v>
       </c>
       <c r="D273" s="4">
         <v>0</v>
@@ -5089,10 +5095,10 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="3">
-        <v>39864</v>
+        <v>39881</v>
       </c>
       <c r="B274" s="4">
-        <v>12</v>
+        <v>12.16</v>
       </c>
       <c r="C274" s="4">
         <v>5.98</v>
@@ -5103,13 +5109,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="3">
-        <v>39850</v>
+        <v>39864</v>
       </c>
       <c r="B275" s="4">
-        <v>9.96</v>
+        <v>12</v>
       </c>
       <c r="C275" s="4">
-        <v>5</v>
+        <v>5.98</v>
       </c>
       <c r="D275" s="4">
         <v>0</v>
@@ -5117,13 +5123,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="3">
-        <v>39828</v>
+        <v>39850</v>
       </c>
       <c r="B276" s="4">
-        <v>9.02</v>
+        <v>9.96</v>
       </c>
       <c r="C276" s="4">
-        <v>4.74</v>
+        <v>5</v>
       </c>
       <c r="D276" s="4">
         <v>0</v>
@@ -5131,13 +5137,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="3">
-        <v>39820</v>
+        <v>39828</v>
       </c>
       <c r="B277" s="4">
-        <v>8.52</v>
+        <v>9.02</v>
       </c>
       <c r="C277" s="4">
-        <v>4.11</v>
+        <v>4.74</v>
       </c>
       <c r="D277" s="4">
         <v>0</v>
@@ -5145,13 +5151,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="3">
-        <v>39806</v>
+        <v>39820</v>
       </c>
       <c r="B278" s="4">
-        <v>9.5</v>
+        <v>8.52</v>
       </c>
       <c r="C278" s="4">
-        <v>3.72</v>
+        <v>4.11</v>
       </c>
       <c r="D278" s="4">
         <v>0</v>
@@ -5159,13 +5165,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="3">
-        <v>39791</v>
+        <v>39806</v>
       </c>
       <c r="B279" s="4">
-        <v>9.42</v>
+        <v>9.5</v>
       </c>
       <c r="C279" s="4">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="D279" s="4">
         <v>0</v>
@@ -5173,13 +5179,13 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="3">
-        <v>39776</v>
+        <v>39791</v>
       </c>
       <c r="B280" s="4">
-        <v>10.84</v>
+        <v>9.42</v>
       </c>
       <c r="C280" s="4">
-        <v>4.85</v>
+        <v>3.62</v>
       </c>
       <c r="D280" s="4">
         <v>0</v>
@@ -5187,7 +5193,7 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="3">
-        <v>39762</v>
+        <v>39776</v>
       </c>
       <c r="B281" s="4">
         <v>10.84</v>
@@ -5201,13 +5207,13 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" s="3">
-        <v>39744</v>
+        <v>39762</v>
       </c>
       <c r="B282" s="4">
-        <v>11.6</v>
+        <v>10.84</v>
       </c>
       <c r="C282" s="4">
-        <v>5.36</v>
+        <v>4.85</v>
       </c>
       <c r="D282" s="4">
         <v>0</v>
@@ -5215,7 +5221,7 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" s="3">
-        <v>39729</v>
+        <v>39744</v>
       </c>
       <c r="B283" s="4">
         <v>11.6</v>
@@ -5229,13 +5235,13 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" s="3">
-        <v>39713</v>
+        <v>39729</v>
       </c>
       <c r="B284" s="4">
-        <v>12.38</v>
+        <v>11.6</v>
       </c>
       <c r="C284" s="4">
-        <v>5.53</v>
+        <v>5.36</v>
       </c>
       <c r="D284" s="4">
         <v>0</v>
@@ -5243,13 +5249,13 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="3">
-        <v>39700</v>
+        <v>39713</v>
       </c>
       <c r="B285" s="4">
-        <v>13.44</v>
+        <v>12.38</v>
       </c>
       <c r="C285" s="4">
-        <v>6.36</v>
+        <v>5.53</v>
       </c>
       <c r="D285" s="4">
         <v>0</v>
@@ -5257,13 +5263,13 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="3">
-        <v>39682</v>
+        <v>39700</v>
       </c>
       <c r="B286" s="4">
-        <v>15</v>
+        <v>13.44</v>
       </c>
       <c r="C286" s="4">
-        <v>7.36</v>
+        <v>6.36</v>
       </c>
       <c r="D286" s="4">
         <v>0</v>
@@ -5271,13 +5277,13 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" s="3">
-        <v>39667</v>
+        <v>39682</v>
       </c>
       <c r="B287" s="4">
-        <v>16.18</v>
+        <v>15</v>
       </c>
       <c r="C287" s="4">
-        <v>7.98</v>
+        <v>7.36</v>
       </c>
       <c r="D287" s="4">
         <v>0</v>
@@ -5285,13 +5291,13 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="3">
-        <v>39652</v>
+        <v>39667</v>
       </c>
       <c r="B288" s="4">
-        <v>18.54</v>
+        <v>16.18</v>
       </c>
       <c r="C288" s="4">
-        <v>9.04</v>
+        <v>7.98</v>
       </c>
       <c r="D288" s="4">
         <v>0</v>
@@ -5299,13 +5305,13 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="3">
-        <v>39636</v>
+        <v>39652</v>
       </c>
       <c r="B289" s="4">
-        <v>19.02</v>
+        <v>18.54</v>
       </c>
       <c r="C289" s="4">
-        <v>9.18</v>
+        <v>9.04</v>
       </c>
       <c r="D289" s="4">
         <v>0</v>
@@ -5313,13 +5319,13 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" s="3">
-        <v>39624</v>
+        <v>39636</v>
       </c>
       <c r="B290" s="4">
-        <v>20.5</v>
+        <v>19.02</v>
       </c>
       <c r="C290" s="4">
-        <v>9.64</v>
+        <v>9.18</v>
       </c>
       <c r="D290" s="4">
         <v>0</v>
@@ -5327,13 +5333,13 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" s="3">
-        <v>39605</v>
+        <v>39624</v>
       </c>
       <c r="B291" s="4">
-        <v>22.7</v>
+        <v>20.5</v>
       </c>
       <c r="C291" s="4">
-        <v>11.16</v>
+        <v>9.64</v>
       </c>
       <c r="D291" s="4">
         <v>0</v>
@@ -5341,13 +5347,13 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" s="3">
-        <v>39591</v>
+        <v>39605</v>
       </c>
       <c r="B292" s="4">
-        <v>23.9</v>
+        <v>22.7</v>
       </c>
       <c r="C292" s="4">
-        <v>11.46</v>
+        <v>11.16</v>
       </c>
       <c r="D292" s="4">
         <v>0</v>
@@ -5355,13 +5361,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" s="3">
-        <v>39576</v>
+        <v>39591</v>
       </c>
       <c r="B293" s="4">
-        <v>24.96</v>
+        <v>23.9</v>
       </c>
       <c r="C293" s="4">
-        <v>11.92</v>
+        <v>11.46</v>
       </c>
       <c r="D293" s="4">
         <v>0</v>
@@ -5369,13 +5375,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" s="3">
-        <v>39561</v>
+        <v>39576</v>
       </c>
       <c r="B294" s="4">
-        <v>25.08</v>
+        <v>24.96</v>
       </c>
       <c r="C294" s="4">
-        <v>11.94</v>
+        <v>11.92</v>
       </c>
       <c r="D294" s="4">
         <v>0</v>
@@ -5383,13 +5389,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" s="3">
-        <v>39549</v>
+        <v>39561</v>
       </c>
       <c r="B295" s="4">
-        <v>26</v>
+        <v>25.08</v>
       </c>
       <c r="C295" s="4">
-        <v>11.76</v>
+        <v>11.94</v>
       </c>
       <c r="D295" s="4">
         <v>0</v>
@@ -5397,13 +5403,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" s="3">
-        <v>39533</v>
+        <v>39549</v>
       </c>
       <c r="B296" s="4">
-        <v>24.76</v>
+        <v>26</v>
       </c>
       <c r="C296" s="4">
-        <v>11.1</v>
+        <v>11.76</v>
       </c>
       <c r="D296" s="4">
         <v>0</v>
@@ -5411,13 +5417,13 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" s="3">
-        <v>39517</v>
+        <v>39533</v>
       </c>
       <c r="B297" s="4">
-        <v>25.3</v>
+        <v>24.76</v>
       </c>
       <c r="C297" s="4">
-        <v>11.32</v>
+        <v>11.1</v>
       </c>
       <c r="D297" s="4">
         <v>0</v>
@@ -5425,13 +5431,13 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" s="3">
-        <v>39503</v>
+        <v>39517</v>
       </c>
       <c r="B298" s="4">
         <v>25.3</v>
       </c>
       <c r="C298" s="4">
-        <v>11.7</v>
+        <v>11.32</v>
       </c>
       <c r="D298" s="4">
         <v>0</v>
@@ -5439,13 +5445,13 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" s="3">
-        <v>39483</v>
+        <v>39503</v>
       </c>
       <c r="B299" s="4">
-        <v>26.16</v>
+        <v>25.3</v>
       </c>
       <c r="C299" s="4">
-        <v>12.12</v>
+        <v>11.7</v>
       </c>
       <c r="D299" s="4">
         <v>0</v>
@@ -5453,7 +5459,7 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" s="3">
-        <v>39469</v>
+        <v>39483</v>
       </c>
       <c r="B300" s="4">
         <v>26.16</v>
@@ -5467,7 +5473,7 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" s="3">
-        <v>39456</v>
+        <v>39469</v>
       </c>
       <c r="B301" s="4">
         <v>26.16</v>
@@ -5476,6 +5482,20 @@
         <v>12.12</v>
       </c>
       <c r="D301" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="5">
+        <v>39456</v>
+      </c>
+      <c r="B302" s="6">
+        <v>26.16</v>
+      </c>
+      <c r="C302" s="6">
+        <v>12.12</v>
+      </c>
+      <c r="D302" s="6">
         <v>0</v>
       </c>
     </row>

--- a/edb_data/NAND合约平均价格.xlsx
+++ b/edb_data/NAND合约平均价格.xlsx
@@ -699,19 +699,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -5486,16 +5480,16 @@
       </c>
     </row>
     <row r="302" spans="1:4">
-      <c r="A302" s="5">
+      <c r="A302" s="3">
         <v>39456</v>
       </c>
-      <c r="B302" s="6">
+      <c r="B302" s="4">
         <v>26.16</v>
       </c>
-      <c r="C302" s="6">
+      <c r="C302" s="4">
         <v>12.12</v>
       </c>
-      <c r="D302" s="6">
+      <c r="D302" s="4">
         <v>0</v>
       </c>
     </row>

--- a/edb_data/NAND合约平均价格.xlsx
+++ b/edb_data/NAND合约平均价格.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="27948" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="合约平均价_NAND Flash(64G" sheetId="1" r:id="rId1"/>

--- a/edb_data/NAND合约平均价格.xlsx
+++ b/edb_data/NAND合约平均价格.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codex\存储行业可视化看板网站制作\edb_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300"/>
+    <workbookView windowWidth="24048" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="合约平均价_NAND Flash(64G" sheetId="1" r:id="rId1"/>
@@ -699,13 +704,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1266,7 +1277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D302"/>
+  <dimension ref="A1:D303"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.8888888888889"/>
@@ -1295,259 +1306,259 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B3" s="4">
-        <v>21.365</v>
+        <v>23.11</v>
       </c>
       <c r="C3" s="4">
-        <v>17.075</v>
+        <v>17.865</v>
       </c>
       <c r="D3" s="4">
-        <v>28.82</v>
+        <v>30.048</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3">
-        <v>46171</v>
+        <v>46203</v>
       </c>
       <c r="B4" s="4">
-        <v>19.165</v>
+        <v>21.365</v>
       </c>
       <c r="C4" s="4">
-        <v>15.493</v>
+        <v>17.075</v>
       </c>
       <c r="D4" s="4">
-        <v>26.508</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3">
-        <v>46142</v>
+        <v>46171</v>
       </c>
       <c r="B5" s="4">
-        <v>17.325</v>
+        <v>19.165</v>
       </c>
       <c r="C5" s="4">
-        <v>14.1</v>
+        <v>15.493</v>
       </c>
       <c r="D5" s="4">
-        <v>24.158</v>
+        <v>26.508</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B6" s="4">
-        <v>12.713</v>
+        <v>17.325</v>
       </c>
       <c r="C6" s="4">
-        <v>10.45</v>
+        <v>14.1</v>
       </c>
       <c r="D6" s="4">
-        <v>17.725</v>
+        <v>24.158</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3">
-        <v>46079</v>
+        <v>46112</v>
       </c>
       <c r="B7" s="4">
-        <v>8.513</v>
+        <v>12.713</v>
       </c>
       <c r="C7" s="4">
-        <v>7.208</v>
+        <v>10.45</v>
       </c>
       <c r="D7" s="4">
-        <v>12.665</v>
+        <v>17.725</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="B8" s="4">
-        <v>7.023</v>
+        <v>8.513</v>
       </c>
       <c r="C8" s="4">
-        <v>5.57</v>
+        <v>7.208</v>
       </c>
       <c r="D8" s="4">
-        <v>9.458</v>
+        <v>12.665</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="B9" s="4">
-        <v>4.59</v>
+        <v>7.023</v>
       </c>
       <c r="C9" s="4">
-        <v>3.66</v>
+        <v>5.57</v>
       </c>
       <c r="D9" s="4">
-        <v>5.738</v>
+        <v>9.458</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="B10" s="4">
-        <v>4.02</v>
+        <v>4.59</v>
       </c>
       <c r="C10" s="4">
-        <v>3.295</v>
+        <v>3.66</v>
       </c>
       <c r="D10" s="4">
-        <v>5.19</v>
+        <v>5.738</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3">
-        <v>45961</v>
+        <v>45989</v>
       </c>
       <c r="B11" s="4">
-        <v>3.333</v>
+        <v>4.02</v>
       </c>
       <c r="C11" s="4">
-        <v>2.795</v>
+        <v>3.295</v>
       </c>
       <c r="D11" s="4">
-        <v>4.35</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B12" s="4">
-        <v>2.825</v>
+        <v>3.333</v>
       </c>
       <c r="C12" s="4">
-        <v>2.39</v>
+        <v>2.795</v>
       </c>
       <c r="D12" s="4">
-        <v>3.785</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3">
-        <v>45898</v>
+        <v>45930</v>
       </c>
       <c r="B13" s="4">
-        <v>2.44</v>
+        <v>2.825</v>
       </c>
       <c r="C13" s="4">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="D13" s="4">
-        <v>3.423</v>
+        <v>3.785</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3">
-        <v>45869</v>
+        <v>45898</v>
       </c>
       <c r="B14" s="4">
-        <v>2.408</v>
+        <v>2.44</v>
       </c>
       <c r="C14" s="4">
-        <v>2.035</v>
+        <v>2.05</v>
       </c>
       <c r="D14" s="4">
-        <v>3.385</v>
+        <v>3.423</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B15" s="4">
-        <v>2.23</v>
+        <v>2.408</v>
       </c>
       <c r="C15" s="4">
-        <v>1.878</v>
+        <v>2.035</v>
       </c>
       <c r="D15" s="4">
-        <v>3.115</v>
+        <v>3.385</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3">
-        <v>45806</v>
+        <v>45838</v>
       </c>
       <c r="B16" s="4">
-        <v>2.028</v>
+        <v>2.23</v>
       </c>
       <c r="C16" s="4">
-        <v>1.74</v>
+        <v>1.878</v>
       </c>
       <c r="D16" s="4">
-        <v>2.923</v>
+        <v>3.115</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3">
-        <v>45777</v>
+        <v>45806</v>
       </c>
       <c r="B17" s="4">
-        <v>1.925</v>
+        <v>2.028</v>
       </c>
       <c r="C17" s="4">
-        <v>1.655</v>
+        <v>1.74</v>
       </c>
       <c r="D17" s="4">
-        <v>2.788</v>
+        <v>2.923</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B18" s="4">
-        <v>0</v>
+        <v>1.925</v>
       </c>
       <c r="C18" s="4">
-        <v>1.455</v>
+        <v>1.655</v>
       </c>
       <c r="D18" s="4">
-        <v>2.51</v>
+        <v>2.788</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3">
-        <v>45715</v>
+        <v>45747</v>
       </c>
       <c r="B19" s="4">
         <v>0</v>
       </c>
       <c r="C19" s="4">
-        <v>1.318</v>
+        <v>1.455</v>
       </c>
       <c r="D19" s="4">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3">
-        <v>45681</v>
+        <v>45715</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
       </c>
       <c r="C20" s="4">
-        <v>0</v>
+        <v>1.318</v>
       </c>
       <c r="D20" s="4">
-        <v>2.175</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3">
-        <v>45657</v>
+        <v>45681</v>
       </c>
       <c r="B21" s="4">
         <v>0</v>
@@ -1556,12 +1567,12 @@
         <v>0</v>
       </c>
       <c r="D21" s="4">
-        <v>2.08</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="3">
-        <v>45625</v>
+        <v>45657</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -1570,54 +1581,54 @@
         <v>0</v>
       </c>
       <c r="D22" s="4">
-        <v>2.155</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="3">
-        <v>45596</v>
+        <v>45625</v>
       </c>
       <c r="B23" s="4">
-        <v>2.388</v>
+        <v>0</v>
       </c>
       <c r="C23" s="4">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4">
-        <v>3.07</v>
+        <v>2.155</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="3">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B24" s="4">
-        <v>2.985</v>
+        <v>2.388</v>
       </c>
       <c r="C24" s="4">
-        <v>2.349</v>
+        <v>1.81</v>
       </c>
       <c r="D24" s="4">
-        <v>4.335</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="3">
-        <v>45534</v>
+        <v>45565</v>
       </c>
       <c r="B25" s="4">
-        <v>3.385</v>
+        <v>2.985</v>
       </c>
       <c r="C25" s="4">
-        <v>2.604</v>
+        <v>2.349</v>
       </c>
       <c r="D25" s="4">
-        <v>4.895</v>
+        <v>4.335</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="3">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B26" s="4">
         <v>3.385</v>
@@ -1631,7 +1642,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="3">
-        <v>45471</v>
+        <v>45504</v>
       </c>
       <c r="B27" s="4">
         <v>3.385</v>
@@ -1645,7 +1656,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="3">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B28" s="4">
         <v>3.385</v>
@@ -1659,7 +1670,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="3">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B29" s="4">
         <v>3.385</v>
@@ -1673,7 +1684,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="3">
-        <v>45380</v>
+        <v>45412</v>
       </c>
       <c r="B30" s="4">
         <v>3.385</v>
@@ -1687,7 +1698,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="3">
-        <v>45351</v>
+        <v>45380</v>
       </c>
       <c r="B31" s="4">
         <v>3.385</v>
@@ -1701,77 +1712,77 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B32" s="4">
-        <v>3.278</v>
+        <v>3.385</v>
       </c>
       <c r="C32" s="4">
         <v>2.604</v>
       </c>
       <c r="D32" s="4">
-        <v>4.715</v>
+        <v>4.895</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="3">
-        <v>45289</v>
+        <v>45322</v>
       </c>
       <c r="B33" s="4">
-        <v>3.02</v>
+        <v>3.278</v>
       </c>
       <c r="C33" s="4">
-        <v>2.57</v>
+        <v>2.604</v>
       </c>
       <c r="D33" s="4">
-        <v>4.331</v>
+        <v>4.715</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3">
-        <v>45260</v>
+        <v>45289</v>
       </c>
       <c r="B34" s="4">
-        <v>2.915</v>
+        <v>3.02</v>
       </c>
       <c r="C34" s="4">
-        <v>2.516</v>
+        <v>2.57</v>
       </c>
       <c r="D34" s="4">
-        <v>4.085</v>
+        <v>4.331</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B35" s="4">
-        <v>2.794</v>
+        <v>2.915</v>
       </c>
       <c r="C35" s="4">
-        <v>2.469</v>
+        <v>2.516</v>
       </c>
       <c r="D35" s="4">
-        <v>3.876</v>
+        <v>4.085</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3">
-        <v>45197</v>
+        <v>45230</v>
       </c>
       <c r="B36" s="4">
-        <v>2.76</v>
+        <v>2.794</v>
       </c>
       <c r="C36" s="4">
-        <v>2.433</v>
+        <v>2.469</v>
       </c>
       <c r="D36" s="4">
-        <v>3.815</v>
+        <v>3.876</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3">
-        <v>45169</v>
+        <v>45197</v>
       </c>
       <c r="B37" s="4">
         <v>2.76</v>
@@ -1785,7 +1796,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B38" s="4">
         <v>2.76</v>
@@ -1799,7 +1810,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B39" s="4">
         <v>2.76</v>
@@ -1813,7 +1824,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B40" s="4">
         <v>2.76</v>
@@ -1827,7 +1838,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3">
-        <v>45044</v>
+        <v>45077</v>
       </c>
       <c r="B41" s="4">
         <v>2.76</v>
@@ -1841,35 +1852,35 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="3">
-        <v>45016</v>
+        <v>45044</v>
       </c>
       <c r="B42" s="4">
-        <v>2.838</v>
+        <v>2.76</v>
       </c>
       <c r="C42" s="4">
-        <v>2.461</v>
+        <v>2.433</v>
       </c>
       <c r="D42" s="4">
-        <v>3.93</v>
+        <v>3.815</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="3">
-        <v>44981</v>
+        <v>45016</v>
       </c>
       <c r="B43" s="4">
-        <v>2.983</v>
+        <v>2.838</v>
       </c>
       <c r="C43" s="4">
-        <v>2.587</v>
+        <v>2.461</v>
       </c>
       <c r="D43" s="4">
-        <v>4.142</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3">
-        <v>44957</v>
+        <v>44981</v>
       </c>
       <c r="B44" s="4">
         <v>2.983</v>
@@ -1883,7 +1894,7 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="3">
-        <v>44925</v>
+        <v>44957</v>
       </c>
       <c r="B45" s="4">
         <v>2.983</v>
@@ -1897,10 +1908,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="3">
-        <v>44895</v>
+        <v>44925</v>
       </c>
       <c r="B46" s="4">
-        <v>2.998</v>
+        <v>2.983</v>
       </c>
       <c r="C46" s="4">
         <v>2.587</v>
@@ -1911,7 +1922,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="3">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B47" s="4">
         <v>2.998</v>
@@ -1925,77 +1936,77 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="3">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B48" s="4">
-        <v>3.105</v>
+        <v>2.998</v>
       </c>
       <c r="C48" s="4">
-        <v>2.685</v>
+        <v>2.587</v>
       </c>
       <c r="D48" s="4">
-        <v>4.303</v>
+        <v>4.142</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="3">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B49" s="4">
-        <v>3.173</v>
+        <v>3.105</v>
       </c>
       <c r="C49" s="4">
-        <v>2.74</v>
+        <v>2.685</v>
       </c>
       <c r="D49" s="4">
-        <v>4.415</v>
+        <v>4.303</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="3">
-        <v>44771</v>
+        <v>44804</v>
       </c>
       <c r="B50" s="4">
-        <v>3.223</v>
+        <v>3.173</v>
       </c>
       <c r="C50" s="4">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="D50" s="4">
-        <v>4.49</v>
+        <v>4.415</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="3">
-        <v>44742</v>
+        <v>44771</v>
       </c>
       <c r="B51" s="4">
-        <v>3.337</v>
+        <v>3.223</v>
       </c>
       <c r="C51" s="4">
-        <v>2.855</v>
+        <v>2.79</v>
       </c>
       <c r="D51" s="4">
-        <v>4.665</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="3">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B52" s="4">
-        <v>3.44</v>
+        <v>3.337</v>
       </c>
       <c r="C52" s="4">
-        <v>3</v>
+        <v>2.855</v>
       </c>
       <c r="D52" s="4">
-        <v>4.81</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="3">
-        <v>44680</v>
+        <v>44712</v>
       </c>
       <c r="B53" s="4">
         <v>3.44</v>
@@ -2009,7 +2020,7 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="3">
-        <v>44651</v>
+        <v>44680</v>
       </c>
       <c r="B54" s="4">
         <v>3.44</v>
@@ -2023,7 +2034,7 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="3">
-        <v>44617</v>
+        <v>44651</v>
       </c>
       <c r="B55" s="4">
         <v>3.44</v>
@@ -2037,7 +2048,7 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="3">
-        <v>44589</v>
+        <v>44617</v>
       </c>
       <c r="B56" s="4">
         <v>3.44</v>
@@ -2051,7 +2062,7 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="3">
-        <v>44560</v>
+        <v>44589</v>
       </c>
       <c r="B57" s="4">
         <v>3.44</v>
@@ -2065,7 +2076,7 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="3">
-        <v>44530</v>
+        <v>44560</v>
       </c>
       <c r="B58" s="4">
         <v>3.44</v>
@@ -2079,7 +2090,7 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="3">
-        <v>44498</v>
+        <v>44530</v>
       </c>
       <c r="B59" s="4">
         <v>3.44</v>
@@ -2093,7 +2104,7 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="3">
-        <v>44469</v>
+        <v>44498</v>
       </c>
       <c r="B60" s="4">
         <v>3.44</v>
@@ -2107,7 +2118,7 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="3">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="B61" s="4">
         <v>3.44</v>
@@ -2121,7 +2132,7 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="3">
-        <v>44407</v>
+        <v>44439</v>
       </c>
       <c r="B62" s="4">
         <v>3.44</v>
@@ -2135,21 +2146,21 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="3">
-        <v>44377</v>
+        <v>44407</v>
       </c>
       <c r="B63" s="4">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="C63" s="4">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="D63" s="4">
-        <v>4.56</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="3">
-        <v>44347</v>
+        <v>44377</v>
       </c>
       <c r="B64" s="4">
         <v>3.26</v>
@@ -2163,13 +2174,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="3">
-        <v>44315</v>
+        <v>44347</v>
       </c>
       <c r="B65" s="4">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="C65" s="4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="D65" s="4">
         <v>4.56</v>
@@ -2177,21 +2188,21 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="3">
-        <v>44286</v>
+        <v>44315</v>
       </c>
       <c r="B66" s="4">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="C66" s="4">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="D66" s="4">
-        <v>4.2</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="3">
-        <v>44253</v>
+        <v>44286</v>
       </c>
       <c r="B67" s="4">
         <v>2.94</v>
@@ -2205,7 +2216,7 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="3">
-        <v>44225</v>
+        <v>44253</v>
       </c>
       <c r="B68" s="4">
         <v>2.94</v>
@@ -2219,7 +2230,7 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="3">
-        <v>44196</v>
+        <v>44225</v>
       </c>
       <c r="B69" s="4">
         <v>2.94</v>
@@ -2233,7 +2244,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="3">
-        <v>44165</v>
+        <v>44196</v>
       </c>
       <c r="B70" s="4">
         <v>2.94</v>
@@ -2247,7 +2258,7 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="3">
-        <v>44134</v>
+        <v>44165</v>
       </c>
       <c r="B71" s="4">
         <v>2.94</v>
@@ -2256,18 +2267,18 @@
         <v>2.55</v>
       </c>
       <c r="D71" s="4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="3">
-        <v>44104</v>
+        <v>44134</v>
       </c>
       <c r="B72" s="4">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="C72" s="4">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="D72" s="4">
         <v>0</v>
@@ -2275,7 +2286,7 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="3">
-        <v>44074</v>
+        <v>44104</v>
       </c>
       <c r="B73" s="4">
         <v>3.03</v>
@@ -2289,13 +2300,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="3">
-        <v>44043</v>
+        <v>44074</v>
       </c>
       <c r="B74" s="4">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="C74" s="4">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="D74" s="4">
         <v>0</v>
@@ -2303,13 +2314,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="3">
-        <v>44012</v>
+        <v>44043</v>
       </c>
       <c r="B75" s="4">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="C75" s="4">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="D75" s="4">
         <v>0</v>
@@ -2317,7 +2328,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="3">
-        <v>43980</v>
+        <v>44012</v>
       </c>
       <c r="B76" s="4">
         <v>3.24</v>
@@ -2331,7 +2342,7 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="3">
-        <v>43951</v>
+        <v>43980</v>
       </c>
       <c r="B77" s="4">
         <v>3.24</v>
@@ -2345,7 +2356,7 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="3">
-        <v>43921</v>
+        <v>43951</v>
       </c>
       <c r="B78" s="4">
         <v>3.24</v>
@@ -2359,13 +2370,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="3">
-        <v>43888</v>
+        <v>43921</v>
       </c>
       <c r="B79" s="4">
-        <v>3.11</v>
+        <v>3.24</v>
       </c>
       <c r="C79" s="4">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="D79" s="4">
         <v>0</v>
@@ -2373,7 +2384,7 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="3">
-        <v>43860</v>
+        <v>43888</v>
       </c>
       <c r="B80" s="4">
         <v>3.11</v>
@@ -2387,10 +2398,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="3">
-        <v>43830</v>
+        <v>43860</v>
       </c>
       <c r="B81" s="4">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="C81" s="4">
         <v>2.66</v>
@@ -2401,13 +2412,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="3">
-        <v>43798</v>
+        <v>43830</v>
       </c>
       <c r="B82" s="4">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="C82" s="4">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="D82" s="4">
         <v>0</v>
@@ -2415,7 +2426,7 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="3">
-        <v>43769</v>
+        <v>43798</v>
       </c>
       <c r="B83" s="4">
         <v>2.85</v>
@@ -2429,13 +2440,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="3">
-        <v>43738</v>
+        <v>43769</v>
       </c>
       <c r="B84" s="4">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="C84" s="4">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="D84" s="4">
         <v>0</v>
@@ -2443,7 +2454,7 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="3">
-        <v>43707</v>
+        <v>43738</v>
       </c>
       <c r="B85" s="4">
         <v>2.75</v>
@@ -2457,13 +2468,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="3">
-        <v>43677</v>
+        <v>43707</v>
       </c>
       <c r="B86" s="4">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="C86" s="4">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="D86" s="4">
         <v>0</v>
@@ -2471,13 +2482,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="3">
-        <v>43644</v>
+        <v>43677</v>
       </c>
       <c r="B87" s="4">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="C87" s="4">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="D87" s="4">
         <v>0</v>
@@ -2485,7 +2496,7 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="3">
-        <v>43616</v>
+        <v>43644</v>
       </c>
       <c r="B88" s="4">
         <v>2.68</v>
@@ -2499,13 +2510,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="3">
-        <v>43585</v>
+        <v>43616</v>
       </c>
       <c r="B89" s="4">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="C89" s="4">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="D89" s="4">
         <v>0</v>
@@ -2513,13 +2524,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="3">
-        <v>43553</v>
+        <v>43585</v>
       </c>
       <c r="B90" s="4">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="C90" s="4">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="D90" s="4">
         <v>0</v>
@@ -2527,13 +2538,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="3">
-        <v>43523</v>
+        <v>43553</v>
       </c>
       <c r="B91" s="4">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="C91" s="4">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="D91" s="4">
         <v>0</v>
@@ -2541,10 +2552,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="3">
-        <v>43496</v>
+        <v>43523</v>
       </c>
       <c r="B92" s="4">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="C92" s="4">
         <v>2.64</v>
@@ -2555,10 +2566,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="3">
-        <v>43462</v>
+        <v>43496</v>
       </c>
       <c r="B93" s="4">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="C93" s="4">
         <v>2.64</v>
@@ -2569,13 +2580,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="3">
-        <v>43434</v>
+        <v>43462</v>
       </c>
       <c r="B94" s="4">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="C94" s="4">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="D94" s="4">
         <v>0</v>
@@ -2583,7 +2594,7 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="3">
-        <v>43404</v>
+        <v>43434</v>
       </c>
       <c r="B95" s="4">
         <v>3.25</v>
@@ -2597,13 +2608,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="3">
-        <v>43371</v>
+        <v>43404</v>
       </c>
       <c r="B96" s="4">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="C96" s="4">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="D96" s="4">
         <v>0</v>
@@ -2611,10 +2622,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="3">
-        <v>43343</v>
+        <v>43371</v>
       </c>
       <c r="B97" s="4">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="C97" s="4">
         <v>2.89</v>
@@ -2625,7 +2636,7 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="3">
-        <v>43312</v>
+        <v>43343</v>
       </c>
       <c r="B98" s="4">
         <v>3.55</v>
@@ -2639,13 +2650,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="3">
-        <v>43280</v>
+        <v>43312</v>
       </c>
       <c r="B99" s="4">
-        <v>3.69</v>
+        <v>3.55</v>
       </c>
       <c r="C99" s="4">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="D99" s="4">
         <v>0</v>
@@ -2653,7 +2664,7 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="3">
-        <v>43251</v>
+        <v>43280</v>
       </c>
       <c r="B100" s="4">
         <v>3.69</v>
@@ -2667,7 +2678,7 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="3">
-        <v>43220</v>
+        <v>43251</v>
       </c>
       <c r="B101" s="4">
         <v>3.69</v>
@@ -2681,7 +2692,7 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="3">
-        <v>43189</v>
+        <v>43220</v>
       </c>
       <c r="B102" s="4">
         <v>3.69</v>
@@ -2695,7 +2706,7 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="3">
-        <v>43158</v>
+        <v>43189</v>
       </c>
       <c r="B103" s="4">
         <v>3.69</v>
@@ -2709,7 +2720,7 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="3">
-        <v>43131</v>
+        <v>43158</v>
       </c>
       <c r="B104" s="4">
         <v>3.69</v>
@@ -2723,7 +2734,7 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="3">
-        <v>43098</v>
+        <v>43131</v>
       </c>
       <c r="B105" s="4">
         <v>3.69</v>
@@ -2737,7 +2748,7 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="3">
-        <v>43069</v>
+        <v>43098</v>
       </c>
       <c r="B106" s="4">
         <v>3.69</v>
@@ -2751,7 +2762,7 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="3">
-        <v>43039</v>
+        <v>43069</v>
       </c>
       <c r="B107" s="4">
         <v>3.69</v>
@@ -2765,13 +2776,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="3">
-        <v>43007</v>
+        <v>43039</v>
       </c>
       <c r="B108" s="4">
         <v>3.69</v>
       </c>
       <c r="C108" s="4">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="D108" s="4">
         <v>0</v>
@@ -2779,10 +2790,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="3">
-        <v>42978</v>
+        <v>43007</v>
       </c>
       <c r="B109" s="4">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="C109" s="4">
         <v>2.82</v>
@@ -2793,13 +2804,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="3">
-        <v>42947</v>
+        <v>42978</v>
       </c>
       <c r="B110" s="4">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="C110" s="4">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="D110" s="4">
         <v>0</v>
@@ -2807,13 +2818,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="3">
-        <v>42916</v>
+        <v>42947</v>
       </c>
       <c r="B111" s="4">
-        <v>3.57</v>
+        <v>3.65</v>
       </c>
       <c r="C111" s="4">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="D111" s="4">
         <v>0</v>
@@ -2821,7 +2832,7 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="3">
-        <v>42881</v>
+        <v>42916</v>
       </c>
       <c r="B112" s="4">
         <v>3.57</v>
@@ -2835,7 +2846,7 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="3">
-        <v>42853</v>
+        <v>42881</v>
       </c>
       <c r="B113" s="4">
         <v>3.57</v>
@@ -2849,13 +2860,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="3">
-        <v>42825</v>
+        <v>42853</v>
       </c>
       <c r="B114" s="4">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="C114" s="4">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="D114" s="4">
         <v>0</v>
@@ -2863,13 +2874,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="3">
-        <v>42790</v>
+        <v>42825</v>
       </c>
       <c r="B115" s="4">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="C115" s="4">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="D115" s="4">
         <v>0</v>
@@ -2877,13 +2888,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="3">
-        <v>42760</v>
+        <v>42790</v>
       </c>
       <c r="B116" s="4">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="C116" s="4">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="D116" s="4">
         <v>0</v>
@@ -2891,13 +2902,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="3">
-        <v>42733</v>
+        <v>42760</v>
       </c>
       <c r="B117" s="4">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="C117" s="4">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="D117" s="4">
         <v>0</v>
@@ -2905,13 +2916,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="3">
-        <v>42704</v>
+        <v>42733</v>
       </c>
       <c r="B118" s="4">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="C118" s="4">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="D118" s="4">
         <v>0</v>
@@ -2919,10 +2930,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="3">
-        <v>42674</v>
+        <v>42704</v>
       </c>
       <c r="B119" s="4">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="C119" s="4">
         <v>1.89</v>
@@ -2933,13 +2944,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="3">
-        <v>42643</v>
+        <v>42674</v>
       </c>
       <c r="B120" s="4">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="C120" s="4">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="D120" s="4">
         <v>0</v>
@@ -2947,13 +2958,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="3">
-        <v>42613</v>
+        <v>42643</v>
       </c>
       <c r="B121" s="4">
         <v>2.32</v>
       </c>
       <c r="C121" s="4">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="D121" s="4">
         <v>0</v>
@@ -2961,13 +2972,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="3">
-        <v>42580</v>
+        <v>42613</v>
       </c>
       <c r="B122" s="4">
         <v>2.32</v>
       </c>
       <c r="C122" s="4">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="D122" s="4">
         <v>0</v>
@@ -2975,13 +2986,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="3">
-        <v>42521</v>
+        <v>42580</v>
       </c>
       <c r="B123" s="4">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="C123" s="4">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="D123" s="4">
         <v>0</v>
@@ -2989,7 +3000,7 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="3">
-        <v>42489</v>
+        <v>42521</v>
       </c>
       <c r="B124" s="4">
         <v>2.02</v>
@@ -3003,13 +3014,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="3">
-        <v>42426</v>
+        <v>42489</v>
       </c>
       <c r="B125" s="4">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="C125" s="4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="D125" s="4">
         <v>0</v>
@@ -3017,13 +3028,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="3">
-        <v>42398</v>
+        <v>42426</v>
       </c>
       <c r="B126" s="4">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="C126" s="4">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="D126" s="4">
         <v>0</v>
@@ -3031,10 +3042,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="3">
-        <v>42368</v>
+        <v>42398</v>
       </c>
       <c r="B127" s="4">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="C127" s="4">
         <v>1.58</v>
@@ -3045,13 +3056,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="3">
-        <v>42338</v>
+        <v>42368</v>
       </c>
       <c r="B128" s="4">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="C128" s="4">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="D128" s="4">
         <v>0</v>
@@ -3059,13 +3070,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="3">
-        <v>42307</v>
+        <v>42338</v>
       </c>
       <c r="B129" s="4">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="C129" s="4">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="D129" s="4">
         <v>0</v>
@@ -3073,13 +3084,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="3">
-        <v>42291</v>
+        <v>42307</v>
       </c>
       <c r="B130" s="4">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="C130" s="4">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="D130" s="4">
         <v>0</v>
@@ -3087,10 +3098,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="3">
-        <v>42277</v>
+        <v>42291</v>
       </c>
       <c r="B131" s="4">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="C131" s="4">
         <v>1.77</v>
@@ -3101,13 +3112,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="3">
-        <v>42262</v>
+        <v>42277</v>
       </c>
       <c r="B132" s="4">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="C132" s="4">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="D132" s="4">
         <v>0</v>
@@ -3115,10 +3126,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="3">
-        <v>42247</v>
+        <v>42262</v>
       </c>
       <c r="B133" s="4">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="C133" s="4">
         <v>1.8</v>
@@ -3129,13 +3140,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="3">
-        <v>42230</v>
+        <v>42247</v>
       </c>
       <c r="B134" s="4">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="C134" s="4">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="D134" s="4">
         <v>0</v>
@@ -3143,13 +3154,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="3">
-        <v>42216</v>
+        <v>42230</v>
       </c>
       <c r="B135" s="4">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="C135" s="4">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="D135" s="4">
         <v>0</v>
@@ -3157,13 +3168,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="3">
-        <v>42200</v>
+        <v>42216</v>
       </c>
       <c r="B136" s="4">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="C136" s="4">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="D136" s="4">
         <v>0</v>
@@ -3171,10 +3182,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="3">
-        <v>42185</v>
+        <v>42200</v>
       </c>
       <c r="B137" s="4">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="C137" s="4">
         <v>1.96</v>
@@ -3185,13 +3196,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="3">
-        <v>42170</v>
+        <v>42185</v>
       </c>
       <c r="B138" s="4">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="C138" s="4">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="D138" s="4">
         <v>0</v>
@@ -3199,7 +3210,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="3">
-        <v>42153</v>
+        <v>42170</v>
       </c>
       <c r="B139" s="4">
         <v>2.58</v>
@@ -3213,13 +3224,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="3">
-        <v>42139</v>
+        <v>42153</v>
       </c>
       <c r="B140" s="4">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="C140" s="4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="D140" s="4">
         <v>0</v>
@@ -3227,7 +3238,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="3">
-        <v>42124</v>
+        <v>42139</v>
       </c>
       <c r="B141" s="4">
         <v>2.61</v>
@@ -3241,7 +3252,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="3">
-        <v>42109</v>
+        <v>42124</v>
       </c>
       <c r="B142" s="4">
         <v>2.61</v>
@@ -3255,7 +3266,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="3">
-        <v>42094</v>
+        <v>42109</v>
       </c>
       <c r="B143" s="4">
         <v>2.61</v>
@@ -3269,10 +3280,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="3">
-        <v>42076</v>
+        <v>42094</v>
       </c>
       <c r="B144" s="4">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="C144" s="4">
         <v>1.98</v>
@@ -3283,10 +3294,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="3">
-        <v>42061</v>
+        <v>42076</v>
       </c>
       <c r="B145" s="4">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="C145" s="4">
         <v>1.98</v>
@@ -3297,13 +3308,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="3">
-        <v>42048</v>
+        <v>42061</v>
       </c>
       <c r="B146" s="4">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="C146" s="4">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="D146" s="4">
         <v>0</v>
@@ -3311,13 +3322,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="3">
-        <v>42034</v>
+        <v>42048</v>
       </c>
       <c r="B147" s="4">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="C147" s="4">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="D147" s="4">
         <v>0</v>
@@ -3325,13 +3336,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="3">
-        <v>42019</v>
+        <v>42034</v>
       </c>
       <c r="B148" s="4">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="C148" s="4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="D148" s="4">
         <v>0</v>
@@ -3339,13 +3350,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="3">
-        <v>42004</v>
+        <v>42019</v>
       </c>
       <c r="B149" s="4">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="C149" s="4">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="D149" s="4">
         <v>0</v>
@@ -3353,13 +3364,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="3">
-        <v>41988</v>
+        <v>42004</v>
       </c>
       <c r="B150" s="4">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="C150" s="4">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="D150" s="4">
         <v>0</v>
@@ -3367,10 +3378,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="3">
-        <v>41971</v>
+        <v>41988</v>
       </c>
       <c r="B151" s="4">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="C151" s="4">
         <v>2.2</v>
@@ -3381,13 +3392,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="3">
-        <v>41957</v>
+        <v>41971</v>
       </c>
       <c r="B152" s="4">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="C152" s="4">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="D152" s="4">
         <v>0</v>
@@ -3395,13 +3406,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="3">
-        <v>41943</v>
+        <v>41957</v>
       </c>
       <c r="B153" s="4">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="C153" s="4">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="D153" s="4">
         <v>0</v>
@@ -3409,13 +3420,13 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="3">
-        <v>41927</v>
+        <v>41943</v>
       </c>
       <c r="B154" s="4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="C154" s="4">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="D154" s="4">
         <v>0</v>
@@ -3423,7 +3434,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="3">
-        <v>41912</v>
+        <v>41927</v>
       </c>
       <c r="B155" s="4">
         <v>3.05</v>
@@ -3437,7 +3448,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="3">
-        <v>41897</v>
+        <v>41912</v>
       </c>
       <c r="B156" s="4">
         <v>3.05</v>
@@ -3451,13 +3462,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="3">
-        <v>41883</v>
+        <v>41897</v>
       </c>
       <c r="B157" s="4">
         <v>3.05</v>
       </c>
       <c r="C157" s="4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="D157" s="4">
         <v>0</v>
@@ -3465,7 +3476,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="3">
-        <v>41866</v>
+        <v>41883</v>
       </c>
       <c r="B158" s="4">
         <v>3.05</v>
@@ -3479,7 +3490,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="3">
-        <v>41851</v>
+        <v>41866</v>
       </c>
       <c r="B159" s="4">
         <v>3.05</v>
@@ -3493,13 +3504,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="3">
-        <v>41835</v>
+        <v>41851</v>
       </c>
       <c r="B160" s="4">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="C160" s="4">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="D160" s="4">
         <v>0</v>
@@ -3507,13 +3518,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="3">
-        <v>41820</v>
+        <v>41835</v>
       </c>
       <c r="B161" s="4">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="C161" s="4">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="D161" s="4">
         <v>0</v>
@@ -3521,13 +3532,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="3">
-        <v>41803</v>
+        <v>41820</v>
       </c>
       <c r="B162" s="4">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="C162" s="4">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="D162" s="4">
         <v>0</v>
@@ -3535,13 +3546,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="3">
-        <v>41789</v>
+        <v>41803</v>
       </c>
       <c r="B163" s="4">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="C163" s="4">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="D163" s="4">
         <v>0</v>
@@ -3549,13 +3560,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="3">
-        <v>41774</v>
+        <v>41789</v>
       </c>
       <c r="B164" s="4">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="C164" s="4">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="D164" s="4">
         <v>0</v>
@@ -3563,10 +3574,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="3">
-        <v>41759</v>
+        <v>41774</v>
       </c>
       <c r="B165" s="4">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="C165" s="4">
         <v>2.14</v>
@@ -3577,13 +3588,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="3">
-        <v>41729</v>
+        <v>41759</v>
       </c>
       <c r="B166" s="4">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="C166" s="4">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="D166" s="4">
         <v>0</v>
@@ -3591,13 +3602,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="3">
-        <v>41697</v>
+        <v>41729</v>
       </c>
       <c r="B167" s="4">
-        <v>3.03</v>
+        <v>2.81</v>
       </c>
       <c r="C167" s="4">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="D167" s="4">
         <v>0</v>
@@ -3605,13 +3616,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="3">
-        <v>41687</v>
+        <v>41697</v>
       </c>
       <c r="B168" s="4">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="C168" s="4">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="D168" s="4">
         <v>0</v>
@@ -3619,13 +3630,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="3">
-        <v>41668</v>
+        <v>41687</v>
       </c>
       <c r="B169" s="4">
-        <v>3.51</v>
+        <v>3.41</v>
       </c>
       <c r="C169" s="4">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="D169" s="4">
         <v>0</v>
@@ -3633,13 +3644,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="3">
-        <v>41655</v>
+        <v>41668</v>
       </c>
       <c r="B170" s="4">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="C170" s="4">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="D170" s="4">
         <v>0</v>
@@ -3647,13 +3658,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="3">
-        <v>41639</v>
+        <v>41655</v>
       </c>
       <c r="B171" s="4">
-        <v>3.68</v>
+        <v>3.56</v>
       </c>
       <c r="C171" s="4">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="D171" s="4">
         <v>0</v>
@@ -3661,13 +3672,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="3">
-        <v>41624</v>
+        <v>41639</v>
       </c>
       <c r="B172" s="4">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="C172" s="4">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="D172" s="4">
         <v>0</v>
@@ -3675,10 +3686,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="3">
-        <v>41610</v>
+        <v>41624</v>
       </c>
       <c r="B173" s="4">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="C173" s="4">
         <v>2.62</v>
@@ -3689,13 +3700,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="3">
-        <v>41592</v>
+        <v>41610</v>
       </c>
       <c r="B174" s="4">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="C174" s="4">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="D174" s="4">
         <v>0</v>
@@ -3703,13 +3714,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="3">
-        <v>41578</v>
+        <v>41592</v>
       </c>
       <c r="B175" s="4">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C175" s="4">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="D175" s="4">
         <v>0</v>
@@ -3717,13 +3728,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="3">
-        <v>41562</v>
+        <v>41578</v>
       </c>
       <c r="B176" s="4">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="C176" s="4">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="D176" s="4">
         <v>0</v>
@@ -3731,7 +3742,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="3">
-        <v>41548</v>
+        <v>41562</v>
       </c>
       <c r="B177" s="4">
         <v>4.72</v>
@@ -3745,13 +3756,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="3">
-        <v>41456</v>
+        <v>41548</v>
       </c>
       <c r="B178" s="4">
-        <v>5.52</v>
+        <v>4.72</v>
       </c>
       <c r="C178" s="4">
-        <v>3.58</v>
+        <v>3.07</v>
       </c>
       <c r="D178" s="4">
         <v>0</v>
@@ -3759,13 +3770,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="3">
-        <v>41428</v>
+        <v>41456</v>
       </c>
       <c r="B179" s="4">
-        <v>5.26</v>
+        <v>5.52</v>
       </c>
       <c r="C179" s="4">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="D179" s="4">
         <v>0</v>
@@ -3773,13 +3784,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="3">
-        <v>41409</v>
+        <v>41428</v>
       </c>
       <c r="B180" s="4">
         <v>5.26</v>
       </c>
       <c r="C180" s="4">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="D180" s="4">
         <v>0</v>
@@ -3787,13 +3798,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="3">
-        <v>41394</v>
+        <v>41409</v>
       </c>
       <c r="B181" s="4">
-        <v>5.34</v>
+        <v>5.26</v>
       </c>
       <c r="C181" s="4">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="D181" s="4">
         <v>0</v>
@@ -3801,13 +3812,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="3">
-        <v>41379</v>
+        <v>41394</v>
       </c>
       <c r="B182" s="4">
         <v>5.34</v>
       </c>
       <c r="C182" s="4">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="D182" s="4">
         <v>0</v>
@@ -3815,13 +3826,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="3">
-        <v>41362</v>
+        <v>41379</v>
       </c>
       <c r="B183" s="4">
         <v>5.34</v>
       </c>
       <c r="C183" s="4">
-        <v>2.96</v>
+        <v>3.14</v>
       </c>
       <c r="D183" s="4">
         <v>0</v>
@@ -3829,13 +3840,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="3">
-        <v>41348</v>
+        <v>41362</v>
       </c>
       <c r="B184" s="4">
         <v>5.34</v>
       </c>
       <c r="C184" s="4">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="D184" s="4">
         <v>0</v>
@@ -3843,13 +3854,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="3">
-        <v>41327</v>
+        <v>41348</v>
       </c>
       <c r="B185" s="4">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="C185" s="4">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="D185" s="4">
         <v>0</v>
@@ -3857,13 +3868,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="3">
-        <v>41304</v>
+        <v>41327</v>
       </c>
       <c r="B186" s="4">
         <v>5</v>
       </c>
       <c r="C186" s="4">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="D186" s="4">
         <v>0</v>
@@ -3871,13 +3882,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="3">
-        <v>41289</v>
+        <v>41304</v>
       </c>
       <c r="B187" s="4">
         <v>5</v>
       </c>
       <c r="C187" s="4">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="D187" s="4">
         <v>0</v>
@@ -3885,13 +3896,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="3">
-        <v>41256</v>
+        <v>41289</v>
       </c>
       <c r="B188" s="4">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="C188" s="4">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="D188" s="4">
         <v>0</v>
@@ -3899,13 +3910,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="3">
-        <v>41243</v>
+        <v>41256</v>
       </c>
       <c r="B189" s="4">
         <v>4.98</v>
       </c>
       <c r="C189" s="4">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="D189" s="4">
         <v>0</v>
@@ -3913,10 +3924,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="3">
-        <v>41228</v>
+        <v>41243</v>
       </c>
       <c r="B190" s="4">
-        <v>5.4</v>
+        <v>4.98</v>
       </c>
       <c r="C190" s="4">
         <v>2.52</v>
@@ -3927,13 +3938,13 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="3">
-        <v>41208</v>
+        <v>41228</v>
       </c>
       <c r="B191" s="4">
-        <v>5.52</v>
+        <v>5.4</v>
       </c>
       <c r="C191" s="4">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="D191" s="4">
         <v>0</v>
@@ -3941,10 +3952,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="3">
-        <v>41197</v>
+        <v>41208</v>
       </c>
       <c r="B192" s="4">
-        <v>4.99</v>
+        <v>5.52</v>
       </c>
       <c r="C192" s="4">
         <v>2.59</v>
@@ -3955,13 +3966,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="3">
-        <v>41184</v>
+        <v>41197</v>
       </c>
       <c r="B193" s="4">
-        <v>4.26</v>
+        <v>4.99</v>
       </c>
       <c r="C193" s="4">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="D193" s="4">
         <v>0</v>
@@ -3969,13 +3980,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="3">
-        <v>41166</v>
+        <v>41184</v>
       </c>
       <c r="B194" s="4">
-        <v>3.91</v>
+        <v>4.26</v>
       </c>
       <c r="C194" s="4">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="D194" s="4">
         <v>0</v>
@@ -3983,13 +3994,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="3">
-        <v>41152</v>
+        <v>41166</v>
       </c>
       <c r="B195" s="4">
-        <v>3.87</v>
+        <v>3.91</v>
       </c>
       <c r="C195" s="4">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="D195" s="4">
         <v>0</v>
@@ -3997,7 +4008,7 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="3">
-        <v>41135</v>
+        <v>41152</v>
       </c>
       <c r="B196" s="4">
         <v>3.87</v>
@@ -4011,7 +4022,7 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="3">
-        <v>41121</v>
+        <v>41135</v>
       </c>
       <c r="B197" s="4">
         <v>3.87</v>
@@ -4025,13 +4036,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="3">
-        <v>41103</v>
+        <v>41121</v>
       </c>
       <c r="B198" s="4">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="C198" s="4">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="D198" s="4">
         <v>0</v>
@@ -4039,13 +4050,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="3">
-        <v>41089</v>
+        <v>41103</v>
       </c>
       <c r="B199" s="4">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="C199" s="4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="D199" s="4">
         <v>0</v>
@@ -4053,13 +4064,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="3">
-        <v>41075</v>
+        <v>41089</v>
       </c>
       <c r="B200" s="4">
-        <v>4.04</v>
+        <v>3.84</v>
       </c>
       <c r="C200" s="4">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="D200" s="4">
         <v>0</v>
@@ -4067,7 +4078,7 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="3">
-        <v>41060</v>
+        <v>41075</v>
       </c>
       <c r="B201" s="4">
         <v>4.04</v>
@@ -4081,13 +4092,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="3">
-        <v>41044</v>
+        <v>41060</v>
       </c>
       <c r="B202" s="4">
-        <v>4.41</v>
+        <v>4.04</v>
       </c>
       <c r="C202" s="4">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="D202" s="4">
         <v>0</v>
@@ -4095,13 +4106,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="3">
-        <v>41029</v>
+        <v>41044</v>
       </c>
       <c r="B203" s="4">
-        <v>4.66</v>
+        <v>4.41</v>
       </c>
       <c r="C203" s="4">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="D203" s="4">
         <v>0</v>
@@ -4109,13 +4120,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="3">
-        <v>41014</v>
+        <v>41029</v>
       </c>
       <c r="B204" s="4">
-        <v>4.79</v>
+        <v>4.66</v>
       </c>
       <c r="C204" s="4">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="D204" s="4">
         <v>0</v>
@@ -4123,13 +4134,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="3">
-        <v>40995</v>
+        <v>41014</v>
       </c>
       <c r="B205" s="4">
-        <v>4.95</v>
+        <v>4.79</v>
       </c>
       <c r="C205" s="4">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="D205" s="4">
         <v>0</v>
@@ -4137,13 +4148,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="3">
-        <v>40982</v>
+        <v>40995</v>
       </c>
       <c r="B206" s="4">
-        <v>5.02</v>
+        <v>4.95</v>
       </c>
       <c r="C206" s="4">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="D206" s="4">
         <v>0</v>
@@ -4151,13 +4162,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="3">
-        <v>40968</v>
+        <v>40982</v>
       </c>
       <c r="B207" s="4">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
       <c r="C207" s="4">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="D207" s="4">
         <v>0</v>
@@ -4165,13 +4176,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="3">
-        <v>40954</v>
+        <v>40968</v>
       </c>
       <c r="B208" s="4">
-        <v>5.34</v>
+        <v>5.06</v>
       </c>
       <c r="C208" s="4">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="D208" s="4">
         <v>0</v>
@@ -4179,13 +4190,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="3">
-        <v>40924</v>
+        <v>40954</v>
       </c>
       <c r="B209" s="4">
-        <v>5.49</v>
+        <v>5.34</v>
       </c>
       <c r="C209" s="4">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="D209" s="4">
         <v>0</v>
@@ -4193,13 +4204,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="3">
-        <v>40907</v>
+        <v>40924</v>
       </c>
       <c r="B210" s="4">
-        <v>5.71</v>
+        <v>5.49</v>
       </c>
       <c r="C210" s="4">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="D210" s="4">
         <v>0</v>
@@ -4207,13 +4218,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="3">
-        <v>40892</v>
+        <v>40907</v>
       </c>
       <c r="B211" s="4">
-        <v>6.09</v>
+        <v>5.71</v>
       </c>
       <c r="C211" s="4">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="D211" s="4">
         <v>0</v>
@@ -4221,10 +4232,10 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="3">
-        <v>40877</v>
+        <v>40892</v>
       </c>
       <c r="B212" s="4">
-        <v>6.12</v>
+        <v>6.09</v>
       </c>
       <c r="C212" s="4">
         <v>3.48</v>
@@ -4235,13 +4246,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="3">
-        <v>40862</v>
+        <v>40877</v>
       </c>
       <c r="B213" s="4">
-        <v>6.38</v>
+        <v>6.12</v>
       </c>
       <c r="C213" s="4">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="D213" s="4">
         <v>0</v>
@@ -4249,13 +4260,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="3">
-        <v>40847</v>
+        <v>40862</v>
       </c>
       <c r="B214" s="4">
-        <v>6.49</v>
+        <v>6.38</v>
       </c>
       <c r="C214" s="4">
-        <v>3.77</v>
+        <v>3.64</v>
       </c>
       <c r="D214" s="4">
         <v>0</v>
@@ -4263,13 +4274,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="3">
-        <v>40830</v>
+        <v>40847</v>
       </c>
       <c r="B215" s="4">
-        <v>6.66</v>
+        <v>6.49</v>
       </c>
       <c r="C215" s="4">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="D215" s="4">
         <v>0</v>
@@ -4277,13 +4288,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="3">
-        <v>40816</v>
+        <v>40830</v>
       </c>
       <c r="B216" s="4">
-        <v>6.72</v>
+        <v>6.66</v>
       </c>
       <c r="C216" s="4">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="D216" s="4">
         <v>0</v>
@@ -4291,13 +4302,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="3">
-        <v>40801</v>
+        <v>40816</v>
       </c>
       <c r="B217" s="4">
-        <v>6.9</v>
+        <v>6.72</v>
       </c>
       <c r="C217" s="4">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="D217" s="4">
         <v>0</v>
@@ -4305,13 +4316,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="3">
-        <v>40786</v>
+        <v>40801</v>
       </c>
       <c r="B218" s="4">
-        <v>8.06</v>
+        <v>6.9</v>
       </c>
       <c r="C218" s="4">
-        <v>4.48</v>
+        <v>3.8</v>
       </c>
       <c r="D218" s="4">
         <v>0</v>
@@ -4319,13 +4330,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="3">
-        <v>40770</v>
+        <v>40786</v>
       </c>
       <c r="B219" s="4">
         <v>8.06</v>
       </c>
       <c r="C219" s="4">
-        <v>4.35</v>
+        <v>4.48</v>
       </c>
       <c r="D219" s="4">
         <v>0</v>
@@ -4333,13 +4344,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="3">
-        <v>40755</v>
+        <v>40770</v>
       </c>
       <c r="B220" s="4">
-        <v>8.16</v>
+        <v>8.06</v>
       </c>
       <c r="C220" s="4">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="D220" s="4">
         <v>0</v>
@@ -4347,13 +4358,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="3">
-        <v>40694</v>
+        <v>40755</v>
       </c>
       <c r="B221" s="4">
-        <v>9.39</v>
+        <v>8.16</v>
       </c>
       <c r="C221" s="4">
-        <v>4.85</v>
+        <v>4.37</v>
       </c>
       <c r="D221" s="4">
         <v>0</v>
@@ -4361,13 +4372,13 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="3">
-        <v>40679</v>
+        <v>40694</v>
       </c>
       <c r="B222" s="4">
-        <v>10.28</v>
+        <v>9.39</v>
       </c>
       <c r="C222" s="4">
-        <v>5.76</v>
+        <v>4.85</v>
       </c>
       <c r="D222" s="4">
         <v>0</v>
@@ -4375,13 +4386,13 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="3">
-        <v>40662</v>
+        <v>40679</v>
       </c>
       <c r="B223" s="4">
-        <v>10.4</v>
+        <v>10.28</v>
       </c>
       <c r="C223" s="4">
-        <v>5.98</v>
+        <v>5.76</v>
       </c>
       <c r="D223" s="4">
         <v>0</v>
@@ -4389,13 +4400,13 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="3">
-        <v>40648</v>
+        <v>40662</v>
       </c>
       <c r="B224" s="4">
-        <v>10.64</v>
+        <v>10.4</v>
       </c>
       <c r="C224" s="4">
-        <v>6.1</v>
+        <v>5.98</v>
       </c>
       <c r="D224" s="4">
         <v>0</v>
@@ -4403,13 +4414,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="3">
-        <v>40627</v>
+        <v>40648</v>
       </c>
       <c r="B225" s="4">
-        <v>10.42</v>
+        <v>10.64</v>
       </c>
       <c r="C225" s="4">
-        <v>5.92</v>
+        <v>6.1</v>
       </c>
       <c r="D225" s="4">
         <v>0</v>
@@ -4417,13 +4428,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="3">
-        <v>40617</v>
+        <v>40627</v>
       </c>
       <c r="B226" s="4">
-        <v>10.12</v>
+        <v>10.42</v>
       </c>
       <c r="C226" s="4">
-        <v>5.66</v>
+        <v>5.92</v>
       </c>
       <c r="D226" s="4">
         <v>0</v>
@@ -4431,13 +4442,13 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="3">
-        <v>40599</v>
+        <v>40617</v>
       </c>
       <c r="B227" s="4">
-        <v>9.34</v>
+        <v>10.12</v>
       </c>
       <c r="C227" s="4">
-        <v>5.36</v>
+        <v>5.66</v>
       </c>
       <c r="D227" s="4">
         <v>0</v>
@@ -4445,13 +4456,13 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="3">
-        <v>40590</v>
+        <v>40599</v>
       </c>
       <c r="B228" s="4">
-        <v>9.5</v>
+        <v>9.34</v>
       </c>
       <c r="C228" s="4">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="D228" s="4">
         <v>0</v>
@@ -4459,7 +4470,7 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="3">
-        <v>40570</v>
+        <v>40590</v>
       </c>
       <c r="B229" s="4">
         <v>9.5</v>
@@ -4473,7 +4484,7 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="3">
-        <v>40557</v>
+        <v>40570</v>
       </c>
       <c r="B230" s="4">
         <v>9.5</v>
@@ -4487,13 +4498,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="3">
-        <v>40536</v>
+        <v>40557</v>
       </c>
       <c r="B231" s="4">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="C231" s="4">
-        <v>5.22</v>
+        <v>5.38</v>
       </c>
       <c r="D231" s="4">
         <v>0</v>
@@ -4501,10 +4512,10 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="3">
-        <v>40526</v>
+        <v>40536</v>
       </c>
       <c r="B232" s="4">
-        <v>9.18</v>
+        <v>9.4</v>
       </c>
       <c r="C232" s="4">
         <v>5.22</v>
@@ -4515,13 +4526,13 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="3">
-        <v>40512</v>
+        <v>40526</v>
       </c>
       <c r="B233" s="4">
-        <v>9.1</v>
+        <v>9.18</v>
       </c>
       <c r="C233" s="4">
-        <v>4.98</v>
+        <v>5.22</v>
       </c>
       <c r="D233" s="4">
         <v>0</v>
@@ -4529,13 +4540,13 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="3">
-        <v>40497</v>
+        <v>40512</v>
       </c>
       <c r="B234" s="4">
-        <v>9.2</v>
+        <v>9.1</v>
       </c>
       <c r="C234" s="4">
-        <v>4.93</v>
+        <v>4.98</v>
       </c>
       <c r="D234" s="4">
         <v>0</v>
@@ -4543,13 +4554,13 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="3">
-        <v>40480</v>
+        <v>40497</v>
       </c>
       <c r="B235" s="4">
-        <v>9.92</v>
+        <v>9.2</v>
       </c>
       <c r="C235" s="4">
-        <v>5.17</v>
+        <v>4.93</v>
       </c>
       <c r="D235" s="4">
         <v>0</v>
@@ -4557,13 +4568,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="3">
-        <v>40466</v>
+        <v>40480</v>
       </c>
       <c r="B236" s="4">
-        <v>10.08</v>
+        <v>9.92</v>
       </c>
       <c r="C236" s="4">
-        <v>5.23</v>
+        <v>5.17</v>
       </c>
       <c r="D236" s="4">
         <v>0</v>
@@ -4571,13 +4582,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="3">
-        <v>40451</v>
+        <v>40466</v>
       </c>
       <c r="B237" s="4">
-        <v>10.68</v>
+        <v>10.08</v>
       </c>
       <c r="C237" s="4">
-        <v>5.27</v>
+        <v>5.23</v>
       </c>
       <c r="D237" s="4">
         <v>0</v>
@@ -4585,13 +4596,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="3">
-        <v>40436</v>
+        <v>40451</v>
       </c>
       <c r="B238" s="4">
-        <v>11.78</v>
+        <v>10.68</v>
       </c>
       <c r="C238" s="4">
-        <v>5.57</v>
+        <v>5.27</v>
       </c>
       <c r="D238" s="4">
         <v>0</v>
@@ -4599,13 +4610,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="3">
-        <v>40421</v>
+        <v>40436</v>
       </c>
       <c r="B239" s="4">
-        <v>12.72</v>
+        <v>11.78</v>
       </c>
       <c r="C239" s="4">
-        <v>5.92</v>
+        <v>5.57</v>
       </c>
       <c r="D239" s="4">
         <v>0</v>
@@ -4613,13 +4624,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="3">
-        <v>40403</v>
+        <v>40421</v>
       </c>
       <c r="B240" s="4">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="C240" s="4">
-        <v>6.36</v>
+        <v>5.92</v>
       </c>
       <c r="D240" s="4">
         <v>0</v>
@@ -4627,13 +4638,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="3">
-        <v>40389</v>
+        <v>40403</v>
       </c>
       <c r="B241" s="4">
-        <v>13.82</v>
+        <v>13.56</v>
       </c>
       <c r="C241" s="4">
-        <v>6.44</v>
+        <v>6.36</v>
       </c>
       <c r="D241" s="4">
         <v>0</v>
@@ -4641,13 +4652,13 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="3">
-        <v>40368</v>
+        <v>40389</v>
       </c>
       <c r="B242" s="4">
         <v>13.82</v>
       </c>
       <c r="C242" s="4">
-        <v>6.58</v>
+        <v>6.44</v>
       </c>
       <c r="D242" s="4">
         <v>0</v>
@@ -4655,13 +4666,13 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="3">
-        <v>40354</v>
+        <v>40368</v>
       </c>
       <c r="B243" s="4">
         <v>13.82</v>
       </c>
       <c r="C243" s="4">
-        <v>6.67</v>
+        <v>6.58</v>
       </c>
       <c r="D243" s="4">
         <v>0</v>
@@ -4669,13 +4680,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="3">
-        <v>40339</v>
+        <v>40354</v>
       </c>
       <c r="B244" s="4">
-        <v>14.36</v>
+        <v>13.82</v>
       </c>
       <c r="C244" s="4">
-        <v>7.07</v>
+        <v>6.67</v>
       </c>
       <c r="D244" s="4">
         <v>0</v>
@@ -4683,13 +4694,13 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="3">
-        <v>40323</v>
+        <v>40339</v>
       </c>
       <c r="B245" s="4">
-        <v>15.16</v>
+        <v>14.36</v>
       </c>
       <c r="C245" s="4">
-        <v>7.19</v>
+        <v>7.07</v>
       </c>
       <c r="D245" s="4">
         <v>0</v>
@@ -4697,13 +4708,13 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="3">
-        <v>40308</v>
+        <v>40323</v>
       </c>
       <c r="B246" s="4">
         <v>15.16</v>
       </c>
       <c r="C246" s="4">
-        <v>7.29</v>
+        <v>7.19</v>
       </c>
       <c r="D246" s="4">
         <v>0</v>
@@ -4711,13 +4722,13 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="3">
-        <v>40291</v>
+        <v>40308</v>
       </c>
       <c r="B247" s="4">
-        <v>15.34</v>
+        <v>15.16</v>
       </c>
       <c r="C247" s="4">
-        <v>7.42</v>
+        <v>7.29</v>
       </c>
       <c r="D247" s="4">
         <v>0</v>
@@ -4725,13 +4736,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="3">
-        <v>40275</v>
+        <v>40291</v>
       </c>
       <c r="B248" s="4">
-        <v>15.38</v>
+        <v>15.34</v>
       </c>
       <c r="C248" s="4">
-        <v>7.54</v>
+        <v>7.42</v>
       </c>
       <c r="D248" s="4">
         <v>0</v>
@@ -4739,13 +4750,13 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="3">
-        <v>40261</v>
+        <v>40275</v>
       </c>
       <c r="B249" s="4">
-        <v>15.34</v>
+        <v>15.38</v>
       </c>
       <c r="C249" s="4">
-        <v>7.04</v>
+        <v>7.54</v>
       </c>
       <c r="D249" s="4">
         <v>0</v>
@@ -4753,13 +4764,13 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="3">
-        <v>40247</v>
+        <v>40261</v>
       </c>
       <c r="B250" s="4">
-        <v>15.18</v>
+        <v>15.34</v>
       </c>
       <c r="C250" s="4">
-        <v>7.12</v>
+        <v>7.04</v>
       </c>
       <c r="D250" s="4">
         <v>0</v>
@@ -4767,13 +4778,13 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="3">
-        <v>40234</v>
+        <v>40247</v>
       </c>
       <c r="B251" s="4">
-        <v>15.26</v>
+        <v>15.18</v>
       </c>
       <c r="C251" s="4">
-        <v>7.18</v>
+        <v>7.12</v>
       </c>
       <c r="D251" s="4">
         <v>0</v>
@@ -4781,13 +4792,13 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="3">
-        <v>40214</v>
+        <v>40234</v>
       </c>
       <c r="B252" s="4">
-        <v>15.34</v>
+        <v>15.26</v>
       </c>
       <c r="C252" s="4">
-        <v>7.22</v>
+        <v>7.18</v>
       </c>
       <c r="D252" s="4">
         <v>0</v>
@@ -4795,13 +4806,13 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="3">
-        <v>40200</v>
+        <v>40214</v>
       </c>
       <c r="B253" s="4">
-        <v>15.5</v>
+        <v>15.34</v>
       </c>
       <c r="C253" s="4">
-        <v>7.24</v>
+        <v>7.22</v>
       </c>
       <c r="D253" s="4">
         <v>0</v>
@@ -4809,13 +4820,13 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="3">
-        <v>40185</v>
+        <v>40200</v>
       </c>
       <c r="B254" s="4">
-        <v>15.1</v>
+        <v>15.5</v>
       </c>
       <c r="C254" s="4">
-        <v>7.18</v>
+        <v>7.24</v>
       </c>
       <c r="D254" s="4">
         <v>0</v>
@@ -4823,10 +4834,10 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="3">
-        <v>40169</v>
+        <v>40185</v>
       </c>
       <c r="B255" s="4">
-        <v>15.14</v>
+        <v>15.1</v>
       </c>
       <c r="C255" s="4">
         <v>7.18</v>
@@ -4837,13 +4848,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="3">
-        <v>40156</v>
+        <v>40169</v>
       </c>
       <c r="B256" s="4">
         <v>15.14</v>
       </c>
       <c r="C256" s="4">
-        <v>7.26</v>
+        <v>7.18</v>
       </c>
       <c r="D256" s="4">
         <v>0</v>
@@ -4851,13 +4862,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="3">
-        <v>40141</v>
+        <v>40156</v>
       </c>
       <c r="B257" s="4">
-        <v>15.72</v>
+        <v>15.14</v>
       </c>
       <c r="C257" s="4">
-        <v>7.72</v>
+        <v>7.26</v>
       </c>
       <c r="D257" s="4">
         <v>0</v>
@@ -4865,13 +4876,13 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="3">
-        <v>40126</v>
+        <v>40141</v>
       </c>
       <c r="B258" s="4">
         <v>15.72</v>
       </c>
       <c r="C258" s="4">
-        <v>8</v>
+        <v>7.72</v>
       </c>
       <c r="D258" s="4">
         <v>0</v>
@@ -4879,13 +4890,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="3">
-        <v>40108</v>
+        <v>40126</v>
       </c>
       <c r="B259" s="4">
-        <v>15.26</v>
+        <v>15.72</v>
       </c>
       <c r="C259" s="4">
-        <v>8.12</v>
+        <v>8</v>
       </c>
       <c r="D259" s="4">
         <v>0</v>
@@ -4893,13 +4904,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="3">
-        <v>40094</v>
+        <v>40108</v>
       </c>
       <c r="B260" s="4">
-        <v>14.5</v>
+        <v>15.26</v>
       </c>
       <c r="C260" s="4">
-        <v>7.68</v>
+        <v>8.12</v>
       </c>
       <c r="D260" s="4">
         <v>0</v>
@@ -4907,13 +4918,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="3">
-        <v>40078</v>
+        <v>40094</v>
       </c>
       <c r="B261" s="4">
-        <v>13.48</v>
+        <v>14.5</v>
       </c>
       <c r="C261" s="4">
-        <v>6.98</v>
+        <v>7.68</v>
       </c>
       <c r="D261" s="4">
         <v>0</v>
@@ -4921,13 +4932,13 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="3">
-        <v>40064</v>
+        <v>40078</v>
       </c>
       <c r="B262" s="4">
-        <v>13.36</v>
+        <v>13.48</v>
       </c>
       <c r="C262" s="4">
-        <v>6.8</v>
+        <v>6.98</v>
       </c>
       <c r="D262" s="4">
         <v>0</v>
@@ -4935,13 +4946,13 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="3">
-        <v>40049</v>
+        <v>40064</v>
       </c>
       <c r="B263" s="4">
-        <v>13</v>
+        <v>13.36</v>
       </c>
       <c r="C263" s="4">
-        <v>6.52</v>
+        <v>6.8</v>
       </c>
       <c r="D263" s="4">
         <v>0</v>
@@ -4949,7 +4960,7 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="3">
-        <v>40031</v>
+        <v>40049</v>
       </c>
       <c r="B264" s="4">
         <v>13</v>
@@ -4963,10 +4974,10 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="3">
-        <v>40016</v>
+        <v>40031</v>
       </c>
       <c r="B265" s="4">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="C265" s="4">
         <v>6.52</v>
@@ -4977,13 +4988,13 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="3">
-        <v>40002</v>
+        <v>40016</v>
       </c>
       <c r="B266" s="4">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="C266" s="4">
-        <v>6.64</v>
+        <v>6.52</v>
       </c>
       <c r="D266" s="4">
         <v>0</v>
@@ -4991,13 +5002,13 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="3">
-        <v>39987</v>
+        <v>40002</v>
       </c>
       <c r="B267" s="4">
-        <v>13.36</v>
+        <v>13.3</v>
       </c>
       <c r="C267" s="4">
-        <v>7</v>
+        <v>6.64</v>
       </c>
       <c r="D267" s="4">
         <v>0</v>
@@ -5005,10 +5016,10 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="3">
-        <v>39972</v>
+        <v>39987</v>
       </c>
       <c r="B268" s="4">
-        <v>14</v>
+        <v>13.36</v>
       </c>
       <c r="C268" s="4">
         <v>7</v>
@@ -5019,13 +5030,13 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="3">
-        <v>39955</v>
+        <v>39972</v>
       </c>
       <c r="B269" s="4">
-        <v>14.26</v>
+        <v>14</v>
       </c>
       <c r="C269" s="4">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="D269" s="4">
         <v>0</v>
@@ -5033,13 +5044,13 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="3">
-        <v>39941</v>
+        <v>39955</v>
       </c>
       <c r="B270" s="4">
-        <v>14.86</v>
+        <v>14.26</v>
       </c>
       <c r="C270" s="4">
-        <v>7.56</v>
+        <v>7.08</v>
       </c>
       <c r="D270" s="4">
         <v>0</v>
@@ -5047,13 +5058,13 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="3">
-        <v>39926</v>
+        <v>39941</v>
       </c>
       <c r="B271" s="4">
         <v>14.86</v>
       </c>
       <c r="C271" s="4">
-        <v>7.4</v>
+        <v>7.56</v>
       </c>
       <c r="D271" s="4">
         <v>0</v>
@@ -5061,13 +5072,13 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="3">
-        <v>39910</v>
+        <v>39926</v>
       </c>
       <c r="B272" s="4">
-        <v>12.58</v>
+        <v>14.86</v>
       </c>
       <c r="C272" s="4">
-        <v>6.44</v>
+        <v>7.4</v>
       </c>
       <c r="D272" s="4">
         <v>0</v>
@@ -5075,13 +5086,13 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="3">
-        <v>39896</v>
+        <v>39910</v>
       </c>
       <c r="B273" s="4">
-        <v>12.16</v>
+        <v>12.58</v>
       </c>
       <c r="C273" s="4">
-        <v>5.88</v>
+        <v>6.44</v>
       </c>
       <c r="D273" s="4">
         <v>0</v>
@@ -5089,13 +5100,13 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="3">
-        <v>39881</v>
+        <v>39896</v>
       </c>
       <c r="B274" s="4">
         <v>12.16</v>
       </c>
       <c r="C274" s="4">
-        <v>5.98</v>
+        <v>5.88</v>
       </c>
       <c r="D274" s="4">
         <v>0</v>
@@ -5103,10 +5114,10 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="3">
-        <v>39864</v>
+        <v>39881</v>
       </c>
       <c r="B275" s="4">
-        <v>12</v>
+        <v>12.16</v>
       </c>
       <c r="C275" s="4">
         <v>5.98</v>
@@ -5117,13 +5128,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="3">
-        <v>39850</v>
+        <v>39864</v>
       </c>
       <c r="B276" s="4">
-        <v>9.96</v>
+        <v>12</v>
       </c>
       <c r="C276" s="4">
-        <v>5</v>
+        <v>5.98</v>
       </c>
       <c r="D276" s="4">
         <v>0</v>
@@ -5131,13 +5142,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="3">
-        <v>39828</v>
+        <v>39850</v>
       </c>
       <c r="B277" s="4">
-        <v>9.02</v>
+        <v>9.96</v>
       </c>
       <c r="C277" s="4">
-        <v>4.74</v>
+        <v>5</v>
       </c>
       <c r="D277" s="4">
         <v>0</v>
@@ -5145,13 +5156,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="3">
-        <v>39820</v>
+        <v>39828</v>
       </c>
       <c r="B278" s="4">
-        <v>8.52</v>
+        <v>9.02</v>
       </c>
       <c r="C278" s="4">
-        <v>4.11</v>
+        <v>4.74</v>
       </c>
       <c r="D278" s="4">
         <v>0</v>
@@ -5159,13 +5170,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="3">
-        <v>39806</v>
+        <v>39820</v>
       </c>
       <c r="B279" s="4">
-        <v>9.5</v>
+        <v>8.52</v>
       </c>
       <c r="C279" s="4">
-        <v>3.72</v>
+        <v>4.11</v>
       </c>
       <c r="D279" s="4">
         <v>0</v>
@@ -5173,13 +5184,13 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="3">
-        <v>39791</v>
+        <v>39806</v>
       </c>
       <c r="B280" s="4">
-        <v>9.42</v>
+        <v>9.5</v>
       </c>
       <c r="C280" s="4">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="D280" s="4">
         <v>0</v>
@@ -5187,13 +5198,13 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="3">
-        <v>39776</v>
+        <v>39791</v>
       </c>
       <c r="B281" s="4">
-        <v>10.84</v>
+        <v>9.42</v>
       </c>
       <c r="C281" s="4">
-        <v>4.85</v>
+        <v>3.62</v>
       </c>
       <c r="D281" s="4">
         <v>0</v>
@@ -5201,7 +5212,7 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" s="3">
-        <v>39762</v>
+        <v>39776</v>
       </c>
       <c r="B282" s="4">
         <v>10.84</v>
@@ -5215,13 +5226,13 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" s="3">
-        <v>39744</v>
+        <v>39762</v>
       </c>
       <c r="B283" s="4">
-        <v>11.6</v>
+        <v>10.84</v>
       </c>
       <c r="C283" s="4">
-        <v>5.36</v>
+        <v>4.85</v>
       </c>
       <c r="D283" s="4">
         <v>0</v>
@@ -5229,7 +5240,7 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" s="3">
-        <v>39729</v>
+        <v>39744</v>
       </c>
       <c r="B284" s="4">
         <v>11.6</v>
@@ -5243,13 +5254,13 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="3">
-        <v>39713</v>
+        <v>39729</v>
       </c>
       <c r="B285" s="4">
-        <v>12.38</v>
+        <v>11.6</v>
       </c>
       <c r="C285" s="4">
-        <v>5.53</v>
+        <v>5.36</v>
       </c>
       <c r="D285" s="4">
         <v>0</v>
@@ -5257,13 +5268,13 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="3">
-        <v>39700</v>
+        <v>39713</v>
       </c>
       <c r="B286" s="4">
-        <v>13.44</v>
+        <v>12.38</v>
       </c>
       <c r="C286" s="4">
-        <v>6.36</v>
+        <v>5.53</v>
       </c>
       <c r="D286" s="4">
         <v>0</v>
@@ -5271,13 +5282,13 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" s="3">
-        <v>39682</v>
+        <v>39700</v>
       </c>
       <c r="B287" s="4">
-        <v>15</v>
+        <v>13.44</v>
       </c>
       <c r="C287" s="4">
-        <v>7.36</v>
+        <v>6.36</v>
       </c>
       <c r="D287" s="4">
         <v>0</v>
@@ -5285,13 +5296,13 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="3">
-        <v>39667</v>
+        <v>39682</v>
       </c>
       <c r="B288" s="4">
-        <v>16.18</v>
+        <v>15</v>
       </c>
       <c r="C288" s="4">
-        <v>7.98</v>
+        <v>7.36</v>
       </c>
       <c r="D288" s="4">
         <v>0</v>
@@ -5299,13 +5310,13 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="3">
-        <v>39652</v>
+        <v>39667</v>
       </c>
       <c r="B289" s="4">
-        <v>18.54</v>
+        <v>16.18</v>
       </c>
       <c r="C289" s="4">
-        <v>9.04</v>
+        <v>7.98</v>
       </c>
       <c r="D289" s="4">
         <v>0</v>
@@ -5313,13 +5324,13 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" s="3">
-        <v>39636</v>
+        <v>39652</v>
       </c>
       <c r="B290" s="4">
-        <v>19.02</v>
+        <v>18.54</v>
       </c>
       <c r="C290" s="4">
-        <v>9.18</v>
+        <v>9.04</v>
       </c>
       <c r="D290" s="4">
         <v>0</v>
@@ -5327,13 +5338,13 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" s="3">
-        <v>39624</v>
+        <v>39636</v>
       </c>
       <c r="B291" s="4">
-        <v>20.5</v>
+        <v>19.02</v>
       </c>
       <c r="C291" s="4">
-        <v>9.64</v>
+        <v>9.18</v>
       </c>
       <c r="D291" s="4">
         <v>0</v>
@@ -5341,13 +5352,13 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" s="3">
-        <v>39605</v>
+        <v>39624</v>
       </c>
       <c r="B292" s="4">
-        <v>22.7</v>
+        <v>20.5</v>
       </c>
       <c r="C292" s="4">
-        <v>11.16</v>
+        <v>9.64</v>
       </c>
       <c r="D292" s="4">
         <v>0</v>
@@ -5355,13 +5366,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" s="3">
-        <v>39591</v>
+        <v>39605</v>
       </c>
       <c r="B293" s="4">
-        <v>23.9</v>
+        <v>22.7</v>
       </c>
       <c r="C293" s="4">
-        <v>11.46</v>
+        <v>11.16</v>
       </c>
       <c r="D293" s="4">
         <v>0</v>
@@ -5369,13 +5380,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" s="3">
-        <v>39576</v>
+        <v>39591</v>
       </c>
       <c r="B294" s="4">
-        <v>24.96</v>
+        <v>23.9</v>
       </c>
       <c r="C294" s="4">
-        <v>11.92</v>
+        <v>11.46</v>
       </c>
       <c r="D294" s="4">
         <v>0</v>
@@ -5383,13 +5394,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" s="3">
-        <v>39561</v>
+        <v>39576</v>
       </c>
       <c r="B295" s="4">
-        <v>25.08</v>
+        <v>24.96</v>
       </c>
       <c r="C295" s="4">
-        <v>11.94</v>
+        <v>11.92</v>
       </c>
       <c r="D295" s="4">
         <v>0</v>
@@ -5397,13 +5408,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" s="3">
-        <v>39549</v>
+        <v>39561</v>
       </c>
       <c r="B296" s="4">
-        <v>26</v>
+        <v>25.08</v>
       </c>
       <c r="C296" s="4">
-        <v>11.76</v>
+        <v>11.94</v>
       </c>
       <c r="D296" s="4">
         <v>0</v>
@@ -5411,13 +5422,13 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" s="3">
-        <v>39533</v>
+        <v>39549</v>
       </c>
       <c r="B297" s="4">
-        <v>24.76</v>
+        <v>26</v>
       </c>
       <c r="C297" s="4">
-        <v>11.1</v>
+        <v>11.76</v>
       </c>
       <c r="D297" s="4">
         <v>0</v>
@@ -5425,13 +5436,13 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" s="3">
-        <v>39517</v>
+        <v>39533</v>
       </c>
       <c r="B298" s="4">
-        <v>25.3</v>
+        <v>24.76</v>
       </c>
       <c r="C298" s="4">
-        <v>11.32</v>
+        <v>11.1</v>
       </c>
       <c r="D298" s="4">
         <v>0</v>
@@ -5439,13 +5450,13 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" s="3">
-        <v>39503</v>
+        <v>39517</v>
       </c>
       <c r="B299" s="4">
         <v>25.3</v>
       </c>
       <c r="C299" s="4">
-        <v>11.7</v>
+        <v>11.32</v>
       </c>
       <c r="D299" s="4">
         <v>0</v>
@@ -5453,13 +5464,13 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" s="3">
-        <v>39483</v>
+        <v>39503</v>
       </c>
       <c r="B300" s="4">
-        <v>26.16</v>
+        <v>25.3</v>
       </c>
       <c r="C300" s="4">
-        <v>12.12</v>
+        <v>11.7</v>
       </c>
       <c r="D300" s="4">
         <v>0</v>
@@ -5467,7 +5478,7 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" s="3">
-        <v>39469</v>
+        <v>39483</v>
       </c>
       <c r="B301" s="4">
         <v>26.16</v>
@@ -5481,7 +5492,7 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" s="3">
-        <v>39456</v>
+        <v>39469</v>
       </c>
       <c r="B302" s="4">
         <v>26.16</v>
@@ -5490,6 +5501,20 @@
         <v>12.12</v>
       </c>
       <c r="D302" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="5">
+        <v>39456</v>
+      </c>
+      <c r="B303" s="6">
+        <v>26.16</v>
+      </c>
+      <c r="C303" s="6">
+        <v>12.12</v>
+      </c>
+      <c r="D303" s="6">
         <v>0</v>
       </c>
     </row>

--- a/edb_data/NAND合约平均价格.xlsx
+++ b/edb_data/NAND合约平均价格.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24048" windowHeight="12300"/>
+    <workbookView windowWidth="27948" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="合约平均价_NAND Flash(64G" sheetId="1" r:id="rId1"/>
@@ -704,19 +704,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -5505,16 +5499,16 @@
       </c>
     </row>
     <row r="303" spans="1:4">
-      <c r="A303" s="5">
+      <c r="A303" s="3">
         <v>39456</v>
       </c>
-      <c r="B303" s="6">
+      <c r="B303" s="4">
         <v>26.16</v>
       </c>
-      <c r="C303" s="6">
+      <c r="C303" s="4">
         <v>12.12</v>
       </c>
-      <c r="D303" s="6">
+      <c r="D303" s="4">
         <v>0</v>
       </c>
     </row>
